--- a/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B03_Normal_1.xlsx
+++ b/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B03_Normal_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J584"/>
+  <dimension ref="A1:K584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Segment_ID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Area</t>
         </is>
       </c>
@@ -515,6 +520,9 @@
         </is>
       </c>
       <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
         <v>24.44938674448072</v>
       </c>
     </row>
@@ -553,6 +561,9 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -591,6 +602,9 @@
         </is>
       </c>
       <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -629,6 +643,9 @@
         </is>
       </c>
       <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -667,6 +684,9 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
         <v>16.22537890841612</v>
       </c>
     </row>
@@ -705,6 +725,9 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
         <v>15.92519383307983</v>
       </c>
     </row>
@@ -743,6 +766,9 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
         <v>15.55123726155539</v>
       </c>
     </row>
@@ -781,6 +807,9 @@
         </is>
       </c>
       <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
         <v>15.50392193361757</v>
       </c>
     </row>
@@ -819,6 +848,9 @@
         </is>
       </c>
       <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
         <v>15.43409332138252</v>
       </c>
     </row>
@@ -857,6 +889,9 @@
         </is>
       </c>
       <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
         <v>15.43409332138252</v>
       </c>
     </row>
@@ -895,6 +930,9 @@
         </is>
       </c>
       <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
         <v>14.91383648998964</v>
       </c>
     </row>
@@ -933,6 +971,9 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
         <v>14.91383648998964</v>
       </c>
     </row>
@@ -971,6 +1012,9 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
         <v>13.96252814601202</v>
       </c>
     </row>
@@ -1009,6 +1053,9 @@
         </is>
       </c>
       <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
         <v>12.8845474029381</v>
       </c>
     </row>
@@ -1047,6 +1094,9 @@
         </is>
       </c>
       <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
         <v>12.56557511094277</v>
       </c>
     </row>
@@ -1085,6 +1135,9 @@
         </is>
       </c>
       <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
         <v>12.56557511094277</v>
       </c>
     </row>
@@ -1123,6 +1176,9 @@
         </is>
       </c>
       <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
         <v>12.42650727241244</v>
       </c>
     </row>
@@ -1161,6 +1217,9 @@
         </is>
       </c>
       <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
         <v>12.61222121789064</v>
       </c>
     </row>
@@ -1199,6 +1258,9 @@
         </is>
       </c>
       <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
         <v>12.6149723565889</v>
       </c>
     </row>
@@ -1237,6 +1299,9 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
         <v>12.6149723565889</v>
       </c>
     </row>
@@ -1275,6 +1340,9 @@
         </is>
       </c>
       <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
         <v>12.88726856229838</v>
       </c>
     </row>
@@ -1313,6 +1381,9 @@
         </is>
       </c>
       <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
         <v>13.08268414389388</v>
       </c>
     </row>
@@ -1351,6 +1422,9 @@
         </is>
       </c>
       <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
         <v>13.11655963642752</v>
       </c>
     </row>
@@ -1389,6 +1463,9 @@
         </is>
       </c>
       <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
         <v>13.06477406907523</v>
       </c>
     </row>
@@ -1427,6 +1504,9 @@
         </is>
       </c>
       <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
         <v>13.00822550737505</v>
       </c>
     </row>
@@ -1465,6 +1545,9 @@
         </is>
       </c>
       <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
         <v>13.00822550737505</v>
       </c>
     </row>
@@ -1503,6 +1586,9 @@
         </is>
       </c>
       <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
         <v>12.82946633796654</v>
       </c>
     </row>
@@ -1541,6 +1627,9 @@
         </is>
       </c>
       <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
         <v>12.72199060197538</v>
       </c>
     </row>
@@ -1579,6 +1668,9 @@
         </is>
       </c>
       <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
         <v>12.76786570293602</v>
       </c>
     </row>
@@ -1617,6 +1709,9 @@
         </is>
       </c>
       <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
         <v>12.94918332241907</v>
       </c>
     </row>
@@ -1655,6 +1750,9 @@
         </is>
       </c>
       <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
         <v>13.29202663846189</v>
       </c>
     </row>
@@ -1693,6 +1791,9 @@
         </is>
       </c>
       <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
         <v>13.29202663846189</v>
       </c>
     </row>
@@ -1731,6 +1832,9 @@
         </is>
       </c>
       <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
         <v>13.74461230569916</v>
       </c>
     </row>
@@ -1769,6 +1873,9 @@
         </is>
       </c>
       <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
         <v>14.01711486461985</v>
       </c>
     </row>
@@ -1807,6 +1914,9 @@
         </is>
       </c>
       <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
         <v>14.25821179004597</v>
       </c>
     </row>
@@ -1845,6 +1955,9 @@
         </is>
       </c>
       <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
         <v>14.35948117378207</v>
       </c>
     </row>
@@ -1883,6 +1996,9 @@
         </is>
       </c>
       <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
         <v>14.35948117378207</v>
       </c>
     </row>
@@ -1921,6 +2037,9 @@
         </is>
       </c>
       <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
         <v>14.39337587577508</v>
       </c>
     </row>
@@ -1959,6 +2078,9 @@
         </is>
       </c>
       <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
         <v>14.33776555810451</v>
       </c>
     </row>
@@ -1997,6 +2119,9 @@
         </is>
       </c>
       <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
         <v>14.33776555810451</v>
       </c>
     </row>
@@ -2035,6 +2160,9 @@
         </is>
       </c>
       <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
         <v>14.33776555810451</v>
       </c>
     </row>
@@ -2073,6 +2201,9 @@
         </is>
       </c>
       <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
         <v>14.46751017667901</v>
       </c>
     </row>
@@ -2111,6 +2242,9 @@
         </is>
       </c>
       <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
         <v>14.90065600322594</v>
       </c>
     </row>
@@ -2149,6 +2283,9 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" t="n">
         <v>15.10789666146953</v>
       </c>
     </row>
@@ -2187,6 +2324,9 @@
         </is>
       </c>
       <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
         <v>15.24076100085329</v>
       </c>
     </row>
@@ -2225,6 +2365,9 @@
         </is>
       </c>
       <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
         <v>15.28683754312319</v>
       </c>
     </row>
@@ -2263,6 +2406,9 @@
         </is>
       </c>
       <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
         <v>15.28683754312319</v>
       </c>
     </row>
@@ -2301,6 +2447,9 @@
         </is>
       </c>
       <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
         <v>15.45586864838683</v>
       </c>
     </row>
@@ -2339,6 +2488,9 @@
         </is>
       </c>
       <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="n">
         <v>38.49477201445094</v>
       </c>
     </row>
@@ -2377,6 +2529,9 @@
         </is>
       </c>
       <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
         <v>50.66302055048502</v>
       </c>
     </row>
@@ -2415,6 +2570,9 @@
         </is>
       </c>
       <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
         <v>50.66302055048502</v>
       </c>
     </row>
@@ -2453,6 +2611,9 @@
         </is>
       </c>
       <c r="J53" t="n">
+        <v>11</v>
+      </c>
+      <c r="K53" t="n">
         <v>73.02287512573871</v>
       </c>
     </row>
@@ -2491,6 +2652,9 @@
         </is>
       </c>
       <c r="J54" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" t="n">
         <v>27.5466963351074</v>
       </c>
     </row>
@@ -2529,6 +2693,9 @@
         </is>
       </c>
       <c r="J55" t="n">
+        <v>6</v>
+      </c>
+      <c r="K55" t="n">
         <v>25.49347212687086</v>
       </c>
     </row>
@@ -2567,6 +2734,9 @@
         </is>
       </c>
       <c r="J56" t="n">
+        <v>6</v>
+      </c>
+      <c r="K56" t="n">
         <v>23.97322394592734</v>
       </c>
     </row>
@@ -2605,6 +2775,9 @@
         </is>
       </c>
       <c r="J57" t="n">
+        <v>6</v>
+      </c>
+      <c r="K57" t="n">
         <v>21.33836097537404</v>
       </c>
     </row>
@@ -2643,6 +2816,9 @@
         </is>
       </c>
       <c r="J58" t="n">
+        <v>6</v>
+      </c>
+      <c r="K58" t="n">
         <v>21.36069899557773</v>
       </c>
     </row>
@@ -2681,6 +2857,9 @@
         </is>
       </c>
       <c r="J59" t="n">
+        <v>6</v>
+      </c>
+      <c r="K59" t="n">
         <v>21.36069899557773</v>
       </c>
     </row>
@@ -2719,6 +2898,9 @@
         </is>
       </c>
       <c r="J60" t="n">
+        <v>6</v>
+      </c>
+      <c r="K60" t="n">
         <v>23.60395345894496</v>
       </c>
     </row>
@@ -2757,6 +2939,9 @@
         </is>
       </c>
       <c r="J61" t="n">
+        <v>6</v>
+      </c>
+      <c r="K61" t="n">
         <v>23.60395345894496</v>
       </c>
     </row>
@@ -2795,6 +2980,9 @@
         </is>
       </c>
       <c r="J62" t="n">
+        <v>6</v>
+      </c>
+      <c r="K62" t="n">
         <v>30.32524846705273</v>
       </c>
     </row>
@@ -2833,6 +3021,9 @@
         </is>
       </c>
       <c r="J63" t="n">
+        <v>6</v>
+      </c>
+      <c r="K63" t="n">
         <v>33.1118269799849</v>
       </c>
     </row>
@@ -2871,6 +3062,9 @@
         </is>
       </c>
       <c r="J64" t="n">
+        <v>6</v>
+      </c>
+      <c r="K64" t="n">
         <v>33.1118269799849</v>
       </c>
     </row>
@@ -2909,6 +3103,9 @@
         </is>
       </c>
       <c r="J65" t="n">
+        <v>6</v>
+      </c>
+      <c r="K65" t="n">
         <v>93.42524075950476</v>
       </c>
     </row>
@@ -2947,6 +3144,9 @@
         </is>
       </c>
       <c r="J66" t="n">
+        <v>6</v>
+      </c>
+      <c r="K66" t="n">
         <v>93.42524075950476</v>
       </c>
     </row>
@@ -2985,6 +3185,9 @@
         </is>
       </c>
       <c r="J67" t="n">
+        <v>6</v>
+      </c>
+      <c r="K67" t="n">
         <v>93.43501340024444</v>
       </c>
     </row>
@@ -3023,6 +3226,9 @@
         </is>
       </c>
       <c r="J68" t="n">
+        <v>6</v>
+      </c>
+      <c r="K68" t="n">
         <v>93.43501340024444</v>
       </c>
     </row>
@@ -3061,6 +3267,9 @@
         </is>
       </c>
       <c r="J69" t="n">
+        <v>6</v>
+      </c>
+      <c r="K69" t="n">
         <v>29.05532579013986</v>
       </c>
     </row>
@@ -3099,6 +3308,9 @@
         </is>
       </c>
       <c r="J70" t="n">
+        <v>6</v>
+      </c>
+      <c r="K70" t="n">
         <v>29.05532579013986</v>
       </c>
     </row>
@@ -3137,6 +3349,9 @@
         </is>
       </c>
       <c r="J71" t="n">
+        <v>6</v>
+      </c>
+      <c r="K71" t="n">
         <v>10.60692062922534</v>
       </c>
     </row>
@@ -3175,6 +3390,9 @@
         </is>
       </c>
       <c r="J72" t="n">
+        <v>6</v>
+      </c>
+      <c r="K72" t="n">
         <v>10.24700477381645</v>
       </c>
     </row>
@@ -3213,6 +3431,9 @@
         </is>
       </c>
       <c r="J73" t="n">
+        <v>6</v>
+      </c>
+      <c r="K73" t="n">
         <v>10.21282575007027</v>
       </c>
     </row>
@@ -3251,6 +3472,9 @@
         </is>
       </c>
       <c r="J74" t="n">
+        <v>6</v>
+      </c>
+      <c r="K74" t="n">
         <v>9.761777786710743</v>
       </c>
     </row>
@@ -3289,6 +3513,9 @@
         </is>
       </c>
       <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
         <v>9.761777786710743</v>
       </c>
     </row>
@@ -3327,6 +3554,9 @@
         </is>
       </c>
       <c r="J76" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" t="n">
         <v>9.33637179119815</v>
       </c>
     </row>
@@ -3365,6 +3595,9 @@
         </is>
       </c>
       <c r="J77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" t="n">
         <v>9.290631264491166</v>
       </c>
     </row>
@@ -3403,6 +3636,9 @@
         </is>
       </c>
       <c r="J78" t="n">
+        <v>6</v>
+      </c>
+      <c r="K78" t="n">
         <v>9.301046132712429</v>
       </c>
     </row>
@@ -3441,6 +3677,9 @@
         </is>
       </c>
       <c r="J79" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" t="n">
         <v>9.452446335487469</v>
       </c>
     </row>
@@ -3479,6 +3718,9 @@
         </is>
       </c>
       <c r="J80" t="n">
+        <v>6</v>
+      </c>
+      <c r="K80" t="n">
         <v>9.661749357520293</v>
       </c>
     </row>
@@ -3517,6 +3759,9 @@
         </is>
       </c>
       <c r="J81" t="n">
+        <v>6</v>
+      </c>
+      <c r="K81" t="n">
         <v>9.737462158199968</v>
       </c>
     </row>
@@ -3555,6 +3800,9 @@
         </is>
       </c>
       <c r="J82" t="n">
+        <v>6</v>
+      </c>
+      <c r="K82" t="n">
         <v>9.809590006987829</v>
       </c>
     </row>
@@ -3593,6 +3841,9 @@
         </is>
       </c>
       <c r="J83" t="n">
+        <v>6</v>
+      </c>
+      <c r="K83" t="n">
         <v>9.807131585129085</v>
       </c>
     </row>
@@ -3631,6 +3882,9 @@
         </is>
       </c>
       <c r="J84" t="n">
+        <v>6</v>
+      </c>
+      <c r="K84" t="n">
         <v>10.03578416659066</v>
       </c>
     </row>
@@ -3669,6 +3923,9 @@
         </is>
       </c>
       <c r="J85" t="n">
+        <v>6</v>
+      </c>
+      <c r="K85" t="n">
         <v>10.12549314622187</v>
       </c>
     </row>
@@ -3707,6 +3964,9 @@
         </is>
       </c>
       <c r="J86" t="n">
+        <v>6</v>
+      </c>
+      <c r="K86" t="n">
         <v>10.57589925462877</v>
       </c>
     </row>
@@ -3745,6 +4005,9 @@
         </is>
       </c>
       <c r="J87" t="n">
+        <v>6</v>
+      </c>
+      <c r="K87" t="n">
         <v>10.60268682414666</v>
       </c>
     </row>
@@ -3783,6 +4046,9 @@
         </is>
       </c>
       <c r="J88" t="n">
+        <v>6</v>
+      </c>
+      <c r="K88" t="n">
         <v>10.62312997770562</v>
       </c>
     </row>
@@ -3821,6 +4087,9 @@
         </is>
       </c>
       <c r="J89" t="n">
+        <v>6</v>
+      </c>
+      <c r="K89" t="n">
         <v>10.62248024777271</v>
       </c>
     </row>
@@ -3859,6 +4128,9 @@
         </is>
       </c>
       <c r="J90" t="n">
+        <v>6</v>
+      </c>
+      <c r="K90" t="n">
         <v>10.87806600786918</v>
       </c>
     </row>
@@ -3897,6 +4169,9 @@
         </is>
       </c>
       <c r="J91" t="n">
+        <v>6</v>
+      </c>
+      <c r="K91" t="n">
         <v>10.92162235687036</v>
       </c>
     </row>
@@ -3935,6 +4210,9 @@
         </is>
       </c>
       <c r="J92" t="n">
+        <v>6</v>
+      </c>
+      <c r="K92" t="n">
         <v>10.95616069257222</v>
       </c>
     </row>
@@ -3973,6 +4251,9 @@
         </is>
       </c>
       <c r="J93" t="n">
+        <v>6</v>
+      </c>
+      <c r="K93" t="n">
         <v>11.00900355804066</v>
       </c>
     </row>
@@ -4011,6 +4292,9 @@
         </is>
       </c>
       <c r="J94" t="n">
+        <v>6</v>
+      </c>
+      <c r="K94" t="n">
         <v>11.01773536723862</v>
       </c>
     </row>
@@ -4049,6 +4333,9 @@
         </is>
       </c>
       <c r="J95" t="n">
+        <v>6</v>
+      </c>
+      <c r="K95" t="n">
         <v>11.01276194340502</v>
       </c>
     </row>
@@ -4087,6 +4374,9 @@
         </is>
       </c>
       <c r="J96" t="n">
+        <v>6</v>
+      </c>
+      <c r="K96" t="n">
         <v>10.91014021015967</v>
       </c>
     </row>
@@ -4125,6 +4415,9 @@
         </is>
       </c>
       <c r="J97" t="n">
+        <v>6</v>
+      </c>
+      <c r="K97" t="n">
         <v>10.75714398709465</v>
       </c>
     </row>
@@ -4163,6 +4456,9 @@
         </is>
       </c>
       <c r="J98" t="n">
+        <v>6</v>
+      </c>
+      <c r="K98" t="n">
         <v>10.53712094521892</v>
       </c>
     </row>
@@ -4201,6 +4497,9 @@
         </is>
       </c>
       <c r="J99" t="n">
+        <v>6</v>
+      </c>
+      <c r="K99" t="n">
         <v>10.38432375970871</v>
       </c>
     </row>
@@ -4239,6 +4538,9 @@
         </is>
       </c>
       <c r="J100" t="n">
+        <v>6</v>
+      </c>
+      <c r="K100" t="n">
         <v>10.11688682207371</v>
       </c>
     </row>
@@ -4277,6 +4579,9 @@
         </is>
       </c>
       <c r="J101" t="n">
+        <v>6</v>
+      </c>
+      <c r="K101" t="n">
         <v>10.11688682207371</v>
       </c>
     </row>
@@ -4315,6 +4620,9 @@
         </is>
       </c>
       <c r="J102" t="n">
+        <v>6</v>
+      </c>
+      <c r="K102" t="n">
         <v>9.579029976242865</v>
       </c>
     </row>
@@ -4353,6 +4661,9 @@
         </is>
       </c>
       <c r="J103" t="n">
+        <v>6</v>
+      </c>
+      <c r="K103" t="n">
         <v>9.579029976242865</v>
       </c>
     </row>
@@ -4391,6 +4702,9 @@
         </is>
       </c>
       <c r="J104" t="n">
+        <v>6</v>
+      </c>
+      <c r="K104" t="n">
         <v>9.552229142031393</v>
       </c>
     </row>
@@ -4429,6 +4743,9 @@
         </is>
       </c>
       <c r="J105" t="n">
+        <v>6</v>
+      </c>
+      <c r="K105" t="n">
         <v>9.337125357350384</v>
       </c>
     </row>
@@ -4467,6 +4784,9 @@
         </is>
       </c>
       <c r="J106" t="n">
+        <v>6</v>
+      </c>
+      <c r="K106" t="n">
         <v>8.794782428856642</v>
       </c>
     </row>
@@ -4505,6 +4825,9 @@
         </is>
       </c>
       <c r="J107" t="n">
+        <v>6</v>
+      </c>
+      <c r="K107" t="n">
         <v>8.704344846279827</v>
       </c>
     </row>
@@ -4543,6 +4866,9 @@
         </is>
       </c>
       <c r="J108" t="n">
+        <v>6</v>
+      </c>
+      <c r="K108" t="n">
         <v>8.655508037001059</v>
       </c>
     </row>
@@ -4581,6 +4907,9 @@
         </is>
       </c>
       <c r="J109" t="n">
+        <v>6</v>
+      </c>
+      <c r="K109" t="n">
         <v>8.858023257647872</v>
       </c>
     </row>
@@ -4619,6 +4948,9 @@
         </is>
       </c>
       <c r="J110" t="n">
+        <v>6</v>
+      </c>
+      <c r="K110" t="n">
         <v>8.971438026392272</v>
       </c>
     </row>
@@ -4657,6 +4989,9 @@
         </is>
       </c>
       <c r="J111" t="n">
+        <v>6</v>
+      </c>
+      <c r="K111" t="n">
         <v>9.152459961658085</v>
       </c>
     </row>
@@ -4695,6 +5030,9 @@
         </is>
       </c>
       <c r="J112" t="n">
+        <v>6</v>
+      </c>
+      <c r="K112" t="n">
         <v>9.158723808345748</v>
       </c>
     </row>
@@ -4733,6 +5071,9 @@
         </is>
       </c>
       <c r="J113" t="n">
+        <v>6</v>
+      </c>
+      <c r="K113" t="n">
         <v>9.153048952007417</v>
       </c>
     </row>
@@ -4771,6 +5112,9 @@
         </is>
       </c>
       <c r="J114" t="n">
+        <v>6</v>
+      </c>
+      <c r="K114" t="n">
         <v>9.256091506980455</v>
       </c>
     </row>
@@ -4809,6 +5153,9 @@
         </is>
       </c>
       <c r="J115" t="n">
+        <v>6</v>
+      </c>
+      <c r="K115" t="n">
         <v>9.403867914857166</v>
       </c>
     </row>
@@ -4847,6 +5194,9 @@
         </is>
       </c>
       <c r="J116" t="n">
+        <v>6</v>
+      </c>
+      <c r="K116" t="n">
         <v>9.368423488149045</v>
       </c>
     </row>
@@ -4885,6 +5235,9 @@
         </is>
       </c>
       <c r="J117" t="n">
+        <v>6</v>
+      </c>
+      <c r="K117" t="n">
         <v>9.268971225409532</v>
       </c>
     </row>
@@ -4923,6 +5276,9 @@
         </is>
       </c>
       <c r="J118" t="n">
+        <v>6</v>
+      </c>
+      <c r="K118" t="n">
         <v>9.159228079297097</v>
       </c>
     </row>
@@ -4961,6 +5317,9 @@
         </is>
       </c>
       <c r="J119" t="n">
+        <v>6</v>
+      </c>
+      <c r="K119" t="n">
         <v>9.051605715933476</v>
       </c>
     </row>
@@ -4999,6 +5358,9 @@
         </is>
       </c>
       <c r="J120" t="n">
+        <v>6</v>
+      </c>
+      <c r="K120" t="n">
         <v>9.049780946629296</v>
       </c>
     </row>
@@ -5037,6 +5399,9 @@
         </is>
       </c>
       <c r="J121" t="n">
+        <v>6</v>
+      </c>
+      <c r="K121" t="n">
         <v>9.049780946629296</v>
       </c>
     </row>
@@ -5075,6 +5440,9 @@
         </is>
       </c>
       <c r="J122" t="n">
+        <v>6</v>
+      </c>
+      <c r="K122" t="n">
         <v>8.797053500090465</v>
       </c>
     </row>
@@ -5113,6 +5481,9 @@
         </is>
       </c>
       <c r="J123" t="n">
+        <v>6</v>
+      </c>
+      <c r="K123" t="n">
         <v>8.797053500090465</v>
       </c>
     </row>
@@ -5151,6 +5522,9 @@
         </is>
       </c>
       <c r="J124" t="n">
+        <v>6</v>
+      </c>
+      <c r="K124" t="n">
         <v>8.679703519346106</v>
       </c>
     </row>
@@ -5189,6 +5563,9 @@
         </is>
       </c>
       <c r="J125" t="n">
+        <v>6</v>
+      </c>
+      <c r="K125" t="n">
         <v>8.671066277014619</v>
       </c>
     </row>
@@ -5227,6 +5604,9 @@
         </is>
       </c>
       <c r="J126" t="n">
+        <v>6</v>
+      </c>
+      <c r="K126" t="n">
         <v>8.527369824730963</v>
       </c>
     </row>
@@ -5265,6 +5645,9 @@
         </is>
       </c>
       <c r="J127" t="n">
+        <v>6</v>
+      </c>
+      <c r="K127" t="n">
         <v>8.527369824730963</v>
       </c>
     </row>
@@ -5303,6 +5686,9 @@
         </is>
       </c>
       <c r="J128" t="n">
+        <v>6</v>
+      </c>
+      <c r="K128" t="n">
         <v>8.560910589123965</v>
       </c>
     </row>
@@ -5341,6 +5727,9 @@
         </is>
       </c>
       <c r="J129" t="n">
+        <v>6</v>
+      </c>
+      <c r="K129" t="n">
         <v>8.614390892598811</v>
       </c>
     </row>
@@ -5379,6 +5768,9 @@
         </is>
       </c>
       <c r="J130" t="n">
+        <v>6</v>
+      </c>
+      <c r="K130" t="n">
         <v>8.614390892598811</v>
       </c>
     </row>
@@ -5417,6 +5809,9 @@
         </is>
       </c>
       <c r="J131" t="n">
+        <v>6</v>
+      </c>
+      <c r="K131" t="n">
         <v>8.671060242963611</v>
       </c>
     </row>
@@ -5455,6 +5850,9 @@
         </is>
       </c>
       <c r="J132" t="n">
+        <v>6</v>
+      </c>
+      <c r="K132" t="n">
         <v>8.736947290759135</v>
       </c>
     </row>
@@ -5493,6 +5891,9 @@
         </is>
       </c>
       <c r="J133" t="n">
+        <v>6</v>
+      </c>
+      <c r="K133" t="n">
         <v>8.899453321332752</v>
       </c>
     </row>
@@ -5531,6 +5932,9 @@
         </is>
       </c>
       <c r="J134" t="n">
+        <v>6</v>
+      </c>
+      <c r="K134" t="n">
         <v>8.976878747685555</v>
       </c>
     </row>
@@ -5569,6 +5973,9 @@
         </is>
       </c>
       <c r="J135" t="n">
+        <v>6</v>
+      </c>
+      <c r="K135" t="n">
         <v>9.070594825751041</v>
       </c>
     </row>
@@ -5607,6 +6014,9 @@
         </is>
       </c>
       <c r="J136" t="n">
+        <v>6</v>
+      </c>
+      <c r="K136" t="n">
         <v>9.549278556066488</v>
       </c>
     </row>
@@ -5645,6 +6055,9 @@
         </is>
       </c>
       <c r="J137" t="n">
+        <v>6</v>
+      </c>
+      <c r="K137" t="n">
         <v>9.549278556066488</v>
       </c>
     </row>
@@ -5683,6 +6096,9 @@
         </is>
       </c>
       <c r="J138" t="n">
+        <v>6</v>
+      </c>
+      <c r="K138" t="n">
         <v>9.954755082868157</v>
       </c>
     </row>
@@ -5721,6 +6137,9 @@
         </is>
       </c>
       <c r="J139" t="n">
+        <v>6</v>
+      </c>
+      <c r="K139" t="n">
         <v>10.06934780780029</v>
       </c>
     </row>
@@ -5759,6 +6178,9 @@
         </is>
       </c>
       <c r="J140" t="n">
+        <v>6</v>
+      </c>
+      <c r="K140" t="n">
         <v>10.06934780780029</v>
       </c>
     </row>
@@ -5797,6 +6219,9 @@
         </is>
       </c>
       <c r="J141" t="n">
+        <v>6</v>
+      </c>
+      <c r="K141" t="n">
         <v>10.238901419118</v>
       </c>
     </row>
@@ -5835,6 +6260,9 @@
         </is>
       </c>
       <c r="J142" t="n">
+        <v>6</v>
+      </c>
+      <c r="K142" t="n">
         <v>10.238901419118</v>
       </c>
     </row>
@@ -5873,6 +6301,9 @@
         </is>
       </c>
       <c r="J143" t="n">
+        <v>6</v>
+      </c>
+      <c r="K143" t="n">
         <v>10.26949459641317</v>
       </c>
     </row>
@@ -5911,6 +6342,9 @@
         </is>
       </c>
       <c r="J144" t="n">
+        <v>6</v>
+      </c>
+      <c r="K144" t="n">
         <v>10.26591014938876</v>
       </c>
     </row>
@@ -5949,6 +6383,9 @@
         </is>
       </c>
       <c r="J145" t="n">
+        <v>6</v>
+      </c>
+      <c r="K145" t="n">
         <v>10.19922334404454</v>
       </c>
     </row>
@@ -5987,6 +6424,9 @@
         </is>
       </c>
       <c r="J146" t="n">
+        <v>6</v>
+      </c>
+      <c r="K146" t="n">
         <v>10.157607343109</v>
       </c>
     </row>
@@ -6025,6 +6465,9 @@
         </is>
       </c>
       <c r="J147" t="n">
+        <v>6</v>
+      </c>
+      <c r="K147" t="n">
         <v>10.15135689057502</v>
       </c>
     </row>
@@ -6063,6 +6506,9 @@
         </is>
       </c>
       <c r="J148" t="n">
+        <v>6</v>
+      </c>
+      <c r="K148" t="n">
         <v>10.14784199584086</v>
       </c>
     </row>
@@ -6101,6 +6547,9 @@
         </is>
       </c>
       <c r="J149" t="n">
+        <v>6</v>
+      </c>
+      <c r="K149" t="n">
         <v>10.1470747339985</v>
       </c>
     </row>
@@ -6139,6 +6588,9 @@
         </is>
       </c>
       <c r="J150" t="n">
+        <v>6</v>
+      </c>
+      <c r="K150" t="n">
         <v>10.26983464027998</v>
       </c>
     </row>
@@ -6177,6 +6629,9 @@
         </is>
       </c>
       <c r="J151" t="n">
+        <v>6</v>
+      </c>
+      <c r="K151" t="n">
         <v>10.33989583046221</v>
       </c>
     </row>
@@ -6215,6 +6670,9 @@
         </is>
       </c>
       <c r="J152" t="n">
+        <v>6</v>
+      </c>
+      <c r="K152" t="n">
         <v>10.34512600052499</v>
       </c>
     </row>
@@ -6253,6 +6711,9 @@
         </is>
       </c>
       <c r="J153" t="n">
+        <v>6</v>
+      </c>
+      <c r="K153" t="n">
         <v>10.54442709905314</v>
       </c>
     </row>
@@ -6291,6 +6752,9 @@
         </is>
       </c>
       <c r="J154" t="n">
+        <v>6</v>
+      </c>
+      <c r="K154" t="n">
         <v>10.61904542555895</v>
       </c>
     </row>
@@ -6329,6 +6793,9 @@
         </is>
       </c>
       <c r="J155" t="n">
+        <v>6</v>
+      </c>
+      <c r="K155" t="n">
         <v>10.69190504591853</v>
       </c>
     </row>
@@ -6367,6 +6834,9 @@
         </is>
       </c>
       <c r="J156" t="n">
+        <v>6</v>
+      </c>
+      <c r="K156" t="n">
         <v>10.75670064819602</v>
       </c>
     </row>
@@ -6405,6 +6875,9 @@
         </is>
       </c>
       <c r="J157" t="n">
+        <v>6</v>
+      </c>
+      <c r="K157" t="n">
         <v>10.83306256459373</v>
       </c>
     </row>
@@ -6443,6 +6916,9 @@
         </is>
       </c>
       <c r="J158" t="n">
+        <v>6</v>
+      </c>
+      <c r="K158" t="n">
         <v>10.92685448189717</v>
       </c>
     </row>
@@ -6481,6 +6957,9 @@
         </is>
       </c>
       <c r="J159" t="n">
+        <v>6</v>
+      </c>
+      <c r="K159" t="n">
         <v>10.94563504361946</v>
       </c>
     </row>
@@ -6519,6 +6998,9 @@
         </is>
       </c>
       <c r="J160" t="n">
+        <v>6</v>
+      </c>
+      <c r="K160" t="n">
         <v>10.94563504361946</v>
       </c>
     </row>
@@ -6557,6 +7039,9 @@
         </is>
       </c>
       <c r="J161" t="n">
+        <v>6</v>
+      </c>
+      <c r="K161" t="n">
         <v>10.9708481273363</v>
       </c>
     </row>
@@ -6595,6 +7080,9 @@
         </is>
       </c>
       <c r="J162" t="n">
+        <v>6</v>
+      </c>
+      <c r="K162" t="n">
         <v>10.95402348740476</v>
       </c>
     </row>
@@ -6633,6 +7121,9 @@
         </is>
       </c>
       <c r="J163" t="n">
+        <v>6</v>
+      </c>
+      <c r="K163" t="n">
         <v>10.95402348740476</v>
       </c>
     </row>
@@ -6671,6 +7162,9 @@
         </is>
       </c>
       <c r="J164" t="n">
+        <v>6</v>
+      </c>
+      <c r="K164" t="n">
         <v>11.12657912438668</v>
       </c>
     </row>
@@ -6709,6 +7203,9 @@
         </is>
       </c>
       <c r="J165" t="n">
+        <v>6</v>
+      </c>
+      <c r="K165" t="n">
         <v>11.14795892046014</v>
       </c>
     </row>
@@ -6747,6 +7244,9 @@
         </is>
       </c>
       <c r="J166" t="n">
+        <v>6</v>
+      </c>
+      <c r="K166" t="n">
         <v>12.05835100310014</v>
       </c>
     </row>
@@ -6785,6 +7285,9 @@
         </is>
       </c>
       <c r="J167" t="n">
+        <v>6</v>
+      </c>
+      <c r="K167" t="n">
         <v>12.05835100310014</v>
       </c>
     </row>
@@ -6823,6 +7326,9 @@
         </is>
       </c>
       <c r="J168" t="n">
+        <v>6</v>
+      </c>
+      <c r="K168" t="n">
         <v>12.05835100310014</v>
       </c>
     </row>
@@ -6861,6 +7367,9 @@
         </is>
       </c>
       <c r="J169" t="n">
+        <v>6</v>
+      </c>
+      <c r="K169" t="n">
         <v>12.7514670715484</v>
       </c>
     </row>
@@ -6899,6 +7408,9 @@
         </is>
       </c>
       <c r="J170" t="n">
+        <v>6</v>
+      </c>
+      <c r="K170" t="n">
         <v>12.99740495364647</v>
       </c>
     </row>
@@ -6937,6 +7449,9 @@
         </is>
       </c>
       <c r="J171" t="n">
+        <v>6</v>
+      </c>
+      <c r="K171" t="n">
         <v>13.22893290283062</v>
       </c>
     </row>
@@ -6975,6 +7490,9 @@
         </is>
       </c>
       <c r="J172" t="n">
+        <v>6</v>
+      </c>
+      <c r="K172" t="n">
         <v>13.38196974327161</v>
       </c>
     </row>
@@ -7013,6 +7531,9 @@
         </is>
       </c>
       <c r="J173" t="n">
+        <v>6</v>
+      </c>
+      <c r="K173" t="n">
         <v>13.52525134411477</v>
       </c>
     </row>
@@ -7051,6 +7572,9 @@
         </is>
       </c>
       <c r="J174" t="n">
+        <v>6</v>
+      </c>
+      <c r="K174" t="n">
         <v>13.52741702524259</v>
       </c>
     </row>
@@ -7089,6 +7613,9 @@
         </is>
       </c>
       <c r="J175" t="n">
+        <v>6</v>
+      </c>
+      <c r="K175" t="n">
         <v>13.52513424291054</v>
       </c>
     </row>
@@ -7127,6 +7654,9 @@
         </is>
       </c>
       <c r="J176" t="n">
+        <v>6</v>
+      </c>
+      <c r="K176" t="n">
         <v>13.45373608070102</v>
       </c>
     </row>
@@ -7165,6 +7695,9 @@
         </is>
       </c>
       <c r="J177" t="n">
+        <v>6</v>
+      </c>
+      <c r="K177" t="n">
         <v>13.45373608070102</v>
       </c>
     </row>
@@ -7203,6 +7736,9 @@
         </is>
       </c>
       <c r="J178" t="n">
+        <v>6</v>
+      </c>
+      <c r="K178" t="n">
         <v>12.87687986559452</v>
       </c>
     </row>
@@ -7241,6 +7777,9 @@
         </is>
       </c>
       <c r="J179" t="n">
+        <v>6</v>
+      </c>
+      <c r="K179" t="n">
         <v>12.78203660848068</v>
       </c>
     </row>
@@ -7279,6 +7818,9 @@
         </is>
       </c>
       <c r="J180" t="n">
+        <v>6</v>
+      </c>
+      <c r="K180" t="n">
         <v>12.88732088272113</v>
       </c>
     </row>
@@ -7317,6 +7859,9 @@
         </is>
       </c>
       <c r="J181" t="n">
+        <v>6</v>
+      </c>
+      <c r="K181" t="n">
         <v>13.10364382962162</v>
       </c>
     </row>
@@ -7355,6 +7900,9 @@
         </is>
       </c>
       <c r="J182" t="n">
+        <v>6</v>
+      </c>
+      <c r="K182" t="n">
         <v>13.21665282962994</v>
       </c>
     </row>
@@ -7393,6 +7941,9 @@
         </is>
       </c>
       <c r="J183" t="n">
+        <v>6</v>
+      </c>
+      <c r="K183" t="n">
         <v>13.22868636362987</v>
       </c>
     </row>
@@ -7431,6 +7982,9 @@
         </is>
       </c>
       <c r="J184" t="n">
+        <v>6</v>
+      </c>
+      <c r="K184" t="n">
         <v>13.22836695411769</v>
       </c>
     </row>
@@ -7469,6 +8023,9 @@
         </is>
       </c>
       <c r="J185" t="n">
+        <v>6</v>
+      </c>
+      <c r="K185" t="n">
         <v>12.56331902858596</v>
       </c>
     </row>
@@ -7507,6 +8064,9 @@
         </is>
       </c>
       <c r="J186" t="n">
+        <v>6</v>
+      </c>
+      <c r="K186" t="n">
         <v>12.54081239321359</v>
       </c>
     </row>
@@ -7545,6 +8105,9 @@
         </is>
       </c>
       <c r="J187" t="n">
+        <v>6</v>
+      </c>
+      <c r="K187" t="n">
         <v>12.29943552785324</v>
       </c>
     </row>
@@ -7583,6 +8146,9 @@
         </is>
       </c>
       <c r="J188" t="n">
+        <v>6</v>
+      </c>
+      <c r="K188" t="n">
         <v>12.2829233494113</v>
       </c>
     </row>
@@ -7621,6 +8187,9 @@
         </is>
       </c>
       <c r="J189" t="n">
+        <v>6</v>
+      </c>
+      <c r="K189" t="n">
         <v>12.29630371710577</v>
       </c>
     </row>
@@ -7659,6 +8228,9 @@
         </is>
       </c>
       <c r="J190" t="n">
+        <v>6</v>
+      </c>
+      <c r="K190" t="n">
         <v>12.30719348999601</v>
       </c>
     </row>
@@ -7697,6 +8269,9 @@
         </is>
       </c>
       <c r="J191" t="n">
+        <v>6</v>
+      </c>
+      <c r="K191" t="n">
         <v>12.35258897367873</v>
       </c>
     </row>
@@ -7735,6 +8310,9 @@
         </is>
       </c>
       <c r="J192" t="n">
+        <v>6</v>
+      </c>
+      <c r="K192" t="n">
         <v>12.35296321494364</v>
       </c>
     </row>
@@ -7773,6 +8351,9 @@
         </is>
       </c>
       <c r="J193" t="n">
+        <v>6</v>
+      </c>
+      <c r="K193" t="n">
         <v>12.35296321494364</v>
       </c>
     </row>
@@ -7811,6 +8392,9 @@
         </is>
       </c>
       <c r="J194" t="n">
+        <v>6</v>
+      </c>
+      <c r="K194" t="n">
         <v>12.49863818307099</v>
       </c>
     </row>
@@ -7849,6 +8433,9 @@
         </is>
       </c>
       <c r="J195" t="n">
+        <v>6</v>
+      </c>
+      <c r="K195" t="n">
         <v>12.5148122688107</v>
       </c>
     </row>
@@ -7887,6 +8474,9 @@
         </is>
       </c>
       <c r="J196" t="n">
+        <v>6</v>
+      </c>
+      <c r="K196" t="n">
         <v>12.64059519103216</v>
       </c>
     </row>
@@ -7925,6 +8515,9 @@
         </is>
       </c>
       <c r="J197" t="n">
+        <v>6</v>
+      </c>
+      <c r="K197" t="n">
         <v>12.75516335641252</v>
       </c>
     </row>
@@ -7963,6 +8556,9 @@
         </is>
       </c>
       <c r="J198" t="n">
+        <v>6</v>
+      </c>
+      <c r="K198" t="n">
         <v>12.82434787857481</v>
       </c>
     </row>
@@ -8001,6 +8597,9 @@
         </is>
       </c>
       <c r="J199" t="n">
+        <v>6</v>
+      </c>
+      <c r="K199" t="n">
         <v>12.87172396313655</v>
       </c>
     </row>
@@ -8039,6 +8638,9 @@
         </is>
       </c>
       <c r="J200" t="n">
+        <v>6</v>
+      </c>
+      <c r="K200" t="n">
         <v>12.91232242971177</v>
       </c>
     </row>
@@ -8077,6 +8679,9 @@
         </is>
       </c>
       <c r="J201" t="n">
+        <v>6</v>
+      </c>
+      <c r="K201" t="n">
         <v>12.91033089851393</v>
       </c>
     </row>
@@ -8115,6 +8720,9 @@
         </is>
       </c>
       <c r="J202" t="n">
+        <v>6</v>
+      </c>
+      <c r="K202" t="n">
         <v>12.80490227021584</v>
       </c>
     </row>
@@ -8153,6 +8761,9 @@
         </is>
       </c>
       <c r="J203" t="n">
+        <v>6</v>
+      </c>
+      <c r="K203" t="n">
         <v>12.802726964012</v>
       </c>
     </row>
@@ -8191,6 +8802,9 @@
         </is>
       </c>
       <c r="J204" t="n">
+        <v>6</v>
+      </c>
+      <c r="K204" t="n">
         <v>12.7379435150013</v>
       </c>
     </row>
@@ -8229,6 +8843,9 @@
         </is>
       </c>
       <c r="J205" t="n">
+        <v>6</v>
+      </c>
+      <c r="K205" t="n">
         <v>12.6701704866137</v>
       </c>
     </row>
@@ -8267,6 +8884,9 @@
         </is>
       </c>
       <c r="J206" t="n">
+        <v>6</v>
+      </c>
+      <c r="K206" t="n">
         <v>12.6701704866137</v>
       </c>
     </row>
@@ -8305,6 +8925,9 @@
         </is>
       </c>
       <c r="J207" t="n">
+        <v>6</v>
+      </c>
+      <c r="K207" t="n">
         <v>12.49945175787417</v>
       </c>
     </row>
@@ -8343,6 +8966,9 @@
         </is>
       </c>
       <c r="J208" t="n">
+        <v>6</v>
+      </c>
+      <c r="K208" t="n">
         <v>12.28779173644725</v>
       </c>
     </row>
@@ -8381,6 +9007,9 @@
         </is>
       </c>
       <c r="J209" t="n">
+        <v>6</v>
+      </c>
+      <c r="K209" t="n">
         <v>11.88832606873517</v>
       </c>
     </row>
@@ -8419,6 +9048,9 @@
         </is>
       </c>
       <c r="J210" t="n">
+        <v>6</v>
+      </c>
+      <c r="K210" t="n">
         <v>11.88790187061831</v>
       </c>
     </row>
@@ -8457,6 +9089,9 @@
         </is>
       </c>
       <c r="J211" t="n">
+        <v>6</v>
+      </c>
+      <c r="K211" t="n">
         <v>12.16318878177189</v>
       </c>
     </row>
@@ -8495,6 +9130,9 @@
         </is>
       </c>
       <c r="J212" t="n">
+        <v>6</v>
+      </c>
+      <c r="K212" t="n">
         <v>12.16318878177189</v>
       </c>
     </row>
@@ -8533,6 +9171,9 @@
         </is>
       </c>
       <c r="J213" t="n">
+        <v>6</v>
+      </c>
+      <c r="K213" t="n">
         <v>12.2850933308724</v>
       </c>
     </row>
@@ -8571,6 +9212,9 @@
         </is>
       </c>
       <c r="J214" t="n">
+        <v>6</v>
+      </c>
+      <c r="K214" t="n">
         <v>12.30729200089643</v>
       </c>
     </row>
@@ -8609,6 +9253,9 @@
         </is>
       </c>
       <c r="J215" t="n">
+        <v>6</v>
+      </c>
+      <c r="K215" t="n">
         <v>12.46602379984828</v>
       </c>
     </row>
@@ -8647,6 +9294,9 @@
         </is>
       </c>
       <c r="J216" t="n">
+        <v>6</v>
+      </c>
+      <c r="K216" t="n">
         <v>12.49982119715622</v>
       </c>
     </row>
@@ -8685,6 +9335,9 @@
         </is>
       </c>
       <c r="J217" t="n">
+        <v>6</v>
+      </c>
+      <c r="K217" t="n">
         <v>12.52439545881572</v>
       </c>
     </row>
@@ -8723,6 +9376,9 @@
         </is>
       </c>
       <c r="J218" t="n">
+        <v>6</v>
+      </c>
+      <c r="K218" t="n">
         <v>12.54340224967523</v>
       </c>
     </row>
@@ -8761,6 +9417,9 @@
         </is>
       </c>
       <c r="J219" t="n">
+        <v>6</v>
+      </c>
+      <c r="K219" t="n">
         <v>12.57716517946826</v>
       </c>
     </row>
@@ -8799,6 +9458,9 @@
         </is>
       </c>
       <c r="J220" t="n">
+        <v>6</v>
+      </c>
+      <c r="K220" t="n">
         <v>12.57716517946826</v>
       </c>
     </row>
@@ -8837,6 +9499,9 @@
         </is>
       </c>
       <c r="J221" t="n">
+        <v>6</v>
+      </c>
+      <c r="K221" t="n">
         <v>12.55626785778556</v>
       </c>
     </row>
@@ -8875,6 +9540,9 @@
         </is>
       </c>
       <c r="J222" t="n">
+        <v>6</v>
+      </c>
+      <c r="K222" t="n">
         <v>12.71987453457647</v>
       </c>
     </row>
@@ -8913,6 +9581,9 @@
         </is>
       </c>
       <c r="J223" t="n">
+        <v>6</v>
+      </c>
+      <c r="K223" t="n">
         <v>12.71883627017913</v>
       </c>
     </row>
@@ -8951,6 +9622,9 @@
         </is>
       </c>
       <c r="J224" t="n">
+        <v>6</v>
+      </c>
+      <c r="K224" t="n">
         <v>12.6066166473486</v>
       </c>
     </row>
@@ -8989,6 +9663,9 @@
         </is>
       </c>
       <c r="J225" t="n">
+        <v>6</v>
+      </c>
+      <c r="K225" t="n">
         <v>12.56723055679825</v>
       </c>
     </row>
@@ -9027,6 +9704,9 @@
         </is>
       </c>
       <c r="J226" t="n">
+        <v>6</v>
+      </c>
+      <c r="K226" t="n">
         <v>12.54480457182633</v>
       </c>
     </row>
@@ -9065,6 +9745,9 @@
         </is>
       </c>
       <c r="J227" t="n">
+        <v>6</v>
+      </c>
+      <c r="K227" t="n">
         <v>12.5861789188918</v>
       </c>
     </row>
@@ -9103,6 +9786,9 @@
         </is>
       </c>
       <c r="J228" t="n">
+        <v>6</v>
+      </c>
+      <c r="K228" t="n">
         <v>12.54329025449246</v>
       </c>
     </row>
@@ -9141,6 +9827,9 @@
         </is>
       </c>
       <c r="J229" t="n">
+        <v>6</v>
+      </c>
+      <c r="K229" t="n">
         <v>12.54329025449246</v>
       </c>
     </row>
@@ -9179,6 +9868,9 @@
         </is>
       </c>
       <c r="J230" t="n">
+        <v>6</v>
+      </c>
+      <c r="K230" t="n">
         <v>12.47729707886387</v>
       </c>
     </row>
@@ -9217,6 +9909,9 @@
         </is>
       </c>
       <c r="J231" t="n">
+        <v>6</v>
+      </c>
+      <c r="K231" t="n">
         <v>12.47721645407332</v>
       </c>
     </row>
@@ -9255,6 +9950,9 @@
         </is>
       </c>
       <c r="J232" t="n">
+        <v>6</v>
+      </c>
+      <c r="K232" t="n">
         <v>12.49451825327216</v>
       </c>
     </row>
@@ -9293,6 +9991,9 @@
         </is>
       </c>
       <c r="J233" t="n">
+        <v>6</v>
+      </c>
+      <c r="K233" t="n">
         <v>12.49451825327216</v>
       </c>
     </row>
@@ -9331,6 +10032,9 @@
         </is>
       </c>
       <c r="J234" t="n">
+        <v>6</v>
+      </c>
+      <c r="K234" t="n">
         <v>12.50066545811739</v>
       </c>
     </row>
@@ -9369,6 +10073,9 @@
         </is>
       </c>
       <c r="J235" t="n">
+        <v>6</v>
+      </c>
+      <c r="K235" t="n">
         <v>12.50066545811739</v>
       </c>
     </row>
@@ -9407,6 +10114,9 @@
         </is>
       </c>
       <c r="J236" t="n">
+        <v>6</v>
+      </c>
+      <c r="K236" t="n">
         <v>12.5438949370723</v>
       </c>
     </row>
@@ -9445,6 +10155,9 @@
         </is>
       </c>
       <c r="J237" t="n">
+        <v>6</v>
+      </c>
+      <c r="K237" t="n">
         <v>12.55371901573918</v>
       </c>
     </row>
@@ -9483,6 +10196,9 @@
         </is>
       </c>
       <c r="J238" t="n">
+        <v>6</v>
+      </c>
+      <c r="K238" t="n">
         <v>12.55371901573918</v>
       </c>
     </row>
@@ -9521,6 +10237,9 @@
         </is>
       </c>
       <c r="J239" t="n">
+        <v>6</v>
+      </c>
+      <c r="K239" t="n">
         <v>12.55371901573918</v>
       </c>
     </row>
@@ -9559,6 +10278,9 @@
         </is>
       </c>
       <c r="J240" t="n">
+        <v>6</v>
+      </c>
+      <c r="K240" t="n">
         <v>12.557311351392</v>
       </c>
     </row>
@@ -9597,6 +10319,9 @@
         </is>
       </c>
       <c r="J241" t="n">
+        <v>6</v>
+      </c>
+      <c r="K241" t="n">
         <v>12.557311351392</v>
       </c>
     </row>
@@ -9635,6 +10360,9 @@
         </is>
       </c>
       <c r="J242" t="n">
+        <v>6</v>
+      </c>
+      <c r="K242" t="n">
         <v>12.45332192399493</v>
       </c>
     </row>
@@ -9673,6 +10401,9 @@
         </is>
       </c>
       <c r="J243" t="n">
+        <v>6</v>
+      </c>
+      <c r="K243" t="n">
         <v>12.45332192399493</v>
       </c>
     </row>
@@ -9711,6 +10442,9 @@
         </is>
       </c>
       <c r="J244" t="n">
+        <v>6</v>
+      </c>
+      <c r="K244" t="n">
         <v>12.40593897788581</v>
       </c>
     </row>
@@ -9749,6 +10483,9 @@
         </is>
       </c>
       <c r="J245" t="n">
+        <v>6</v>
+      </c>
+      <c r="K245" t="n">
         <v>12.19413671075773</v>
       </c>
     </row>
@@ -9787,6 +10524,9 @@
         </is>
       </c>
       <c r="J246" t="n">
+        <v>6</v>
+      </c>
+      <c r="K246" t="n">
         <v>12.08990666231681</v>
       </c>
     </row>
@@ -9825,6 +10565,9 @@
         </is>
       </c>
       <c r="J247" t="n">
+        <v>6</v>
+      </c>
+      <c r="K247" t="n">
         <v>12.0907797271752</v>
       </c>
     </row>
@@ -9863,6 +10606,9 @@
         </is>
       </c>
       <c r="J248" t="n">
+        <v>6</v>
+      </c>
+      <c r="K248" t="n">
         <v>12.09182775173085</v>
       </c>
     </row>
@@ -9901,6 +10647,9 @@
         </is>
       </c>
       <c r="J249" t="n">
+        <v>7</v>
+      </c>
+      <c r="K249" t="n">
         <v>12.0953605974493</v>
       </c>
     </row>
@@ -9939,6 +10688,9 @@
         </is>
       </c>
       <c r="J250" t="n">
+        <v>7</v>
+      </c>
+      <c r="K250" t="n">
         <v>12.1052150235773</v>
       </c>
     </row>
@@ -9977,6 +10729,9 @@
         </is>
       </c>
       <c r="J251" t="n">
+        <v>7</v>
+      </c>
+      <c r="K251" t="n">
         <v>12.1067013623614</v>
       </c>
     </row>
@@ -10015,6 +10770,9 @@
         </is>
       </c>
       <c r="J252" t="n">
+        <v>7</v>
+      </c>
+      <c r="K252" t="n">
         <v>12.1605822292569</v>
       </c>
     </row>
@@ -10053,6 +10811,9 @@
         </is>
       </c>
       <c r="J253" t="n">
+        <v>7</v>
+      </c>
+      <c r="K253" t="n">
         <v>12.229154793299</v>
       </c>
     </row>
@@ -10091,6 +10852,9 @@
         </is>
       </c>
       <c r="J254" t="n">
+        <v>7</v>
+      </c>
+      <c r="K254" t="n">
         <v>12.39318867506093</v>
       </c>
     </row>
@@ -10129,6 +10893,9 @@
         </is>
       </c>
       <c r="J255" t="n">
+        <v>7</v>
+      </c>
+      <c r="K255" t="n">
         <v>12.63399979306722</v>
       </c>
     </row>
@@ -10167,6 +10934,9 @@
         </is>
       </c>
       <c r="J256" t="n">
+        <v>7</v>
+      </c>
+      <c r="K256" t="n">
         <v>12.77277566475786</v>
       </c>
     </row>
@@ -10205,6 +10975,9 @@
         </is>
       </c>
       <c r="J257" t="n">
+        <v>7</v>
+      </c>
+      <c r="K257" t="n">
         <v>12.92361940445302</v>
       </c>
     </row>
@@ -10243,6 +11016,9 @@
         </is>
       </c>
       <c r="J258" t="n">
+        <v>7</v>
+      </c>
+      <c r="K258" t="n">
         <v>13.00581980539971</v>
       </c>
     </row>
@@ -10281,6 +11057,9 @@
         </is>
       </c>
       <c r="J259" t="n">
+        <v>7</v>
+      </c>
+      <c r="K259" t="n">
         <v>11.21371983920643</v>
       </c>
     </row>
@@ -10319,6 +11098,9 @@
         </is>
       </c>
       <c r="J260" t="n">
+        <v>7</v>
+      </c>
+      <c r="K260" t="n">
         <v>10.91295735455809</v>
       </c>
     </row>
@@ -10357,6 +11139,9 @@
         </is>
       </c>
       <c r="J261" t="n">
+        <v>7</v>
+      </c>
+      <c r="K261" t="n">
         <v>10.90630933043323</v>
       </c>
     </row>
@@ -10395,6 +11180,9 @@
         </is>
       </c>
       <c r="J262" t="n">
+        <v>7</v>
+      </c>
+      <c r="K262" t="n">
         <v>11.11067537123716</v>
       </c>
     </row>
@@ -10433,6 +11221,9 @@
         </is>
       </c>
       <c r="J263" t="n">
+        <v>7</v>
+      </c>
+      <c r="K263" t="n">
         <v>11.12092613981406</v>
       </c>
     </row>
@@ -10471,6 +11262,9 @@
         </is>
       </c>
       <c r="J264" t="n">
+        <v>7</v>
+      </c>
+      <c r="K264" t="n">
         <v>11.41452067011062</v>
       </c>
     </row>
@@ -10509,6 +11303,9 @@
         </is>
       </c>
       <c r="J265" t="n">
+        <v>7</v>
+      </c>
+      <c r="K265" t="n">
         <v>11.41803390508936</v>
       </c>
     </row>
@@ -10547,6 +11344,9 @@
         </is>
       </c>
       <c r="J266" t="n">
+        <v>7</v>
+      </c>
+      <c r="K266" t="n">
         <v>11.42474323728245</v>
       </c>
     </row>
@@ -10585,6 +11385,9 @@
         </is>
       </c>
       <c r="J267" t="n">
+        <v>7</v>
+      </c>
+      <c r="K267" t="n">
         <v>11.52098055181535</v>
       </c>
     </row>
@@ -10623,6 +11426,9 @@
         </is>
       </c>
       <c r="J268" t="n">
+        <v>7</v>
+      </c>
+      <c r="K268" t="n">
         <v>11.60063562855445</v>
       </c>
     </row>
@@ -10661,6 +11467,9 @@
         </is>
       </c>
       <c r="J269" t="n">
+        <v>7</v>
+      </c>
+      <c r="K269" t="n">
         <v>11.63492252765004</v>
       </c>
     </row>
@@ -10699,6 +11508,9 @@
         </is>
       </c>
       <c r="J270" t="n">
+        <v>7</v>
+      </c>
+      <c r="K270" t="n">
         <v>11.59571903340261</v>
       </c>
     </row>
@@ -10737,6 +11549,9 @@
         </is>
       </c>
       <c r="J271" t="n">
+        <v>7</v>
+      </c>
+      <c r="K271" t="n">
         <v>11.47482411747132</v>
       </c>
     </row>
@@ -10775,6 +11590,9 @@
         </is>
       </c>
       <c r="J272" t="n">
+        <v>7</v>
+      </c>
+      <c r="K272" t="n">
         <v>11.41973742778242</v>
       </c>
     </row>
@@ -10813,6 +11631,9 @@
         </is>
       </c>
       <c r="J273" t="n">
+        <v>7</v>
+      </c>
+      <c r="K273" t="n">
         <v>11.41973742778242</v>
       </c>
     </row>
@@ -10851,6 +11672,9 @@
         </is>
       </c>
       <c r="J274" t="n">
+        <v>7</v>
+      </c>
+      <c r="K274" t="n">
         <v>11.33187334346197</v>
       </c>
     </row>
@@ -10889,6 +11713,9 @@
         </is>
       </c>
       <c r="J275" t="n">
+        <v>7</v>
+      </c>
+      <c r="K275" t="n">
         <v>11.1448551788642</v>
       </c>
     </row>
@@ -10927,6 +11754,9 @@
         </is>
       </c>
       <c r="J276" t="n">
+        <v>7</v>
+      </c>
+      <c r="K276" t="n">
         <v>10.98126156842115</v>
       </c>
     </row>
@@ -10965,6 +11795,9 @@
         </is>
       </c>
       <c r="J277" t="n">
+        <v>7</v>
+      </c>
+      <c r="K277" t="n">
         <v>10.93366607274151</v>
       </c>
     </row>
@@ -11003,6 +11836,9 @@
         </is>
       </c>
       <c r="J278" t="n">
+        <v>7</v>
+      </c>
+      <c r="K278" t="n">
         <v>10.99451771464207</v>
       </c>
     </row>
@@ -11041,6 +11877,9 @@
         </is>
       </c>
       <c r="J279" t="n">
+        <v>7</v>
+      </c>
+      <c r="K279" t="n">
         <v>11.01398975244947</v>
       </c>
     </row>
@@ -11079,6 +11918,9 @@
         </is>
       </c>
       <c r="J280" t="n">
+        <v>7</v>
+      </c>
+      <c r="K280" t="n">
         <v>10.94464035966949</v>
       </c>
     </row>
@@ -11117,6 +11959,9 @@
         </is>
       </c>
       <c r="J281" t="n">
+        <v>7</v>
+      </c>
+      <c r="K281" t="n">
         <v>10.87454393270211</v>
       </c>
     </row>
@@ -11155,6 +12000,9 @@
         </is>
       </c>
       <c r="J282" t="n">
+        <v>7</v>
+      </c>
+      <c r="K282" t="n">
         <v>10.8697265650179</v>
       </c>
     </row>
@@ -11193,6 +12041,9 @@
         </is>
       </c>
       <c r="J283" t="n">
+        <v>7</v>
+      </c>
+      <c r="K283" t="n">
         <v>10.78344121762455</v>
       </c>
     </row>
@@ -11231,6 +12082,9 @@
         </is>
       </c>
       <c r="J284" t="n">
+        <v>7</v>
+      </c>
+      <c r="K284" t="n">
         <v>10.47894384845322</v>
       </c>
     </row>
@@ -11269,6 +12123,9 @@
         </is>
       </c>
       <c r="J285" t="n">
+        <v>7</v>
+      </c>
+      <c r="K285" t="n">
         <v>10.40804462411561</v>
       </c>
     </row>
@@ -11307,6 +12164,9 @@
         </is>
       </c>
       <c r="J286" t="n">
+        <v>7</v>
+      </c>
+      <c r="K286" t="n">
         <v>10.39862734326141</v>
       </c>
     </row>
@@ -11345,6 +12205,9 @@
         </is>
       </c>
       <c r="J287" t="n">
+        <v>7</v>
+      </c>
+      <c r="K287" t="n">
         <v>10.31465250658979</v>
       </c>
     </row>
@@ -11383,6 +12246,9 @@
         </is>
       </c>
       <c r="J288" t="n">
+        <v>7</v>
+      </c>
+      <c r="K288" t="n">
         <v>10.09146661452745</v>
       </c>
     </row>
@@ -11421,6 +12287,9 @@
         </is>
       </c>
       <c r="J289" t="n">
+        <v>7</v>
+      </c>
+      <c r="K289" t="n">
         <v>10.09146661452745</v>
       </c>
     </row>
@@ -11459,6 +12328,9 @@
         </is>
       </c>
       <c r="J290" t="n">
+        <v>7</v>
+      </c>
+      <c r="K290" t="n">
         <v>10.09146661452745</v>
       </c>
     </row>
@@ -11497,6 +12369,9 @@
         </is>
       </c>
       <c r="J291" t="n">
+        <v>7</v>
+      </c>
+      <c r="K291" t="n">
         <v>9.998652005373946</v>
       </c>
     </row>
@@ -11535,6 +12410,9 @@
         </is>
       </c>
       <c r="J292" t="n">
+        <v>7</v>
+      </c>
+      <c r="K292" t="n">
         <v>9.627176800538392</v>
       </c>
     </row>
@@ -11573,6 +12451,9 @@
         </is>
       </c>
       <c r="J293" t="n">
+        <v>7</v>
+      </c>
+      <c r="K293" t="n">
         <v>9.547101279853123</v>
       </c>
     </row>
@@ -11611,6 +12492,9 @@
         </is>
       </c>
       <c r="J294" t="n">
+        <v>7</v>
+      </c>
+      <c r="K294" t="n">
         <v>9.537637545562722</v>
       </c>
     </row>
@@ -11649,6 +12533,9 @@
         </is>
       </c>
       <c r="J295" t="n">
+        <v>7</v>
+      </c>
+      <c r="K295" t="n">
         <v>9.339565464354987</v>
       </c>
     </row>
@@ -11687,6 +12574,9 @@
         </is>
       </c>
       <c r="J296" t="n">
+        <v>7</v>
+      </c>
+      <c r="K296" t="n">
         <v>9.173625430582824</v>
       </c>
     </row>
@@ -11725,6 +12615,9 @@
         </is>
       </c>
       <c r="J297" t="n">
+        <v>7</v>
+      </c>
+      <c r="K297" t="n">
         <v>9.025812203187257</v>
       </c>
     </row>
@@ -11763,6 +12656,9 @@
         </is>
       </c>
       <c r="J298" t="n">
+        <v>7</v>
+      </c>
+      <c r="K298" t="n">
         <v>9.006879282161655</v>
       </c>
     </row>
@@ -11801,6 +12697,9 @@
         </is>
       </c>
       <c r="J299" t="n">
+        <v>7</v>
+      </c>
+      <c r="K299" t="n">
         <v>9.006879282161655</v>
       </c>
     </row>
@@ -11839,6 +12738,9 @@
         </is>
       </c>
       <c r="J300" t="n">
+        <v>7</v>
+      </c>
+      <c r="K300" t="n">
         <v>8.861183513553238</v>
       </c>
     </row>
@@ -11877,6 +12779,9 @@
         </is>
       </c>
       <c r="J301" t="n">
+        <v>7</v>
+      </c>
+      <c r="K301" t="n">
         <v>8.547412728732105</v>
       </c>
     </row>
@@ -11915,6 +12820,9 @@
         </is>
       </c>
       <c r="J302" t="n">
+        <v>7</v>
+      </c>
+      <c r="K302" t="n">
         <v>8.404708773756287</v>
       </c>
     </row>
@@ -11953,6 +12861,9 @@
         </is>
       </c>
       <c r="J303" t="n">
+        <v>7</v>
+      </c>
+      <c r="K303" t="n">
         <v>8.291888650451861</v>
       </c>
     </row>
@@ -11991,6 +12902,9 @@
         </is>
       </c>
       <c r="J304" t="n">
+        <v>7</v>
+      </c>
+      <c r="K304" t="n">
         <v>8.291888650451861</v>
       </c>
     </row>
@@ -12029,6 +12943,9 @@
         </is>
       </c>
       <c r="J305" t="n">
+        <v>7</v>
+      </c>
+      <c r="K305" t="n">
         <v>8.165029969200923</v>
       </c>
     </row>
@@ -12067,6 +12984,9 @@
         </is>
       </c>
       <c r="J306" t="n">
+        <v>7</v>
+      </c>
+      <c r="K306" t="n">
         <v>8.165029969200923</v>
       </c>
     </row>
@@ -12105,6 +13025,9 @@
         </is>
       </c>
       <c r="J307" t="n">
+        <v>7</v>
+      </c>
+      <c r="K307" t="n">
         <v>8.084842963827313</v>
       </c>
     </row>
@@ -12143,6 +13066,9 @@
         </is>
       </c>
       <c r="J308" t="n">
+        <v>7</v>
+      </c>
+      <c r="K308" t="n">
         <v>8.084842963827313</v>
       </c>
     </row>
@@ -12181,6 +13107,9 @@
         </is>
       </c>
       <c r="J309" t="n">
+        <v>7</v>
+      </c>
+      <c r="K309" t="n">
         <v>10.10820283313736</v>
       </c>
     </row>
@@ -12219,6 +13148,9 @@
         </is>
       </c>
       <c r="J310" t="n">
+        <v>7</v>
+      </c>
+      <c r="K310" t="n">
         <v>10.10820283313736</v>
       </c>
     </row>
@@ -12257,6 +13189,9 @@
         </is>
       </c>
       <c r="J311" t="n">
+        <v>7</v>
+      </c>
+      <c r="K311" t="n">
         <v>8.012503119472658</v>
       </c>
     </row>
@@ -12295,6 +13230,9 @@
         </is>
       </c>
       <c r="J312" t="n">
+        <v>7</v>
+      </c>
+      <c r="K312" t="n">
         <v>8.012503119472658</v>
       </c>
     </row>
@@ -12333,6 +13271,9 @@
         </is>
       </c>
       <c r="J313" t="n">
+        <v>8</v>
+      </c>
+      <c r="K313" t="n">
         <v>8.962446912990094</v>
       </c>
     </row>
@@ -12371,6 +13312,9 @@
         </is>
       </c>
       <c r="J314" t="n">
+        <v>8</v>
+      </c>
+      <c r="K314" t="n">
         <v>10.04429015944742</v>
       </c>
     </row>
@@ -12409,6 +13353,9 @@
         </is>
       </c>
       <c r="J315" t="n">
+        <v>8</v>
+      </c>
+      <c r="K315" t="n">
         <v>10.04429015944742</v>
       </c>
     </row>
@@ -12447,6 +13394,9 @@
         </is>
       </c>
       <c r="J316" t="n">
+        <v>8</v>
+      </c>
+      <c r="K316" t="n">
         <v>10.37771817328758</v>
       </c>
     </row>
@@ -12485,6 +13435,9 @@
         </is>
       </c>
       <c r="J317" t="n">
+        <v>8</v>
+      </c>
+      <c r="K317" t="n">
         <v>11.03656923159764</v>
       </c>
     </row>
@@ -12523,6 +13476,9 @@
         </is>
       </c>
       <c r="J318" t="n">
+        <v>8</v>
+      </c>
+      <c r="K318" t="n">
         <v>11.95788110580619</v>
       </c>
     </row>
@@ -12561,6 +13517,9 @@
         </is>
       </c>
       <c r="J319" t="n">
+        <v>8</v>
+      </c>
+      <c r="K319" t="n">
         <v>12.48307800769145</v>
       </c>
     </row>
@@ -12599,6 +13558,9 @@
         </is>
       </c>
       <c r="J320" t="n">
+        <v>8</v>
+      </c>
+      <c r="K320" t="n">
         <v>15.0180188076118</v>
       </c>
     </row>
@@ -12637,6 +13599,9 @@
         </is>
       </c>
       <c r="J321" t="n">
+        <v>8</v>
+      </c>
+      <c r="K321" t="n">
         <v>14.99113673485492</v>
       </c>
     </row>
@@ -12675,6 +13640,9 @@
         </is>
       </c>
       <c r="J322" t="n">
+        <v>8</v>
+      </c>
+      <c r="K322" t="n">
         <v>12.27388887120917</v>
       </c>
     </row>
@@ -12713,6 +13681,9 @@
         </is>
       </c>
       <c r="J323" t="n">
+        <v>8</v>
+      </c>
+      <c r="K323" t="n">
         <v>12.12900492634642</v>
       </c>
     </row>
@@ -12751,6 +13722,9 @@
         </is>
       </c>
       <c r="J324" t="n">
+        <v>8</v>
+      </c>
+      <c r="K324" t="n">
         <v>12.12900492634642</v>
       </c>
     </row>
@@ -12789,6 +13763,9 @@
         </is>
       </c>
       <c r="J325" t="n">
+        <v>8</v>
+      </c>
+      <c r="K325" t="n">
         <v>12.00777517994545</v>
       </c>
     </row>
@@ -12827,6 +13804,9 @@
         </is>
       </c>
       <c r="J326" t="n">
+        <v>8</v>
+      </c>
+      <c r="K326" t="n">
         <v>12.00777517994545</v>
       </c>
     </row>
@@ -12865,6 +13845,9 @@
         </is>
       </c>
       <c r="J327" t="n">
+        <v>8</v>
+      </c>
+      <c r="K327" t="n">
         <v>3.884433380990276</v>
       </c>
     </row>
@@ -12903,6 +13886,9 @@
         </is>
       </c>
       <c r="J328" t="n">
+        <v>8</v>
+      </c>
+      <c r="K328" t="n">
         <v>3.622531082202372</v>
       </c>
     </row>
@@ -12941,6 +13927,9 @@
         </is>
       </c>
       <c r="J329" t="n">
+        <v>8</v>
+      </c>
+      <c r="K329" t="n">
         <v>3.598712166195315</v>
       </c>
     </row>
@@ -12979,6 +13968,9 @@
         </is>
       </c>
       <c r="J330" t="n">
+        <v>8</v>
+      </c>
+      <c r="K330" t="n">
         <v>3.917737752631037</v>
       </c>
     </row>
@@ -13017,6 +14009,9 @@
         </is>
       </c>
       <c r="J331" t="n">
+        <v>8</v>
+      </c>
+      <c r="K331" t="n">
         <v>3.917737752631037</v>
       </c>
     </row>
@@ -13055,6 +14050,9 @@
         </is>
       </c>
       <c r="J332" t="n">
+        <v>8</v>
+      </c>
+      <c r="K332" t="n">
         <v>4.136809907297358</v>
       </c>
     </row>
@@ -13093,6 +14091,9 @@
         </is>
       </c>
       <c r="J333" t="n">
+        <v>8</v>
+      </c>
+      <c r="K333" t="n">
         <v>4.136809907297358</v>
       </c>
     </row>
@@ -13131,6 +14132,9 @@
         </is>
       </c>
       <c r="J334" t="n">
+        <v>8</v>
+      </c>
+      <c r="K334" t="n">
         <v>4.158115381825009</v>
       </c>
     </row>
@@ -13169,6 +14173,9 @@
         </is>
       </c>
       <c r="J335" t="n">
+        <v>8</v>
+      </c>
+      <c r="K335" t="n">
         <v>4.158115381825009</v>
       </c>
     </row>
@@ -13207,6 +14214,9 @@
         </is>
       </c>
       <c r="J336" t="n">
+        <v>8</v>
+      </c>
+      <c r="K336" t="n">
         <v>4.158115381825009</v>
       </c>
     </row>
@@ -13245,6 +14255,9 @@
         </is>
       </c>
       <c r="J337" t="n">
+        <v>8</v>
+      </c>
+      <c r="K337" t="n">
         <v>4.133096902042531</v>
       </c>
     </row>
@@ -13283,6 +14296,9 @@
         </is>
       </c>
       <c r="J338" t="n">
+        <v>8</v>
+      </c>
+      <c r="K338" t="n">
         <v>4.070340637306797</v>
       </c>
     </row>
@@ -13321,6 +14337,9 @@
         </is>
       </c>
       <c r="J339" t="n">
+        <v>8</v>
+      </c>
+      <c r="K339" t="n">
         <v>4.028032961093987</v>
       </c>
     </row>
@@ -13359,6 +14378,9 @@
         </is>
       </c>
       <c r="J340" t="n">
+        <v>8</v>
+      </c>
+      <c r="K340" t="n">
         <v>4.400722162326129</v>
       </c>
     </row>
@@ -13397,6 +14419,9 @@
         </is>
       </c>
       <c r="J341" t="n">
+        <v>8</v>
+      </c>
+      <c r="K341" t="n">
         <v>4.90360089809189</v>
       </c>
     </row>
@@ -13435,6 +14460,9 @@
         </is>
       </c>
       <c r="J342" t="n">
+        <v>8</v>
+      </c>
+      <c r="K342" t="n">
         <v>5.188158174608672</v>
       </c>
     </row>
@@ -13473,6 +14501,9 @@
         </is>
       </c>
       <c r="J343" t="n">
+        <v>8</v>
+      </c>
+      <c r="K343" t="n">
         <v>5.348460043825728</v>
       </c>
     </row>
@@ -13511,6 +14542,9 @@
         </is>
       </c>
       <c r="J344" t="n">
+        <v>8</v>
+      </c>
+      <c r="K344" t="n">
         <v>5.348460043825728</v>
       </c>
     </row>
@@ -13549,6 +14583,9 @@
         </is>
       </c>
       <c r="J345" t="n">
+        <v>8</v>
+      </c>
+      <c r="K345" t="n">
         <v>5.348460043825728</v>
       </c>
     </row>
@@ -13587,6 +14624,9 @@
         </is>
       </c>
       <c r="J346" t="n">
+        <v>8</v>
+      </c>
+      <c r="K346" t="n">
         <v>5.478333415292999</v>
       </c>
     </row>
@@ -13625,6 +14665,9 @@
         </is>
       </c>
       <c r="J347" t="n">
+        <v>8</v>
+      </c>
+      <c r="K347" t="n">
         <v>5.488795294232706</v>
       </c>
     </row>
@@ -13663,6 +14706,9 @@
         </is>
       </c>
       <c r="J348" t="n">
+        <v>8</v>
+      </c>
+      <c r="K348" t="n">
         <v>5.497198494964292</v>
       </c>
     </row>
@@ -13701,6 +14747,9 @@
         </is>
       </c>
       <c r="J349" t="n">
+        <v>8</v>
+      </c>
+      <c r="K349" t="n">
         <v>5.497198494964292</v>
       </c>
     </row>
@@ -13739,6 +14788,9 @@
         </is>
       </c>
       <c r="J350" t="n">
+        <v>8</v>
+      </c>
+      <c r="K350" t="n">
         <v>5.486406504185313</v>
       </c>
     </row>
@@ -13777,6 +14829,9 @@
         </is>
       </c>
       <c r="J351" t="n">
+        <v>8</v>
+      </c>
+      <c r="K351" t="n">
         <v>5.477443803054033</v>
       </c>
     </row>
@@ -13815,6 +14870,9 @@
         </is>
       </c>
       <c r="J352" t="n">
+        <v>8</v>
+      </c>
+      <c r="K352" t="n">
         <v>5.477443803054033</v>
       </c>
     </row>
@@ -13853,6 +14911,9 @@
         </is>
       </c>
       <c r="J353" t="n">
+        <v>8</v>
+      </c>
+      <c r="K353" t="n">
         <v>5.491522189547601</v>
       </c>
     </row>
@@ -13891,6 +14952,9 @@
         </is>
       </c>
       <c r="J354" t="n">
+        <v>8</v>
+      </c>
+      <c r="K354" t="n">
         <v>5.491522189547601</v>
       </c>
     </row>
@@ -13929,6 +14993,9 @@
         </is>
       </c>
       <c r="J355" t="n">
+        <v>8</v>
+      </c>
+      <c r="K355" t="n">
         <v>5.491522189547601</v>
       </c>
     </row>
@@ -13967,6 +15034,9 @@
         </is>
       </c>
       <c r="J356" t="n">
+        <v>8</v>
+      </c>
+      <c r="K356" t="n">
         <v>5.707097386306653</v>
       </c>
     </row>
@@ -14005,6 +15075,9 @@
         </is>
       </c>
       <c r="J357" t="n">
+        <v>8</v>
+      </c>
+      <c r="K357" t="n">
         <v>6.744113134025241</v>
       </c>
     </row>
@@ -14043,6 +15116,9 @@
         </is>
       </c>
       <c r="J358" t="n">
+        <v>8</v>
+      </c>
+      <c r="K358" t="n">
         <v>6.870150773213437</v>
       </c>
     </row>
@@ -14081,6 +15157,9 @@
         </is>
       </c>
       <c r="J359" t="n">
+        <v>8</v>
+      </c>
+      <c r="K359" t="n">
         <v>6.870150773213437</v>
       </c>
     </row>
@@ -14119,6 +15198,9 @@
         </is>
       </c>
       <c r="J360" t="n">
+        <v>8</v>
+      </c>
+      <c r="K360" t="n">
         <v>7.179054632564358</v>
       </c>
     </row>
@@ -14157,6 +15239,9 @@
         </is>
       </c>
       <c r="J361" t="n">
+        <v>8</v>
+      </c>
+      <c r="K361" t="n">
         <v>7.179054632564358</v>
       </c>
     </row>
@@ -14195,6 +15280,9 @@
         </is>
       </c>
       <c r="J362" t="n">
+        <v>8</v>
+      </c>
+      <c r="K362" t="n">
         <v>7.179054632564358</v>
       </c>
     </row>
@@ -14233,6 +15321,9 @@
         </is>
       </c>
       <c r="J363" t="n">
+        <v>8</v>
+      </c>
+      <c r="K363" t="n">
         <v>7.258122634681863</v>
       </c>
     </row>
@@ -14271,6 +15362,9 @@
         </is>
       </c>
       <c r="J364" t="n">
+        <v>8</v>
+      </c>
+      <c r="K364" t="n">
         <v>7.306276720897095</v>
       </c>
     </row>
@@ -14309,6 +15403,9 @@
         </is>
       </c>
       <c r="J365" t="n">
+        <v>8</v>
+      </c>
+      <c r="K365" t="n">
         <v>7.348743207040283</v>
       </c>
     </row>
@@ -14347,6 +15444,9 @@
         </is>
       </c>
       <c r="J366" t="n">
+        <v>8</v>
+      </c>
+      <c r="K366" t="n">
         <v>7.348743207040283</v>
       </c>
     </row>
@@ -14385,6 +15485,9 @@
         </is>
       </c>
       <c r="J367" t="n">
+        <v>8</v>
+      </c>
+      <c r="K367" t="n">
         <v>7.365072711322708</v>
       </c>
     </row>
@@ -14423,6 +15526,9 @@
         </is>
       </c>
       <c r="J368" t="n">
+        <v>8</v>
+      </c>
+      <c r="K368" t="n">
         <v>7.404052151859517</v>
       </c>
     </row>
@@ -14461,6 +15567,9 @@
         </is>
       </c>
       <c r="J369" t="n">
+        <v>8</v>
+      </c>
+      <c r="K369" t="n">
         <v>7.404052151859517</v>
       </c>
     </row>
@@ -14499,6 +15608,9 @@
         </is>
       </c>
       <c r="J370" t="n">
+        <v>8</v>
+      </c>
+      <c r="K370" t="n">
         <v>8.087367220920493</v>
       </c>
     </row>
@@ -14537,6 +15649,9 @@
         </is>
       </c>
       <c r="J371" t="n">
+        <v>8</v>
+      </c>
+      <c r="K371" t="n">
         <v>8.340750589921145</v>
       </c>
     </row>
@@ -14575,6 +15690,9 @@
         </is>
       </c>
       <c r="J372" t="n">
+        <v>8</v>
+      </c>
+      <c r="K372" t="n">
         <v>8.623745928928621</v>
       </c>
     </row>
@@ -14613,6 +15731,9 @@
         </is>
       </c>
       <c r="J373" t="n">
+        <v>8</v>
+      </c>
+      <c r="K373" t="n">
         <v>8.697296182943857</v>
       </c>
     </row>
@@ -14651,6 +15772,9 @@
         </is>
       </c>
       <c r="J374" t="n">
+        <v>8</v>
+      </c>
+      <c r="K374" t="n">
         <v>8.659404250601028</v>
       </c>
     </row>
@@ -14689,6 +15813,9 @@
         </is>
       </c>
       <c r="J375" t="n">
+        <v>8</v>
+      </c>
+      <c r="K375" t="n">
         <v>8.659404250601028</v>
       </c>
     </row>
@@ -14727,6 +15854,9 @@
         </is>
       </c>
       <c r="J376" t="n">
+        <v>8</v>
+      </c>
+      <c r="K376" t="n">
         <v>8.538718972935298</v>
       </c>
     </row>
@@ -14765,6 +15895,9 @@
         </is>
       </c>
       <c r="J377" t="n">
+        <v>8</v>
+      </c>
+      <c r="K377" t="n">
         <v>8.538718972935298</v>
       </c>
     </row>
@@ -14803,6 +15936,9 @@
         </is>
       </c>
       <c r="J378" t="n">
+        <v>8</v>
+      </c>
+      <c r="K378" t="n">
         <v>8.404225858255087</v>
       </c>
     </row>
@@ -14841,6 +15977,9 @@
         </is>
       </c>
       <c r="J379" t="n">
+        <v>8</v>
+      </c>
+      <c r="K379" t="n">
         <v>8.404225858255087</v>
       </c>
     </row>
@@ -14879,6 +16018,9 @@
         </is>
       </c>
       <c r="J380" t="n">
+        <v>8</v>
+      </c>
+      <c r="K380" t="n">
         <v>8.391287514488182</v>
       </c>
     </row>
@@ -14917,6 +16059,9 @@
         </is>
       </c>
       <c r="J381" t="n">
+        <v>8</v>
+      </c>
+      <c r="K381" t="n">
         <v>8.463281404358067</v>
       </c>
     </row>
@@ -14955,6 +16100,9 @@
         </is>
       </c>
       <c r="J382" t="n">
+        <v>8</v>
+      </c>
+      <c r="K382" t="n">
         <v>8.700570124913613</v>
       </c>
     </row>
@@ -14993,6 +16141,9 @@
         </is>
       </c>
       <c r="J383" t="n">
+        <v>8</v>
+      </c>
+      <c r="K383" t="n">
         <v>8.799567433230429</v>
       </c>
     </row>
@@ -15031,6 +16182,9 @@
         </is>
       </c>
       <c r="J384" t="n">
+        <v>8</v>
+      </c>
+      <c r="K384" t="n">
         <v>8.843701850391344</v>
       </c>
     </row>
@@ -15069,6 +16223,9 @@
         </is>
       </c>
       <c r="J385" t="n">
+        <v>8</v>
+      </c>
+      <c r="K385" t="n">
         <v>8.843701850391344</v>
       </c>
     </row>
@@ -15107,6 +16264,9 @@
         </is>
       </c>
       <c r="J386" t="n">
+        <v>8</v>
+      </c>
+      <c r="K386" t="n">
         <v>8.837430548943365</v>
       </c>
     </row>
@@ -15145,6 +16305,9 @@
         </is>
       </c>
       <c r="J387" t="n">
+        <v>8</v>
+      </c>
+      <c r="K387" t="n">
         <v>8.749537786932692</v>
       </c>
     </row>
@@ -15183,6 +16346,9 @@
         </is>
       </c>
       <c r="J388" t="n">
+        <v>8</v>
+      </c>
+      <c r="K388" t="n">
         <v>8.749537786932692</v>
       </c>
     </row>
@@ -15221,6 +16387,9 @@
         </is>
       </c>
       <c r="J389" t="n">
+        <v>8</v>
+      </c>
+      <c r="K389" t="n">
         <v>8.55068835419284</v>
       </c>
     </row>
@@ -15259,6 +16428,9 @@
         </is>
       </c>
       <c r="J390" t="n">
+        <v>8</v>
+      </c>
+      <c r="K390" t="n">
         <v>8.309932461868314</v>
       </c>
     </row>
@@ -15297,6 +16469,9 @@
         </is>
       </c>
       <c r="J391" t="n">
+        <v>8</v>
+      </c>
+      <c r="K391" t="n">
         <v>8.004749304126664</v>
       </c>
     </row>
@@ -15335,6 +16510,9 @@
         </is>
       </c>
       <c r="J392" t="n">
+        <v>8</v>
+      </c>
+      <c r="K392" t="n">
         <v>8.004749304126664</v>
       </c>
     </row>
@@ -15373,6 +16551,9 @@
         </is>
       </c>
       <c r="J393" t="n">
+        <v>8</v>
+      </c>
+      <c r="K393" t="n">
         <v>7.980597705416823</v>
       </c>
     </row>
@@ -15411,6 +16592,9 @@
         </is>
       </c>
       <c r="J394" t="n">
+        <v>8</v>
+      </c>
+      <c r="K394" t="n">
         <v>8.026457772919128</v>
       </c>
     </row>
@@ -15449,6 +16633,9 @@
         </is>
       </c>
       <c r="J395" t="n">
+        <v>8</v>
+      </c>
+      <c r="K395" t="n">
         <v>8.05747743403867</v>
       </c>
     </row>
@@ -15487,6 +16674,9 @@
         </is>
       </c>
       <c r="J396" t="n">
+        <v>8</v>
+      </c>
+      <c r="K396" t="n">
         <v>8.057113182471557</v>
       </c>
     </row>
@@ -15525,6 +16715,9 @@
         </is>
       </c>
       <c r="J397" t="n">
+        <v>8</v>
+      </c>
+      <c r="K397" t="n">
         <v>8.02406702144741</v>
       </c>
     </row>
@@ -15563,6 +16756,9 @@
         </is>
       </c>
       <c r="J398" t="n">
+        <v>8</v>
+      </c>
+      <c r="K398" t="n">
         <v>7.879034253500655</v>
       </c>
     </row>
@@ -15601,6 +16797,9 @@
         </is>
       </c>
       <c r="J399" t="n">
+        <v>8</v>
+      </c>
+      <c r="K399" t="n">
         <v>7.879034253500655</v>
       </c>
     </row>
@@ -15639,6 +16838,9 @@
         </is>
       </c>
       <c r="J400" t="n">
+        <v>8</v>
+      </c>
+      <c r="K400" t="n">
         <v>7.817602445190611</v>
       </c>
     </row>
@@ -15677,6 +16879,9 @@
         </is>
       </c>
       <c r="J401" t="n">
+        <v>8</v>
+      </c>
+      <c r="K401" t="n">
         <v>7.817602445190611</v>
       </c>
     </row>
@@ -15715,6 +16920,9 @@
         </is>
       </c>
       <c r="J402" t="n">
+        <v>8</v>
+      </c>
+      <c r="K402" t="n">
         <v>7.736349103445513</v>
       </c>
     </row>
@@ -15753,6 +16961,9 @@
         </is>
       </c>
       <c r="J403" t="n">
+        <v>8</v>
+      </c>
+      <c r="K403" t="n">
         <v>7.736349103445513</v>
       </c>
     </row>
@@ -15791,6 +17002,9 @@
         </is>
       </c>
       <c r="J404" t="n">
+        <v>8</v>
+      </c>
+      <c r="K404" t="n">
         <v>7.736349103445513</v>
       </c>
     </row>
@@ -15829,6 +17043,9 @@
         </is>
       </c>
       <c r="J405" t="n">
+        <v>8</v>
+      </c>
+      <c r="K405" t="n">
         <v>7.653238757860326</v>
       </c>
     </row>
@@ -15867,6 +17084,9 @@
         </is>
       </c>
       <c r="J406" t="n">
+        <v>8</v>
+      </c>
+      <c r="K406" t="n">
         <v>7.587469474219201</v>
       </c>
     </row>
@@ -15905,6 +17125,9 @@
         </is>
       </c>
       <c r="J407" t="n">
+        <v>8</v>
+      </c>
+      <c r="K407" t="n">
         <v>7.534771954579769</v>
       </c>
     </row>
@@ -15943,6 +17166,9 @@
         </is>
       </c>
       <c r="J408" t="n">
+        <v>8</v>
+      </c>
+      <c r="K408" t="n">
         <v>7.485768987206552</v>
       </c>
     </row>
@@ -15981,6 +17207,9 @@
         </is>
       </c>
       <c r="J409" t="n">
+        <v>8</v>
+      </c>
+      <c r="K409" t="n">
         <v>7.485768987206552</v>
       </c>
     </row>
@@ -16019,6 +17248,9 @@
         </is>
       </c>
       <c r="J410" t="n">
+        <v>8</v>
+      </c>
+      <c r="K410" t="n">
         <v>7.420703799823401</v>
       </c>
     </row>
@@ -16057,6 +17289,9 @@
         </is>
       </c>
       <c r="J411" t="n">
+        <v>8</v>
+      </c>
+      <c r="K411" t="n">
         <v>7.420703799823401</v>
       </c>
     </row>
@@ -16095,6 +17330,9 @@
         </is>
       </c>
       <c r="J412" t="n">
+        <v>8</v>
+      </c>
+      <c r="K412" t="n">
         <v>7.431752521869918</v>
       </c>
     </row>
@@ -16133,6 +17371,9 @@
         </is>
       </c>
       <c r="J413" t="n">
+        <v>8</v>
+      </c>
+      <c r="K413" t="n">
         <v>7.42865706242139</v>
       </c>
     </row>
@@ -16171,6 +17412,9 @@
         </is>
       </c>
       <c r="J414" t="n">
+        <v>8</v>
+      </c>
+      <c r="K414" t="n">
         <v>7.42865706242139</v>
       </c>
     </row>
@@ -16209,6 +17453,9 @@
         </is>
       </c>
       <c r="J415" t="n">
+        <v>8</v>
+      </c>
+      <c r="K415" t="n">
         <v>7.407001590927718</v>
       </c>
     </row>
@@ -16247,6 +17494,9 @@
         </is>
       </c>
       <c r="J416" t="n">
+        <v>8</v>
+      </c>
+      <c r="K416" t="n">
         <v>7.407001590927718</v>
       </c>
     </row>
@@ -16285,6 +17535,9 @@
         </is>
       </c>
       <c r="J417" t="n">
+        <v>8</v>
+      </c>
+      <c r="K417" t="n">
         <v>7.407001590927718</v>
       </c>
     </row>
@@ -16323,6 +17576,9 @@
         </is>
       </c>
       <c r="J418" t="n">
+        <v>8</v>
+      </c>
+      <c r="K418" t="n">
         <v>7.394775202099418</v>
       </c>
     </row>
@@ -16361,6 +17617,9 @@
         </is>
       </c>
       <c r="J419" t="n">
+        <v>8</v>
+      </c>
+      <c r="K419" t="n">
         <v>7.47514438232257</v>
       </c>
     </row>
@@ -16399,6 +17658,9 @@
         </is>
       </c>
       <c r="J420" t="n">
+        <v>8</v>
+      </c>
+      <c r="K420" t="n">
         <v>7.47514438232257</v>
       </c>
     </row>
@@ -16437,6 +17699,9 @@
         </is>
       </c>
       <c r="J421" t="n">
+        <v>8</v>
+      </c>
+      <c r="K421" t="n">
         <v>7.548352359179225</v>
       </c>
     </row>
@@ -16475,6 +17740,9 @@
         </is>
       </c>
       <c r="J422" t="n">
+        <v>8</v>
+      </c>
+      <c r="K422" t="n">
         <v>7.690723817060812</v>
       </c>
     </row>
@@ -16513,6 +17781,9 @@
         </is>
       </c>
       <c r="J423" t="n">
+        <v>8</v>
+      </c>
+      <c r="K423" t="n">
         <v>7.690723817060812</v>
       </c>
     </row>
@@ -16551,6 +17822,9 @@
         </is>
       </c>
       <c r="J424" t="n">
+        <v>8</v>
+      </c>
+      <c r="K424" t="n">
         <v>7.742221438687249</v>
       </c>
     </row>
@@ -16589,6 +17863,9 @@
         </is>
       </c>
       <c r="J425" t="n">
+        <v>8</v>
+      </c>
+      <c r="K425" t="n">
         <v>7.760793803264704</v>
       </c>
     </row>
@@ -16627,6 +17904,9 @@
         </is>
       </c>
       <c r="J426" t="n">
+        <v>8</v>
+      </c>
+      <c r="K426" t="n">
         <v>7.748843574772835</v>
       </c>
     </row>
@@ -16665,6 +17945,9 @@
         </is>
       </c>
       <c r="J427" t="n">
+        <v>8</v>
+      </c>
+      <c r="K427" t="n">
         <v>7.697250352476516</v>
       </c>
     </row>
@@ -16703,6 +17986,9 @@
         </is>
       </c>
       <c r="J428" t="n">
+        <v>8</v>
+      </c>
+      <c r="K428" t="n">
         <v>7.663500383200234</v>
       </c>
     </row>
@@ -16741,6 +18027,9 @@
         </is>
       </c>
       <c r="J429" t="n">
+        <v>8</v>
+      </c>
+      <c r="K429" t="n">
         <v>7.663500383200234</v>
       </c>
     </row>
@@ -16779,6 +18068,9 @@
         </is>
       </c>
       <c r="J430" t="n">
+        <v>8</v>
+      </c>
+      <c r="K430" t="n">
         <v>7.663500383200234</v>
       </c>
     </row>
@@ -16817,6 +18109,9 @@
         </is>
       </c>
       <c r="J431" t="n">
+        <v>8</v>
+      </c>
+      <c r="K431" t="n">
         <v>7.620721963861576</v>
       </c>
     </row>
@@ -16855,6 +18150,9 @@
         </is>
       </c>
       <c r="J432" t="n">
+        <v>8</v>
+      </c>
+      <c r="K432" t="n">
         <v>7.583389237265234</v>
       </c>
     </row>
@@ -16893,6 +18191,9 @@
         </is>
       </c>
       <c r="J433" t="n">
+        <v>8</v>
+      </c>
+      <c r="K433" t="n">
         <v>7.583389237265234</v>
       </c>
     </row>
@@ -16931,6 +18232,9 @@
         </is>
       </c>
       <c r="J434" t="n">
+        <v>8</v>
+      </c>
+      <c r="K434" t="n">
         <v>7.493900677171784</v>
       </c>
     </row>
@@ -16969,6 +18273,9 @@
         </is>
       </c>
       <c r="J435" t="n">
+        <v>8</v>
+      </c>
+      <c r="K435" t="n">
         <v>7.494215154032344</v>
       </c>
     </row>
@@ -17007,6 +18314,9 @@
         </is>
       </c>
       <c r="J436" t="n">
+        <v>8</v>
+      </c>
+      <c r="K436" t="n">
         <v>7.453650234517263</v>
       </c>
     </row>
@@ -17045,6 +18355,9 @@
         </is>
       </c>
       <c r="J437" t="n">
+        <v>8</v>
+      </c>
+      <c r="K437" t="n">
         <v>7.412763008893109</v>
       </c>
     </row>
@@ -17083,6 +18396,9 @@
         </is>
       </c>
       <c r="J438" t="n">
+        <v>8</v>
+      </c>
+      <c r="K438" t="n">
         <v>7.347021858356184</v>
       </c>
     </row>
@@ -17121,6 +18437,9 @@
         </is>
       </c>
       <c r="J439" t="n">
+        <v>8</v>
+      </c>
+      <c r="K439" t="n">
         <v>7.347021858356184</v>
       </c>
     </row>
@@ -17159,6 +18478,9 @@
         </is>
       </c>
       <c r="J440" t="n">
+        <v>8</v>
+      </c>
+      <c r="K440" t="n">
         <v>7.226002592159174</v>
       </c>
     </row>
@@ -17197,6 +18519,9 @@
         </is>
       </c>
       <c r="J441" t="n">
+        <v>8</v>
+      </c>
+      <c r="K441" t="n">
         <v>7.226002592159174</v>
       </c>
     </row>
@@ -17235,6 +18560,9 @@
         </is>
       </c>
       <c r="J442" t="n">
+        <v>8</v>
+      </c>
+      <c r="K442" t="n">
         <v>7.165442106631088</v>
       </c>
     </row>
@@ -17273,6 +18601,9 @@
         </is>
       </c>
       <c r="J443" t="n">
+        <v>8</v>
+      </c>
+      <c r="K443" t="n">
         <v>6.999368546921748</v>
       </c>
     </row>
@@ -17311,6 +18642,9 @@
         </is>
       </c>
       <c r="J444" t="n">
+        <v>8</v>
+      </c>
+      <c r="K444" t="n">
         <v>6.915708436118067</v>
       </c>
     </row>
@@ -17349,6 +18683,9 @@
         </is>
       </c>
       <c r="J445" t="n">
+        <v>8</v>
+      </c>
+      <c r="K445" t="n">
         <v>6.792166952248122</v>
       </c>
     </row>
@@ -17387,6 +18724,9 @@
         </is>
       </c>
       <c r="J446" t="n">
+        <v>8</v>
+      </c>
+      <c r="K446" t="n">
         <v>6.734986402288253</v>
       </c>
     </row>
@@ -17425,6 +18765,9 @@
         </is>
       </c>
       <c r="J447" t="n">
+        <v>8</v>
+      </c>
+      <c r="K447" t="n">
         <v>6.734986402288253</v>
       </c>
     </row>
@@ -17463,6 +18806,9 @@
         </is>
       </c>
       <c r="J448" t="n">
+        <v>8</v>
+      </c>
+      <c r="K448" t="n">
         <v>6.734986402288253</v>
       </c>
     </row>
@@ -17501,6 +18847,9 @@
         </is>
       </c>
       <c r="J449" t="n">
+        <v>8</v>
+      </c>
+      <c r="K449" t="n">
         <v>6.692801400992137</v>
       </c>
     </row>
@@ -17539,6 +18888,9 @@
         </is>
       </c>
       <c r="J450" t="n">
+        <v>8</v>
+      </c>
+      <c r="K450" t="n">
         <v>6.692801400992137</v>
       </c>
     </row>
@@ -17577,6 +18929,9 @@
         </is>
       </c>
       <c r="J451" t="n">
+        <v>8</v>
+      </c>
+      <c r="K451" t="n">
         <v>6.643340672420938</v>
       </c>
     </row>
@@ -17615,6 +18970,9 @@
         </is>
       </c>
       <c r="J452" t="n">
+        <v>8</v>
+      </c>
+      <c r="K452" t="n">
         <v>6.643340672420938</v>
       </c>
     </row>
@@ -17653,6 +19011,9 @@
         </is>
       </c>
       <c r="J453" t="n">
+        <v>8</v>
+      </c>
+      <c r="K453" t="n">
         <v>6.580519510065824</v>
       </c>
     </row>
@@ -17691,6 +19052,9 @@
         </is>
       </c>
       <c r="J454" t="n">
+        <v>8</v>
+      </c>
+      <c r="K454" t="n">
         <v>6.537610963367728</v>
       </c>
     </row>
@@ -17729,6 +19093,9 @@
         </is>
       </c>
       <c r="J455" t="n">
+        <v>8</v>
+      </c>
+      <c r="K455" t="n">
         <v>6.537610963367728</v>
       </c>
     </row>
@@ -17767,6 +19134,9 @@
         </is>
       </c>
       <c r="J456" t="n">
+        <v>8</v>
+      </c>
+      <c r="K456" t="n">
         <v>6.490942147165584</v>
       </c>
     </row>
@@ -17805,6 +19175,9 @@
         </is>
       </c>
       <c r="J457" t="n">
+        <v>8</v>
+      </c>
+      <c r="K457" t="n">
         <v>6.460936097684441</v>
       </c>
     </row>
@@ -17843,6 +19216,9 @@
         </is>
       </c>
       <c r="J458" t="n">
+        <v>8</v>
+      </c>
+      <c r="K458" t="n">
         <v>6.4470393470795</v>
       </c>
     </row>
@@ -17881,6 +19257,9 @@
         </is>
       </c>
       <c r="J459" t="n">
+        <v>8</v>
+      </c>
+      <c r="K459" t="n">
         <v>6.448807491095861</v>
       </c>
     </row>
@@ -17919,6 +19298,9 @@
         </is>
       </c>
       <c r="J460" t="n">
+        <v>8</v>
+      </c>
+      <c r="K460" t="n">
         <v>6.424136051140363</v>
       </c>
     </row>
@@ -17957,6 +19339,9 @@
         </is>
       </c>
       <c r="J461" t="n">
+        <v>8</v>
+      </c>
+      <c r="K461" t="n">
         <v>6.424136051140363</v>
       </c>
     </row>
@@ -17995,6 +19380,9 @@
         </is>
       </c>
       <c r="J462" t="n">
+        <v>8</v>
+      </c>
+      <c r="K462" t="n">
         <v>6.4918602191819</v>
       </c>
     </row>
@@ -18033,6 +19421,9 @@
         </is>
       </c>
       <c r="J463" t="n">
+        <v>8</v>
+      </c>
+      <c r="K463" t="n">
         <v>6.525411988807496</v>
       </c>
     </row>
@@ -18071,6 +19462,9 @@
         </is>
       </c>
       <c r="J464" t="n">
+        <v>8</v>
+      </c>
+      <c r="K464" t="n">
         <v>6.722232742995771</v>
       </c>
     </row>
@@ -18109,6 +19503,9 @@
         </is>
       </c>
       <c r="J465" t="n">
+        <v>8</v>
+      </c>
+      <c r="K465" t="n">
         <v>6.722232742995771</v>
       </c>
     </row>
@@ -18147,6 +19544,9 @@
         </is>
       </c>
       <c r="J466" t="n">
+        <v>8</v>
+      </c>
+      <c r="K466" t="n">
         <v>6.782814894425483</v>
       </c>
     </row>
@@ -18185,6 +19585,9 @@
         </is>
       </c>
       <c r="J467" t="n">
+        <v>8</v>
+      </c>
+      <c r="K467" t="n">
         <v>6.828055490999511</v>
       </c>
     </row>
@@ -18223,6 +19626,9 @@
         </is>
       </c>
       <c r="J468" t="n">
+        <v>8</v>
+      </c>
+      <c r="K468" t="n">
         <v>6.837217126248234</v>
       </c>
     </row>
@@ -18261,6 +19667,9 @@
         </is>
       </c>
       <c r="J469" t="n">
+        <v>8</v>
+      </c>
+      <c r="K469" t="n">
         <v>6.82970298783613</v>
       </c>
     </row>
@@ -18299,6 +19708,9 @@
         </is>
       </c>
       <c r="J470" t="n">
+        <v>8</v>
+      </c>
+      <c r="K470" t="n">
         <v>6.82970298783613</v>
       </c>
     </row>
@@ -18337,6 +19749,9 @@
         </is>
       </c>
       <c r="J471" t="n">
+        <v>8</v>
+      </c>
+      <c r="K471" t="n">
         <v>6.761866688053744</v>
       </c>
     </row>
@@ -18375,6 +19790,9 @@
         </is>
       </c>
       <c r="J472" t="n">
+        <v>8</v>
+      </c>
+      <c r="K472" t="n">
         <v>6.714596691439461</v>
       </c>
     </row>
@@ -18413,6 +19831,9 @@
         </is>
       </c>
       <c r="J473" t="n">
+        <v>8</v>
+      </c>
+      <c r="K473" t="n">
         <v>6.502353806899219</v>
       </c>
     </row>
@@ -18451,6 +19872,9 @@
         </is>
       </c>
       <c r="J474" t="n">
+        <v>8</v>
+      </c>
+      <c r="K474" t="n">
         <v>6.419123464553661</v>
       </c>
     </row>
@@ -18489,6 +19913,9 @@
         </is>
       </c>
       <c r="J475" t="n">
+        <v>8</v>
+      </c>
+      <c r="K475" t="n">
         <v>6.421942525599955</v>
       </c>
     </row>
@@ -18527,6 +19954,9 @@
         </is>
       </c>
       <c r="J476" t="n">
+        <v>8</v>
+      </c>
+      <c r="K476" t="n">
         <v>6.487141782442913</v>
       </c>
     </row>
@@ -18565,6 +19995,9 @@
         </is>
       </c>
       <c r="J477" t="n">
+        <v>8</v>
+      </c>
+      <c r="K477" t="n">
         <v>6.574359814674901</v>
       </c>
     </row>
@@ -18603,6 +20036,9 @@
         </is>
       </c>
       <c r="J478" t="n">
+        <v>8</v>
+      </c>
+      <c r="K478" t="n">
         <v>7.462176575568333</v>
       </c>
     </row>
@@ -18641,6 +20077,9 @@
         </is>
       </c>
       <c r="J479" t="n">
+        <v>8</v>
+      </c>
+      <c r="K479" t="n">
         <v>7.543984587235664</v>
       </c>
     </row>
@@ -18679,6 +20118,9 @@
         </is>
       </c>
       <c r="J480" t="n">
+        <v>8</v>
+      </c>
+      <c r="K480" t="n">
         <v>7.445559242238189</v>
       </c>
     </row>
@@ -18717,6 +20159,9 @@
         </is>
       </c>
       <c r="J481" t="n">
+        <v>8</v>
+      </c>
+      <c r="K481" t="n">
         <v>7.445559242238189</v>
       </c>
     </row>
@@ -18755,6 +20200,9 @@
         </is>
       </c>
       <c r="J482" t="n">
+        <v>8</v>
+      </c>
+      <c r="K482" t="n">
         <v>7.445559242238189</v>
       </c>
     </row>
@@ -18793,6 +20241,9 @@
         </is>
       </c>
       <c r="J483" t="n">
+        <v>8</v>
+      </c>
+      <c r="K483" t="n">
         <v>7.643434689205128</v>
       </c>
     </row>
@@ -18831,6 +20282,9 @@
         </is>
       </c>
       <c r="J484" t="n">
+        <v>8</v>
+      </c>
+      <c r="K484" t="n">
         <v>7.799410224410647</v>
       </c>
     </row>
@@ -18869,6 +20323,9 @@
         </is>
       </c>
       <c r="J485" t="n">
+        <v>8</v>
+      </c>
+      <c r="K485" t="n">
         <v>8.54444280178312</v>
       </c>
     </row>
@@ -18907,6 +20364,9 @@
         </is>
       </c>
       <c r="J486" t="n">
+        <v>8</v>
+      </c>
+      <c r="K486" t="n">
         <v>8.868340429734996</v>
       </c>
     </row>
@@ -18945,6 +20405,9 @@
         </is>
       </c>
       <c r="J487" t="n">
+        <v>8</v>
+      </c>
+      <c r="K487" t="n">
         <v>8.868340429734996</v>
       </c>
     </row>
@@ -18983,6 +20446,9 @@
         </is>
       </c>
       <c r="J488" t="n">
+        <v>8</v>
+      </c>
+      <c r="K488" t="n">
         <v>9.590831002629944</v>
       </c>
     </row>
@@ -19021,6 +20487,9 @@
         </is>
       </c>
       <c r="J489" t="n">
+        <v>8</v>
+      </c>
+      <c r="K489" t="n">
         <v>9.821170185428153</v>
       </c>
     </row>
@@ -19059,6 +20528,9 @@
         </is>
       </c>
       <c r="J490" t="n">
+        <v>8</v>
+      </c>
+      <c r="K490" t="n">
         <v>9.821170185428153</v>
       </c>
     </row>
@@ -19097,6 +20569,9 @@
         </is>
       </c>
       <c r="J491" t="n">
+        <v>8</v>
+      </c>
+      <c r="K491" t="n">
         <v>9.757112264971322</v>
       </c>
     </row>
@@ -19135,6 +20610,9 @@
         </is>
       </c>
       <c r="J492" t="n">
+        <v>8</v>
+      </c>
+      <c r="K492" t="n">
         <v>9.757112264971322</v>
       </c>
     </row>
@@ -19173,6 +20651,9 @@
         </is>
       </c>
       <c r="J493" t="n">
+        <v>8</v>
+      </c>
+      <c r="K493" t="n">
         <v>9.594593115290277</v>
       </c>
     </row>
@@ -19211,6 +20692,9 @@
         </is>
       </c>
       <c r="J494" t="n">
+        <v>8</v>
+      </c>
+      <c r="K494" t="n">
         <v>9.679328450888336</v>
       </c>
     </row>
@@ -19249,6 +20733,9 @@
         </is>
       </c>
       <c r="J495" t="n">
+        <v>8</v>
+      </c>
+      <c r="K495" t="n">
         <v>10.28204465498533</v>
       </c>
     </row>
@@ -19287,6 +20774,9 @@
         </is>
       </c>
       <c r="J496" t="n">
+        <v>8</v>
+      </c>
+      <c r="K496" t="n">
         <v>10.28204465498533</v>
       </c>
     </row>
@@ -19325,6 +20815,9 @@
         </is>
       </c>
       <c r="J497" t="n">
+        <v>8</v>
+      </c>
+      <c r="K497" t="n">
         <v>11.65451815317547</v>
       </c>
     </row>
@@ -19363,6 +20856,9 @@
         </is>
       </c>
       <c r="J498" t="n">
+        <v>8</v>
+      </c>
+      <c r="K498" t="n">
         <v>11.65451815317547</v>
       </c>
     </row>
@@ -19401,6 +20897,9 @@
         </is>
       </c>
       <c r="J499" t="n">
+        <v>8</v>
+      </c>
+      <c r="K499" t="n">
         <v>11.65451815317547</v>
       </c>
     </row>
@@ -19439,6 +20938,9 @@
         </is>
       </c>
       <c r="J500" t="n">
+        <v>8</v>
+      </c>
+      <c r="K500" t="n">
         <v>11.65451815317547</v>
       </c>
     </row>
@@ -19477,6 +20979,9 @@
         </is>
       </c>
       <c r="J501" t="n">
+        <v>8</v>
+      </c>
+      <c r="K501" t="n">
         <v>12.56764572808129</v>
       </c>
     </row>
@@ -19515,6 +21020,9 @@
         </is>
       </c>
       <c r="J502" t="n">
+        <v>8</v>
+      </c>
+      <c r="K502" t="n">
         <v>12.56764572808129</v>
       </c>
     </row>
@@ -19553,6 +21061,9 @@
         </is>
       </c>
       <c r="J503" t="n">
+        <v>8</v>
+      </c>
+      <c r="K503" t="n">
         <v>12.56764572808129</v>
       </c>
     </row>
@@ -19591,6 +21102,9 @@
         </is>
       </c>
       <c r="J504" t="n">
+        <v>8</v>
+      </c>
+      <c r="K504" t="n">
         <v>12.56764572808129</v>
       </c>
     </row>
@@ -19629,6 +21143,9 @@
         </is>
       </c>
       <c r="J505" t="n">
+        <v>8</v>
+      </c>
+      <c r="K505" t="n">
         <v>12.28275412133916</v>
       </c>
     </row>
@@ -19667,6 +21184,9 @@
         </is>
       </c>
       <c r="J506" t="n">
+        <v>8</v>
+      </c>
+      <c r="K506" t="n">
         <v>11.95297558050846</v>
       </c>
     </row>
@@ -19705,6 +21225,9 @@
         </is>
       </c>
       <c r="J507" t="n">
+        <v>8</v>
+      </c>
+      <c r="K507" t="n">
         <v>11.98256901992308</v>
       </c>
     </row>
@@ -19743,6 +21266,9 @@
         </is>
       </c>
       <c r="J508" t="n">
+        <v>8</v>
+      </c>
+      <c r="K508" t="n">
         <v>11.9670705359759</v>
       </c>
     </row>
@@ -19781,6 +21307,9 @@
         </is>
       </c>
       <c r="J509" t="n">
+        <v>8</v>
+      </c>
+      <c r="K509" t="n">
         <v>11.94388011410195</v>
       </c>
     </row>
@@ -19819,6 +21348,9 @@
         </is>
       </c>
       <c r="J510" t="n">
+        <v>8</v>
+      </c>
+      <c r="K510" t="n">
         <v>11.94984037627904</v>
       </c>
     </row>
@@ -19857,6 +21389,9 @@
         </is>
       </c>
       <c r="J511" t="n">
+        <v>8</v>
+      </c>
+      <c r="K511" t="n">
         <v>11.94984037627904</v>
       </c>
     </row>
@@ -19895,6 +21430,9 @@
         </is>
       </c>
       <c r="J512" t="n">
+        <v>8</v>
+      </c>
+      <c r="K512" t="n">
         <v>11.98482961517762</v>
       </c>
     </row>
@@ -19933,6 +21471,9 @@
         </is>
       </c>
       <c r="J513" t="n">
+        <v>8</v>
+      </c>
+      <c r="K513" t="n">
         <v>11.98916214856828</v>
       </c>
     </row>
@@ -19971,6 +21512,9 @@
         </is>
       </c>
       <c r="J514" t="n">
+        <v>19</v>
+      </c>
+      <c r="K514" t="n">
         <v>11.90068433427212</v>
       </c>
     </row>
@@ -20009,6 +21553,9 @@
         </is>
       </c>
       <c r="J515" t="n">
+        <v>19</v>
+      </c>
+      <c r="K515" t="n">
         <v>1.854511666012223</v>
       </c>
     </row>
@@ -20047,6 +21594,9 @@
         </is>
       </c>
       <c r="J516" t="n">
+        <v>19</v>
+      </c>
+      <c r="K516" t="n">
         <v>1.837854804432754</v>
       </c>
     </row>
@@ -20085,6 +21635,9 @@
         </is>
       </c>
       <c r="J517" t="n">
+        <v>19</v>
+      </c>
+      <c r="K517" t="n">
         <v>1.837854804432754</v>
       </c>
     </row>
@@ -20123,6 +21676,9 @@
         </is>
       </c>
       <c r="J518" t="n">
+        <v>19</v>
+      </c>
+      <c r="K518" t="n">
         <v>1.878518409700617</v>
       </c>
     </row>
@@ -20161,6 +21717,9 @@
         </is>
       </c>
       <c r="J519" t="n">
+        <v>19</v>
+      </c>
+      <c r="K519" t="n">
         <v>1.933052751035792</v>
       </c>
     </row>
@@ -20199,6 +21758,9 @@
         </is>
       </c>
       <c r="J520" t="n">
+        <v>19</v>
+      </c>
+      <c r="K520" t="n">
         <v>1.936871790508979</v>
       </c>
     </row>
@@ -20237,6 +21799,9 @@
         </is>
       </c>
       <c r="J521" t="n">
+        <v>19</v>
+      </c>
+      <c r="K521" t="n">
         <v>2.031667658521711</v>
       </c>
     </row>
@@ -20275,6 +21840,9 @@
         </is>
       </c>
       <c r="J522" t="n">
+        <v>19</v>
+      </c>
+      <c r="K522" t="n">
         <v>2.058067351255422</v>
       </c>
     </row>
@@ -20313,6 +21881,9 @@
         </is>
       </c>
       <c r="J523" t="n">
+        <v>19</v>
+      </c>
+      <c r="K523" t="n">
         <v>2.075892286368119</v>
       </c>
     </row>
@@ -20351,6 +21922,9 @@
         </is>
       </c>
       <c r="J524" t="n">
+        <v>19</v>
+      </c>
+      <c r="K524" t="n">
         <v>2.103265806005446</v>
       </c>
     </row>
@@ -20389,6 +21963,9 @@
         </is>
       </c>
       <c r="J525" t="n">
+        <v>19</v>
+      </c>
+      <c r="K525" t="n">
         <v>2.103265806005446</v>
       </c>
     </row>
@@ -20427,6 +22004,9 @@
         </is>
       </c>
       <c r="J526" t="n">
+        <v>19</v>
+      </c>
+      <c r="K526" t="n">
         <v>2.117983780045384</v>
       </c>
     </row>
@@ -20465,6 +22045,9 @@
         </is>
       </c>
       <c r="J527" t="n">
+        <v>19</v>
+      </c>
+      <c r="K527" t="n">
         <v>2.074231144885531</v>
       </c>
     </row>
@@ -20503,6 +22086,9 @@
         </is>
       </c>
       <c r="J528" t="n">
+        <v>19</v>
+      </c>
+      <c r="K528" t="n">
         <v>2.03991513908291</v>
       </c>
     </row>
@@ -20541,6 +22127,9 @@
         </is>
       </c>
       <c r="J529" t="n">
+        <v>19</v>
+      </c>
+      <c r="K529" t="n">
         <v>2.03991513908291</v>
       </c>
     </row>
@@ -20579,6 +22168,9 @@
         </is>
       </c>
       <c r="J530" t="n">
+        <v>19</v>
+      </c>
+      <c r="K530" t="n">
         <v>2.03991513908291</v>
       </c>
     </row>
@@ -20617,6 +22209,9 @@
         </is>
       </c>
       <c r="J531" t="n">
+        <v>19</v>
+      </c>
+      <c r="K531" t="n">
         <v>1.942154179002464</v>
       </c>
     </row>
@@ -20655,6 +22250,9 @@
         </is>
       </c>
       <c r="J532" t="n">
+        <v>19</v>
+      </c>
+      <c r="K532" t="n">
         <v>1.942154179002464</v>
       </c>
     </row>
@@ -20693,6 +22291,9 @@
         </is>
       </c>
       <c r="J533" t="n">
+        <v>19</v>
+      </c>
+      <c r="K533" t="n">
         <v>1.918784314882659</v>
       </c>
     </row>
@@ -20731,6 +22332,9 @@
         </is>
       </c>
       <c r="J534" t="n">
+        <v>19</v>
+      </c>
+      <c r="K534" t="n">
         <v>1.918784314882659</v>
       </c>
     </row>
@@ -20769,6 +22373,9 @@
         </is>
       </c>
       <c r="J535" t="n">
+        <v>19</v>
+      </c>
+      <c r="K535" t="n">
         <v>1.894223016198969</v>
       </c>
     </row>
@@ -20807,6 +22414,9 @@
         </is>
       </c>
       <c r="J536" t="n">
+        <v>19</v>
+      </c>
+      <c r="K536" t="n">
         <v>1.856385428556687</v>
       </c>
     </row>
@@ -20845,6 +22455,9 @@
         </is>
       </c>
       <c r="J537" t="n">
+        <v>19</v>
+      </c>
+      <c r="K537" t="n">
         <v>1.804787300755467</v>
       </c>
     </row>
@@ -20883,6 +22496,9 @@
         </is>
       </c>
       <c r="J538" t="n">
+        <v>19</v>
+      </c>
+      <c r="K538" t="n">
         <v>1.804787300755467</v>
       </c>
     </row>
@@ -20921,6 +22537,9 @@
         </is>
       </c>
       <c r="J539" t="n">
+        <v>19</v>
+      </c>
+      <c r="K539" t="n">
         <v>1.754472334537045</v>
       </c>
     </row>
@@ -20959,6 +22578,9 @@
         </is>
       </c>
       <c r="J540" t="n">
+        <v>19</v>
+      </c>
+      <c r="K540" t="n">
         <v>1.657703849841727</v>
       </c>
     </row>
@@ -20997,6 +22619,9 @@
         </is>
       </c>
       <c r="J541" t="n">
+        <v>19</v>
+      </c>
+      <c r="K541" t="n">
         <v>1.616854180602157</v>
       </c>
     </row>
@@ -21035,6 +22660,9 @@
         </is>
       </c>
       <c r="J542" t="n">
+        <v>19</v>
+      </c>
+      <c r="K542" t="n">
         <v>1.616854180602157</v>
       </c>
     </row>
@@ -21073,6 +22701,9 @@
         </is>
       </c>
       <c r="J543" t="n">
+        <v>19</v>
+      </c>
+      <c r="K543" t="n">
         <v>1.616854180602157</v>
       </c>
     </row>
@@ -21111,6 +22742,9 @@
         </is>
       </c>
       <c r="J544" t="n">
+        <v>19</v>
+      </c>
+      <c r="K544" t="n">
         <v>1.611744298764642</v>
       </c>
     </row>
@@ -21149,6 +22783,9 @@
         </is>
       </c>
       <c r="J545" t="n">
+        <v>19</v>
+      </c>
+      <c r="K545" t="n">
         <v>1.666858466927333</v>
       </c>
     </row>
@@ -21187,6 +22824,9 @@
         </is>
       </c>
       <c r="J546" t="n">
+        <v>19</v>
+      </c>
+      <c r="K546" t="n">
         <v>1.689231826882966</v>
       </c>
     </row>
@@ -21225,6 +22865,9 @@
         </is>
       </c>
       <c r="J547" t="n">
+        <v>19</v>
+      </c>
+      <c r="K547" t="n">
         <v>1.734199260558366</v>
       </c>
     </row>
@@ -21263,6 +22906,9 @@
         </is>
       </c>
       <c r="J548" t="n">
+        <v>19</v>
+      </c>
+      <c r="K548" t="n">
         <v>1.734199260558366</v>
       </c>
     </row>
@@ -21301,6 +22947,9 @@
         </is>
       </c>
       <c r="J549" t="n">
+        <v>19</v>
+      </c>
+      <c r="K549" t="n">
         <v>1.73466354682686</v>
       </c>
     </row>
@@ -21339,6 +22988,9 @@
         </is>
       </c>
       <c r="J550" t="n">
+        <v>19</v>
+      </c>
+      <c r="K550" t="n">
         <v>1.745256985177947</v>
       </c>
     </row>
@@ -21377,6 +23029,9 @@
         </is>
       </c>
       <c r="J551" t="n">
+        <v>19</v>
+      </c>
+      <c r="K551" t="n">
         <v>1.765590904903235</v>
       </c>
     </row>
@@ -21415,6 +23070,9 @@
         </is>
       </c>
       <c r="J552" t="n">
+        <v>19</v>
+      </c>
+      <c r="K552" t="n">
         <v>1.795184173327543</v>
       </c>
     </row>
@@ -21453,6 +23111,9 @@
         </is>
       </c>
       <c r="J553" t="n">
+        <v>19</v>
+      </c>
+      <c r="K553" t="n">
         <v>2.089489818513586</v>
       </c>
     </row>
@@ -21491,6 +23152,9 @@
         </is>
       </c>
       <c r="J554" t="n">
+        <v>19</v>
+      </c>
+      <c r="K554" t="n">
         <v>2.14523251725942</v>
       </c>
     </row>
@@ -21529,6 +23193,9 @@
         </is>
       </c>
       <c r="J555" t="n">
+        <v>19</v>
+      </c>
+      <c r="K555" t="n">
         <v>2.159373018416571</v>
       </c>
     </row>
@@ -21567,6 +23234,9 @@
         </is>
       </c>
       <c r="J556" t="n">
+        <v>19</v>
+      </c>
+      <c r="K556" t="n">
         <v>2.159373018416571</v>
       </c>
     </row>
@@ -21605,6 +23275,9 @@
         </is>
       </c>
       <c r="J557" t="n">
+        <v>19</v>
+      </c>
+      <c r="K557" t="n">
         <v>2.063991914309505</v>
       </c>
     </row>
@@ -21643,6 +23316,9 @@
         </is>
       </c>
       <c r="J558" t="n">
+        <v>19</v>
+      </c>
+      <c r="K558" t="n">
         <v>2.063991914309505</v>
       </c>
     </row>
@@ -21681,6 +23357,9 @@
         </is>
       </c>
       <c r="J559" t="n">
+        <v>19</v>
+      </c>
+      <c r="K559" t="n">
         <v>2.022490606573764</v>
       </c>
     </row>
@@ -21719,6 +23398,9 @@
         </is>
       </c>
       <c r="J560" t="n">
+        <v>19</v>
+      </c>
+      <c r="K560" t="n">
         <v>1.876291638813557</v>
       </c>
     </row>
@@ -21757,6 +23439,9 @@
         </is>
       </c>
       <c r="J561" t="n">
+        <v>19</v>
+      </c>
+      <c r="K561" t="n">
         <v>1.80215443369725</v>
       </c>
     </row>
@@ -21795,6 +23480,9 @@
         </is>
       </c>
       <c r="J562" t="n">
+        <v>19</v>
+      </c>
+      <c r="K562" t="n">
         <v>1.80215443369725</v>
       </c>
     </row>
@@ -21833,6 +23521,9 @@
         </is>
       </c>
       <c r="J563" t="n">
+        <v>19</v>
+      </c>
+      <c r="K563" t="n">
         <v>1.722970997575011</v>
       </c>
     </row>
@@ -21871,6 +23562,9 @@
         </is>
       </c>
       <c r="J564" t="n">
+        <v>19</v>
+      </c>
+      <c r="K564" t="n">
         <v>1.646222765020578</v>
       </c>
     </row>
@@ -21909,6 +23603,9 @@
         </is>
       </c>
       <c r="J565" t="n">
+        <v>19</v>
+      </c>
+      <c r="K565" t="n">
         <v>1.579538031108389</v>
       </c>
     </row>
@@ -21947,6 +23644,9 @@
         </is>
       </c>
       <c r="J566" t="n">
+        <v>19</v>
+      </c>
+      <c r="K566" t="n">
         <v>1.337429187511639</v>
       </c>
     </row>
@@ -21985,6 +23685,9 @@
         </is>
       </c>
       <c r="J567" t="n">
+        <v>19</v>
+      </c>
+      <c r="K567" t="n">
         <v>1.337429187511639</v>
       </c>
     </row>
@@ -22023,6 +23726,9 @@
         </is>
       </c>
       <c r="J568" t="n">
+        <v>19</v>
+      </c>
+      <c r="K568" t="n">
         <v>1.286885940281709</v>
       </c>
     </row>
@@ -22061,6 +23767,9 @@
         </is>
       </c>
       <c r="J569" t="n">
+        <v>19</v>
+      </c>
+      <c r="K569" t="n">
         <v>1.214426202748521</v>
       </c>
     </row>
@@ -22099,6 +23808,9 @@
         </is>
       </c>
       <c r="J570" t="n">
+        <v>19</v>
+      </c>
+      <c r="K570" t="n">
         <v>1.006379263468961</v>
       </c>
     </row>
@@ -22137,6 +23849,9 @@
         </is>
       </c>
       <c r="J571" t="n">
+        <v>19</v>
+      </c>
+      <c r="K571" t="n">
         <v>0.8976153529990392</v>
       </c>
     </row>
@@ -22175,6 +23890,9 @@
         </is>
       </c>
       <c r="J572" t="n">
+        <v>19</v>
+      </c>
+      <c r="K572" t="n">
         <v>0.8089631242646705</v>
       </c>
     </row>
@@ -22213,6 +23931,9 @@
         </is>
       </c>
       <c r="J573" t="n">
+        <v>19</v>
+      </c>
+      <c r="K573" t="n">
         <v>0.8089631242646705</v>
       </c>
     </row>
@@ -22251,6 +23972,9 @@
         </is>
       </c>
       <c r="J574" t="n">
+        <v>19</v>
+      </c>
+      <c r="K574" t="n">
         <v>0.8089631242646705</v>
       </c>
     </row>
@@ -22289,6 +24013,9 @@
         </is>
       </c>
       <c r="J575" t="n">
+        <v>19</v>
+      </c>
+      <c r="K575" t="n">
         <v>0.8753441795877797</v>
       </c>
     </row>
@@ -22327,6 +24054,9 @@
         </is>
       </c>
       <c r="J576" t="n">
+        <v>19</v>
+      </c>
+      <c r="K576" t="n">
         <v>0.9155859948818886</v>
       </c>
     </row>
@@ -22365,6 +24095,9 @@
         </is>
       </c>
       <c r="J577" t="n">
+        <v>19</v>
+      </c>
+      <c r="K577" t="n">
         <v>0.9155859948818886</v>
       </c>
     </row>
@@ -22403,6 +24136,9 @@
         </is>
       </c>
       <c r="J578" t="n">
+        <v>19</v>
+      </c>
+      <c r="K578" t="n">
         <v>0.9977260068355764</v>
       </c>
     </row>
@@ -22441,6 +24177,9 @@
         </is>
       </c>
       <c r="J579" t="n">
+        <v>19</v>
+      </c>
+      <c r="K579" t="n">
         <v>1.032098116289559</v>
       </c>
     </row>
@@ -22479,6 +24218,9 @@
         </is>
       </c>
       <c r="J580" t="n">
+        <v>19</v>
+      </c>
+      <c r="K580" t="n">
         <v>1.041232127642572</v>
       </c>
     </row>
@@ -22517,6 +24259,9 @@
         </is>
       </c>
       <c r="J581" t="n">
+        <v>19</v>
+      </c>
+      <c r="K581" t="n">
         <v>1.050726503268967</v>
       </c>
     </row>
@@ -22555,6 +24300,9 @@
         </is>
       </c>
       <c r="J582" t="n">
+        <v>19</v>
+      </c>
+      <c r="K582" t="n">
         <v>1.075127849159322</v>
       </c>
     </row>
@@ -22593,6 +24341,9 @@
         </is>
       </c>
       <c r="J583" t="n">
+        <v>19</v>
+      </c>
+      <c r="K583" t="n">
         <v>1.219802879810765</v>
       </c>
     </row>
@@ -22631,6 +24382,9 @@
         </is>
       </c>
       <c r="J584" t="n">
+        <v>19</v>
+      </c>
+      <c r="K584" t="n">
         <v>1.251228837352856</v>
       </c>
     </row>

--- a/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B03_Normal_1.xlsx
+++ b/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B03_Normal_1.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>24.44938674448072</v>
+        <v>22.73756640125236</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>16.22537890841612</v>
+        <v>16.29324050952215</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>15.92519383307983</v>
+        <v>15.99543613326018</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>15.55123726155539</v>
+        <v>15.62439489880449</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>15.50392193361757</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86969785602394</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86959415022024</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>13.96252814601202</v>
+        <v>13.91864954866779</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>12.8845474029381</v>
+        <v>12.87463469178007</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>12.56557511094277</v>
+        <v>12.56213898660848</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>12.56557511094277</v>
+        <v>12.55954078162074</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>12.42650727241244</v>
+        <v>12.41804037237105</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>12.61222121789064</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>12.88726856229838</v>
+        <v>12.89114719647669</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>13.08268414389388</v>
+        <v>13.08601325120547</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>13.11655963642752</v>
+        <v>13.1112961343127</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>13.06477406907523</v>
+        <v>13.06050754757873</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>12.82946633796654</v>
+        <v>12.82287865109407</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>12.72199060197538</v>
+        <v>12.71927945377958</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>12.76786570293602</v>
+        <v>12.77031387086443</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>12.94918332241907</v>
+        <v>12.95485717835137</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29520804089071</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29710102990174</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>13.74461230569916</v>
+        <v>13.75403391875815</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>14.01711486461985</v>
+        <v>14.02366076953313</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>14.25821179004597</v>
+        <v>14.26268479452115</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>14.35948117378207</v>
+        <v>14.35993720530086</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>14.35948117378207</v>
+        <v>14.35993720530086</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>14.39337587577508</v>
+        <v>14.39231959267601</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>14.33776555810451</v>
+        <v>14.34250198872172</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>14.33776555810451</v>
+        <v>14.33763057188486</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>14.33776555810451</v>
+        <v>14.33763057188486</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>14.46751017667901</v>
+        <v>14.46958771214976</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>14.90065600322594</v>
+        <v>14.88833480134777</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>15.10789666146953</v>
+        <v>15.08131980831518</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>15.24076100085329</v>
+        <v>15.23824314337372</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>15.28683754312319</v>
+        <v>15.31237881114555</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>15.28683754312319</v>
+        <v>15.31237881114555</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>15.45586864838683</v>
+        <v>15.53738489344973</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>38.49477201445094</v>
+        <v>41.85527415873189</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>50.66302055048502</v>
+        <v>51.03791363001811</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>50.66302055048502</v>
+        <v>51.03791363001811</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>73.02287512573871</v>
+        <v>70.22101375492795</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>27.5466963351074</v>
+        <v>28.13926043732958</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>25.49347212687086</v>
+        <v>25.80032314541072</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>6</v>
       </c>
       <c r="K56" t="n">
-        <v>23.97322394592734</v>
+        <v>25.67335572679642</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>21.33836097537404</v>
+        <v>22.39575428021364</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>6</v>
       </c>
       <c r="K58" t="n">
-        <v>21.36069899557773</v>
+        <v>22.40658457261621</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>21.36069899557773</v>
+        <v>22.40658457261621</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>23.60395345894496</v>
+        <v>22.66819578486057</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>6</v>
       </c>
       <c r="K61" t="n">
-        <v>23.60395345894496</v>
+        <v>22.66819578486057</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>6</v>
       </c>
       <c r="K62" t="n">
-        <v>30.32524846705273</v>
+        <v>27.24711752730424</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>6</v>
       </c>
       <c r="K63" t="n">
-        <v>33.1118269799849</v>
+        <v>29.32917623785547</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>33.1118269799849</v>
+        <v>29.32917623785547</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>6</v>
       </c>
       <c r="K65" t="n">
-        <v>93.42524075950476</v>
+        <v>31.27985483414414</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>93.42524075950476</v>
+        <v>31.27985483414414</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>6</v>
       </c>
       <c r="K67" t="n">
-        <v>93.43501340024444</v>
+        <v>31.88841857057561</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>93.43501340024444</v>
+        <v>31.88841857057561</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>6</v>
       </c>
       <c r="K69" t="n">
-        <v>29.05532579013986</v>
+        <v>28.70137421356502</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>6</v>
       </c>
       <c r="K70" t="n">
-        <v>29.05532579013986</v>
+        <v>28.56331160274965</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>6</v>
       </c>
       <c r="K71" t="n">
-        <v>10.60692062922534</v>
+        <v>10.56353720219123</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="K72" t="n">
-        <v>10.24700477381645</v>
+        <v>10.19530365223804</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>10.21282575007027</v>
+        <v>10.16809568606692</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>6</v>
       </c>
       <c r="K74" t="n">
-        <v>9.761777786710743</v>
+        <v>9.74244778248134</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>9.761777786710743</v>
+        <v>9.74244778248134</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>9.33637179119815</v>
+        <v>9.334382106700145</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>9.290631264491166</v>
+        <v>9.289206683320749</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>9.301046132712429</v>
+        <v>9.305111203703676</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>9.452446335487469</v>
+        <v>9.463950560908867</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>6</v>
       </c>
       <c r="K80" t="n">
-        <v>9.661749357520293</v>
+        <v>9.671360125421126</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="K81" t="n">
-        <v>9.737462158199968</v>
+        <v>9.713089998084643</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="K82" t="n">
-        <v>9.809590006987829</v>
+        <v>9.812524218291237</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>6</v>
       </c>
       <c r="K83" t="n">
-        <v>9.807131585129085</v>
+        <v>9.812524218291237</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>10.03578416659066</v>
+        <v>10.04075472918658</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>6</v>
       </c>
       <c r="K85" t="n">
-        <v>10.12549314622187</v>
+        <v>10.14534989254991</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>6</v>
       </c>
       <c r="K86" t="n">
-        <v>10.57589925462877</v>
+        <v>10.5784806282848</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>6</v>
       </c>
       <c r="K87" t="n">
-        <v>10.60268682414666</v>
+        <v>10.60555613158018</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>6</v>
       </c>
       <c r="K88" t="n">
-        <v>10.62312997770562</v>
+        <v>10.6077046424083</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>10.62248024777271</v>
+        <v>10.62865290898554</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>10.87806600786918</v>
+        <v>10.88520124779484</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>10.92162235687036</v>
+        <v>10.92709848806466</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>6</v>
       </c>
       <c r="K92" t="n">
-        <v>10.95616069257222</v>
+        <v>10.96189869435236</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>6</v>
       </c>
       <c r="K93" t="n">
-        <v>11.00900355804066</v>
+        <v>11.01112865213726</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>6</v>
       </c>
       <c r="K94" t="n">
-        <v>11.01773536723862</v>
+        <v>11.018354095561</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>6</v>
       </c>
       <c r="K95" t="n">
-        <v>11.01276194340502</v>
+        <v>11.00953264575653</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>6</v>
       </c>
       <c r="K96" t="n">
-        <v>10.91014021015967</v>
+        <v>10.89968555114491</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>6</v>
       </c>
       <c r="K97" t="n">
-        <v>10.75714398709465</v>
+        <v>10.74641774112814</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>6</v>
       </c>
       <c r="K98" t="n">
-        <v>10.53712094521892</v>
+        <v>10.53428444199073</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>6</v>
       </c>
       <c r="K99" t="n">
-        <v>10.38432375970871</v>
+        <v>10.35174796601055</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>6</v>
       </c>
       <c r="K100" t="n">
-        <v>10.11688682207371</v>
+        <v>10.0797334699099</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>6</v>
       </c>
       <c r="K101" t="n">
-        <v>10.11688682207371</v>
+        <v>10.0797334699099</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>6</v>
       </c>
       <c r="K102" t="n">
-        <v>9.579029976242865</v>
+        <v>9.547526235149299</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>6</v>
       </c>
       <c r="K103" t="n">
-        <v>9.579029976242865</v>
+        <v>9.547526235149299</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>6</v>
       </c>
       <c r="K104" t="n">
-        <v>9.552229142031393</v>
+        <v>9.515191599918353</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>6</v>
       </c>
       <c r="K105" t="n">
-        <v>9.337125357350384</v>
+        <v>9.515191599918353</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>6</v>
       </c>
       <c r="K106" t="n">
-        <v>8.794782428856642</v>
+        <v>8.778468627187005</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>6</v>
       </c>
       <c r="K107" t="n">
-        <v>8.704344846279827</v>
+        <v>8.766071098486607</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>6</v>
       </c>
       <c r="K108" t="n">
-        <v>8.655508037001059</v>
+        <v>8.660472291933454</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>6</v>
       </c>
       <c r="K109" t="n">
-        <v>8.858023257647872</v>
+        <v>8.87437875450698</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="K110" t="n">
-        <v>8.971438026392272</v>
+        <v>8.973642303512785</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>6</v>
       </c>
       <c r="K111" t="n">
-        <v>9.152459961658085</v>
+        <v>9.158641167072478</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>6</v>
       </c>
       <c r="K112" t="n">
-        <v>9.158723808345748</v>
+        <v>9.158898762760314</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>6</v>
       </c>
       <c r="K113" t="n">
-        <v>9.153048952007417</v>
+        <v>9.151724631834414</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>6</v>
       </c>
       <c r="K114" t="n">
-        <v>9.256091506980455</v>
+        <v>9.205402671033942</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>6</v>
       </c>
       <c r="K115" t="n">
-        <v>9.403867914857166</v>
+        <v>9.403399618816287</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>6</v>
       </c>
       <c r="K116" t="n">
-        <v>9.368423488149045</v>
+        <v>9.399987799230123</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>6</v>
       </c>
       <c r="K117" t="n">
-        <v>9.268971225409532</v>
+        <v>9.250192540660322</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>6</v>
       </c>
       <c r="K118" t="n">
-        <v>9.159228079297097</v>
+        <v>9.141918112841262</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>6</v>
       </c>
       <c r="K119" t="n">
-        <v>9.051605715933476</v>
+        <v>9.126831340801603</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>6</v>
       </c>
       <c r="K120" t="n">
-        <v>9.049780946629296</v>
+        <v>9.032940356461713</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>6</v>
       </c>
       <c r="K121" t="n">
-        <v>9.049780946629296</v>
+        <v>9.032940356461713</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>6</v>
       </c>
       <c r="K122" t="n">
-        <v>8.797053500090465</v>
+        <v>8.778672810676495</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>6</v>
       </c>
       <c r="K123" t="n">
-        <v>8.797053500090465</v>
+        <v>8.778672810676495</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>6</v>
       </c>
       <c r="K124" t="n">
-        <v>8.679703519346106</v>
+        <v>8.672861443756478</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>6</v>
       </c>
       <c r="K125" t="n">
-        <v>8.671066277014619</v>
+        <v>8.670969426295731</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>6</v>
       </c>
       <c r="K126" t="n">
-        <v>8.527369824730963</v>
+        <v>8.533079617107587</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>6</v>
       </c>
       <c r="K127" t="n">
-        <v>8.527369824730963</v>
+        <v>8.533079617107587</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>6</v>
       </c>
       <c r="K128" t="n">
-        <v>8.560910589123965</v>
+        <v>8.563832986313626</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>6</v>
       </c>
       <c r="K129" t="n">
-        <v>8.614390892598811</v>
+        <v>8.618593561821877</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>6</v>
       </c>
       <c r="K130" t="n">
-        <v>8.614390892598811</v>
+        <v>8.618593561821877</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>6</v>
       </c>
       <c r="K131" t="n">
-        <v>8.671060242963611</v>
+        <v>8.670332350741491</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>6</v>
       </c>
       <c r="K132" t="n">
-        <v>8.736947290759135</v>
+        <v>8.737214268524154</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>6</v>
       </c>
       <c r="K133" t="n">
-        <v>8.899453321332752</v>
+        <v>8.908018607468405</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>6</v>
       </c>
       <c r="K134" t="n">
-        <v>8.976878747685555</v>
+        <v>8.988453081253281</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>6</v>
       </c>
       <c r="K135" t="n">
-        <v>9.070594825751041</v>
+        <v>9.082257227677049</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>6</v>
       </c>
       <c r="K136" t="n">
-        <v>9.549278556066488</v>
+        <v>9.493207473678842</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>6</v>
       </c>
       <c r="K137" t="n">
-        <v>9.549278556066488</v>
+        <v>9.562461236943456</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>6</v>
       </c>
       <c r="K138" t="n">
-        <v>9.954755082868157</v>
+        <v>9.977092619200015</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>6</v>
       </c>
       <c r="K139" t="n">
-        <v>10.06934780780029</v>
+        <v>10.08724170276781</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>6</v>
       </c>
       <c r="K140" t="n">
-        <v>10.06934780780029</v>
+        <v>10.08724170276781</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>6</v>
       </c>
       <c r="K141" t="n">
-        <v>10.238901419118</v>
+        <v>10.23949170105669</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>6</v>
       </c>
       <c r="K142" t="n">
-        <v>10.238901419118</v>
+        <v>10.23949170105669</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>6</v>
       </c>
       <c r="K143" t="n">
-        <v>10.26949459641317</v>
+        <v>10.26722045282886</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>6</v>
       </c>
       <c r="K144" t="n">
-        <v>10.26591014938876</v>
+        <v>10.26722045282886</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>6</v>
       </c>
       <c r="K145" t="n">
-        <v>10.19922334404454</v>
+        <v>10.23143391066543</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>6</v>
       </c>
       <c r="K146" t="n">
-        <v>10.157607343109</v>
+        <v>10.15570606108186</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="K147" t="n">
-        <v>10.15135689057502</v>
+        <v>10.15088300892058</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>6</v>
       </c>
       <c r="K148" t="n">
-        <v>10.14784199584086</v>
+        <v>10.14758974514527</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>6</v>
       </c>
       <c r="K149" t="n">
-        <v>10.1470747339985</v>
+        <v>10.14761124577038</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>6</v>
       </c>
       <c r="K150" t="n">
-        <v>10.26983464027998</v>
+        <v>10.27903163951837</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>6</v>
       </c>
       <c r="K151" t="n">
-        <v>10.33989583046221</v>
+        <v>10.35214190465377</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>6</v>
       </c>
       <c r="K152" t="n">
-        <v>10.34512600052499</v>
+        <v>10.35214190465377</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>6</v>
       </c>
       <c r="K153" t="n">
-        <v>10.54442709905314</v>
+        <v>10.55296270291239</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>6</v>
       </c>
       <c r="K154" t="n">
-        <v>10.61904542555895</v>
+        <v>10.62689904180005</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>6</v>
       </c>
       <c r="K155" t="n">
-        <v>10.69190504591853</v>
+        <v>10.70087459568568</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>6</v>
       </c>
       <c r="K156" t="n">
-        <v>10.75670064819602</v>
+        <v>10.76665165193404</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>6</v>
       </c>
       <c r="K157" t="n">
-        <v>10.83306256459373</v>
+        <v>10.84256885912033</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>6</v>
       </c>
       <c r="K158" t="n">
-        <v>10.92685448189717</v>
+        <v>10.9287005537623</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>6</v>
       </c>
       <c r="K159" t="n">
-        <v>10.94563504361946</v>
+        <v>10.94679446313857</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>6</v>
       </c>
       <c r="K160" t="n">
-        <v>10.94563504361946</v>
+        <v>10.94679446313857</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>6</v>
       </c>
       <c r="K161" t="n">
-        <v>10.9708481273363</v>
+        <v>10.97041257937665</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>6</v>
       </c>
       <c r="K162" t="n">
-        <v>10.95402348740476</v>
+        <v>10.96875577444526</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>6</v>
       </c>
       <c r="K163" t="n">
-        <v>10.95402348740476</v>
+        <v>10.95155561779406</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="K164" t="n">
-        <v>11.12657912438668</v>
+        <v>11.13825635405057</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>6</v>
       </c>
       <c r="K165" t="n">
-        <v>11.14795892046014</v>
+        <v>11.15692066664699</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>6</v>
       </c>
       <c r="K166" t="n">
-        <v>12.05835100310014</v>
+        <v>12.08239445078688</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>6</v>
       </c>
       <c r="K167" t="n">
-        <v>12.05835100310014</v>
+        <v>12.08239445078688</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>6</v>
       </c>
       <c r="K168" t="n">
-        <v>12.05835100310014</v>
+        <v>12.08239445078688</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>6</v>
       </c>
       <c r="K169" t="n">
-        <v>12.7514670715484</v>
+        <v>12.77050304400545</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>6</v>
       </c>
       <c r="K170" t="n">
-        <v>12.99740495364647</v>
+        <v>13.02315010602378</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>6</v>
       </c>
       <c r="K171" t="n">
-        <v>13.22893290283062</v>
+        <v>13.21812533502401</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>6</v>
       </c>
       <c r="K172" t="n">
-        <v>13.38196974327161</v>
+        <v>13.40533484643394</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>6</v>
       </c>
       <c r="K173" t="n">
-        <v>13.52525134411477</v>
+        <v>13.537726437254</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>6</v>
       </c>
       <c r="K174" t="n">
-        <v>13.52741702524259</v>
+        <v>13.537726437254</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>6</v>
       </c>
       <c r="K175" t="n">
-        <v>13.52513424291054</v>
+        <v>13.51603029642644</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>6</v>
       </c>
       <c r="K176" t="n">
-        <v>13.45373608070102</v>
+        <v>13.43835883743389</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>6</v>
       </c>
       <c r="K177" t="n">
-        <v>13.45373608070102</v>
+        <v>13.43835883743389</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>6</v>
       </c>
       <c r="K178" t="n">
-        <v>12.87687986559452</v>
+        <v>12.87049897305267</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>6</v>
       </c>
       <c r="K179" t="n">
-        <v>12.78203660848068</v>
+        <v>12.7867235364597</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>6</v>
       </c>
       <c r="K180" t="n">
-        <v>12.88732088272113</v>
+        <v>12.89096747702697</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>6</v>
       </c>
       <c r="K181" t="n">
-        <v>13.10364382962162</v>
+        <v>13.05682586052934</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>13.21665282962994</v>
+        <v>13.28858676062679</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>6</v>
       </c>
       <c r="K183" t="n">
-        <v>13.22868636362987</v>
+        <v>13.22856214979317</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>6</v>
       </c>
       <c r="K184" t="n">
-        <v>13.22836695411769</v>
+        <v>13.22815891986998</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>6</v>
       </c>
       <c r="K185" t="n">
-        <v>12.56331902858596</v>
+        <v>12.55278671512658</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>6</v>
       </c>
       <c r="K186" t="n">
-        <v>12.54081239321359</v>
+        <v>12.53041601577564</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>6</v>
       </c>
       <c r="K187" t="n">
-        <v>12.29943552785324</v>
+        <v>12.29751099175077</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>6</v>
       </c>
       <c r="K188" t="n">
-        <v>12.2829233494113</v>
+        <v>12.29277387507475</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>6</v>
       </c>
       <c r="K189" t="n">
-        <v>12.29630371710577</v>
+        <v>12.29958707864683</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>6</v>
       </c>
       <c r="K190" t="n">
-        <v>12.30719348999601</v>
+        <v>12.3111585689887</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>6</v>
       </c>
       <c r="K191" t="n">
-        <v>12.35258897367873</v>
+        <v>12.35319462240552</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>6</v>
       </c>
       <c r="K192" t="n">
-        <v>12.35296321494364</v>
+        <v>12.35342338176835</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>6</v>
       </c>
       <c r="K193" t="n">
-        <v>12.35296321494364</v>
+        <v>12.35342338176835</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>6</v>
       </c>
       <c r="K194" t="n">
-        <v>12.49863818307099</v>
+        <v>12.50552073045885</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>6</v>
       </c>
       <c r="K195" t="n">
-        <v>12.5148122688107</v>
+        <v>12.52090093383555</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>6</v>
       </c>
       <c r="K196" t="n">
-        <v>12.64059519103216</v>
+        <v>12.64447152506395</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>6</v>
       </c>
       <c r="K197" t="n">
-        <v>12.75516335641252</v>
+        <v>12.74559832073476</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="K198" t="n">
-        <v>12.82434787857481</v>
+        <v>12.82934323440308</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>6</v>
       </c>
       <c r="K199" t="n">
-        <v>12.87172396313655</v>
+        <v>12.87675709584725</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>6</v>
       </c>
       <c r="K200" t="n">
-        <v>12.91232242971177</v>
+        <v>12.91446486725206</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>6</v>
       </c>
       <c r="K201" t="n">
-        <v>12.91033089851393</v>
+        <v>12.90839304015632</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>6</v>
       </c>
       <c r="K202" t="n">
-        <v>12.80490227021584</v>
+        <v>12.80505334864713</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>6</v>
       </c>
       <c r="K203" t="n">
-        <v>12.802726964012</v>
+        <v>12.80470013952624</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>6</v>
       </c>
       <c r="K204" t="n">
-        <v>12.7379435150013</v>
+        <v>12.73965880607229</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>6</v>
       </c>
       <c r="K205" t="n">
-        <v>12.6701704866137</v>
+        <v>12.66848637001136</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>6</v>
       </c>
       <c r="K206" t="n">
-        <v>12.6701704866137</v>
+        <v>12.66848637001136</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>6</v>
       </c>
       <c r="K207" t="n">
-        <v>12.49945175787417</v>
+        <v>12.50157920325796</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>6</v>
       </c>
       <c r="K208" t="n">
-        <v>12.28779173644725</v>
+        <v>12.27482045438042</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>6</v>
       </c>
       <c r="K209" t="n">
-        <v>11.88832606873517</v>
+        <v>11.88670746705587</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>6</v>
       </c>
       <c r="K210" t="n">
-        <v>11.88790187061831</v>
+        <v>11.88670746705587</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>6</v>
       </c>
       <c r="K211" t="n">
-        <v>12.16318878177189</v>
+        <v>12.16944965305047</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>6</v>
       </c>
       <c r="K212" t="n">
-        <v>12.16318878177189</v>
+        <v>12.16944965305047</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>6</v>
       </c>
       <c r="K213" t="n">
-        <v>12.2850933308724</v>
+        <v>12.27993027022316</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>6</v>
       </c>
       <c r="K214" t="n">
-        <v>12.30729200089643</v>
+        <v>12.28702891766755</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>6</v>
       </c>
       <c r="K215" t="n">
-        <v>12.46602379984828</v>
+        <v>12.46436863874414</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>6</v>
       </c>
       <c r="K216" t="n">
-        <v>12.49982119715622</v>
+        <v>12.49027804851815</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>6</v>
       </c>
       <c r="K217" t="n">
-        <v>12.52439545881572</v>
+        <v>12.51606374896549</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>6</v>
       </c>
       <c r="K218" t="n">
-        <v>12.54340224967523</v>
+        <v>12.54276937654406</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>6</v>
       </c>
       <c r="K219" t="n">
-        <v>12.57716517946826</v>
+        <v>12.57750305453999</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>6</v>
       </c>
       <c r="K220" t="n">
-        <v>12.57716517946826</v>
+        <v>12.57750305453999</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>6</v>
       </c>
       <c r="K221" t="n">
-        <v>12.55626785778556</v>
+        <v>12.55976736519636</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>6</v>
       </c>
       <c r="K222" t="n">
-        <v>12.71987453457647</v>
+        <v>12.71757990463073</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>6</v>
       </c>
       <c r="K223" t="n">
-        <v>12.71883627017913</v>
+        <v>12.71667284304397</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>6</v>
       </c>
       <c r="K224" t="n">
-        <v>12.6066166473486</v>
+        <v>12.60397629558391</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>6</v>
       </c>
       <c r="K225" t="n">
-        <v>12.56723055679825</v>
+        <v>12.56827758091871</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>6</v>
       </c>
       <c r="K226" t="n">
-        <v>12.54480457182633</v>
+        <v>12.5514918954519</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>6</v>
       </c>
       <c r="K227" t="n">
-        <v>12.5861789188918</v>
+        <v>12.58638839885045</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>6</v>
       </c>
       <c r="K228" t="n">
-        <v>12.54329025449246</v>
+        <v>12.57450141296879</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>6</v>
       </c>
       <c r="K229" t="n">
-        <v>12.54329025449246</v>
+        <v>12.57450141296879</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>6</v>
       </c>
       <c r="K230" t="n">
-        <v>12.47729707886387</v>
+        <v>12.48355666974042</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>6</v>
       </c>
       <c r="K231" t="n">
-        <v>12.47721645407332</v>
+        <v>12.48340261345813</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>6</v>
       </c>
       <c r="K232" t="n">
-        <v>12.49451825327216</v>
+        <v>12.48171924833751</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>6</v>
       </c>
       <c r="K233" t="n">
-        <v>12.49451825327216</v>
+        <v>12.48171924833751</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>6</v>
       </c>
       <c r="K234" t="n">
-        <v>12.50066545811739</v>
+        <v>12.48668153897131</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>6</v>
       </c>
       <c r="K235" t="n">
-        <v>12.50066545811739</v>
+        <v>12.48668153897131</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>6</v>
       </c>
       <c r="K236" t="n">
-        <v>12.5438949370723</v>
+        <v>12.5439341252388</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>6</v>
       </c>
       <c r="K237" t="n">
-        <v>12.55371901573918</v>
+        <v>12.54848340969551</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>6</v>
       </c>
       <c r="K238" t="n">
-        <v>12.55371901573918</v>
+        <v>12.54830848625804</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>6</v>
       </c>
       <c r="K239" t="n">
-        <v>12.55371901573918</v>
+        <v>12.54830848625804</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>6</v>
       </c>
       <c r="K240" t="n">
-        <v>12.557311351392</v>
+        <v>12.54830848625804</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>6</v>
       </c>
       <c r="K241" t="n">
-        <v>12.557311351392</v>
+        <v>12.54701813750437</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>6</v>
       </c>
       <c r="K242" t="n">
-        <v>12.45332192399493</v>
+        <v>12.44763178568168</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>6</v>
       </c>
       <c r="K243" t="n">
-        <v>12.45332192399493</v>
+        <v>12.44763178568168</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>6</v>
       </c>
       <c r="K244" t="n">
-        <v>12.40593897788581</v>
+        <v>12.40318891736148</v>
       </c>
     </row>
     <row r="245">
@@ -10486,7 +10486,7 @@
         <v>6</v>
       </c>
       <c r="K245" t="n">
-        <v>12.19413671075773</v>
+        <v>12.18857742981998</v>
       </c>
     </row>
     <row r="246">
@@ -10527,7 +10527,7 @@
         <v>6</v>
       </c>
       <c r="K246" t="n">
-        <v>12.08990666231681</v>
+        <v>12.08974146158847</v>
       </c>
     </row>
     <row r="247">
@@ -10568,7 +10568,7 @@
         <v>6</v>
       </c>
       <c r="K247" t="n">
-        <v>12.0907797271752</v>
+        <v>12.0911207414604</v>
       </c>
     </row>
     <row r="248">
@@ -10609,7 +10609,7 @@
         <v>6</v>
       </c>
       <c r="K248" t="n">
-        <v>12.09182775173085</v>
+        <v>12.09182940507767</v>
       </c>
     </row>
     <row r="249">
@@ -10650,7 +10650,7 @@
         <v>7</v>
       </c>
       <c r="K249" t="n">
-        <v>12.0953605974493</v>
+        <v>12.09598596468677</v>
       </c>
     </row>
     <row r="250">
@@ -10691,7 +10691,7 @@
         <v>7</v>
       </c>
       <c r="K250" t="n">
-        <v>12.1052150235773</v>
+        <v>12.10642473098731</v>
       </c>
     </row>
     <row r="251">
@@ -10732,7 +10732,7 @@
         <v>7</v>
       </c>
       <c r="K251" t="n">
-        <v>12.1067013623614</v>
+        <v>12.1067270130998</v>
       </c>
     </row>
     <row r="252">
@@ -10773,7 +10773,7 @@
         <v>7</v>
       </c>
       <c r="K252" t="n">
-        <v>12.1605822292569</v>
+        <v>12.16272564065115</v>
       </c>
     </row>
     <row r="253">
@@ -10814,7 +10814,7 @@
         <v>7</v>
       </c>
       <c r="K253" t="n">
-        <v>12.229154793299</v>
+        <v>12.2311785122366</v>
       </c>
     </row>
     <row r="254">
@@ -10855,7 +10855,7 @@
         <v>7</v>
       </c>
       <c r="K254" t="n">
-        <v>12.39318867506093</v>
+        <v>12.39841015681416</v>
       </c>
     </row>
     <row r="255">
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="K255" t="n">
-        <v>12.63399979306722</v>
+        <v>12.63438262869062</v>
       </c>
     </row>
     <row r="256">
@@ -10937,7 +10937,7 @@
         <v>7</v>
       </c>
       <c r="K256" t="n">
-        <v>12.77277566475786</v>
+        <v>12.6423103050087</v>
       </c>
     </row>
     <row r="257">
@@ -10978,7 +10978,7 @@
         <v>7</v>
       </c>
       <c r="K257" t="n">
-        <v>12.92361940445302</v>
+        <v>12.93319383577244</v>
       </c>
     </row>
     <row r="258">
@@ -11019,7 +11019,7 @@
         <v>7</v>
       </c>
       <c r="K258" t="n">
-        <v>13.00581980539971</v>
+        <v>12.99985311520591</v>
       </c>
     </row>
     <row r="259">
@@ -11060,7 +11060,7 @@
         <v>7</v>
       </c>
       <c r="K259" t="n">
-        <v>11.21371983920643</v>
+        <v>11.20503957697606</v>
       </c>
     </row>
     <row r="260">
@@ -11101,7 +11101,7 @@
         <v>7</v>
       </c>
       <c r="K260" t="n">
-        <v>10.91295735455809</v>
+        <v>10.90825101063755</v>
       </c>
     </row>
     <row r="261">
@@ -11142,7 +11142,7 @@
         <v>7</v>
       </c>
       <c r="K261" t="n">
-        <v>10.90630933043323</v>
+        <v>10.90493944776398</v>
       </c>
     </row>
     <row r="262">
@@ -11183,7 +11183,7 @@
         <v>7</v>
       </c>
       <c r="K262" t="n">
-        <v>11.11067537123716</v>
+        <v>11.11747203295466</v>
       </c>
     </row>
     <row r="263">
@@ -11224,7 +11224,7 @@
         <v>7</v>
       </c>
       <c r="K263" t="n">
-        <v>11.12092613981406</v>
+        <v>11.12288100999922</v>
       </c>
     </row>
     <row r="264">
@@ -11265,7 +11265,7 @@
         <v>7</v>
       </c>
       <c r="K264" t="n">
-        <v>11.41452067011062</v>
+        <v>11.32387376443929</v>
       </c>
     </row>
     <row r="265">
@@ -11306,7 +11306,7 @@
         <v>7</v>
       </c>
       <c r="K265" t="n">
-        <v>11.41803390508936</v>
+        <v>11.42106618993412</v>
       </c>
     </row>
     <row r="266">
@@ -11347,7 +11347,7 @@
         <v>7</v>
       </c>
       <c r="K266" t="n">
-        <v>11.42474323728245</v>
+        <v>11.42637066840364</v>
       </c>
     </row>
     <row r="267">
@@ -11388,7 +11388,7 @@
         <v>7</v>
       </c>
       <c r="K267" t="n">
-        <v>11.52098055181535</v>
+        <v>11.52264720329341</v>
       </c>
     </row>
     <row r="268">
@@ -11429,7 +11429,7 @@
         <v>7</v>
       </c>
       <c r="K268" t="n">
-        <v>11.60063562855445</v>
+        <v>11.60571276836865</v>
       </c>
     </row>
     <row r="269">
@@ -11470,7 +11470,7 @@
         <v>7</v>
       </c>
       <c r="K269" t="n">
-        <v>11.63492252765004</v>
+        <v>11.63462537719781</v>
       </c>
     </row>
     <row r="270">
@@ -11511,7 +11511,7 @@
         <v>7</v>
       </c>
       <c r="K270" t="n">
-        <v>11.59571903340261</v>
+        <v>11.59495023728868</v>
       </c>
     </row>
     <row r="271">
@@ -11552,7 +11552,7 @@
         <v>7</v>
       </c>
       <c r="K271" t="n">
-        <v>11.47482411747132</v>
+        <v>11.47413396052639</v>
       </c>
     </row>
     <row r="272">
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="K272" t="n">
-        <v>11.41973742778242</v>
+        <v>11.41489990968029</v>
       </c>
     </row>
     <row r="273">
@@ -11634,7 +11634,7 @@
         <v>7</v>
       </c>
       <c r="K273" t="n">
-        <v>11.41973742778242</v>
+        <v>11.41489990968029</v>
       </c>
     </row>
     <row r="274">
@@ -11675,7 +11675,7 @@
         <v>7</v>
       </c>
       <c r="K274" t="n">
-        <v>11.33187334346197</v>
+        <v>11.32954314383762</v>
       </c>
     </row>
     <row r="275">
@@ -11716,7 +11716,7 @@
         <v>7</v>
       </c>
       <c r="K275" t="n">
-        <v>11.1448551788642</v>
+        <v>11.13895581474152</v>
       </c>
     </row>
     <row r="276">
@@ -11757,7 +11757,7 @@
         <v>7</v>
       </c>
       <c r="K276" t="n">
-        <v>10.98126156842115</v>
+        <v>10.97826395037231</v>
       </c>
     </row>
     <row r="277">
@@ -11798,7 +11798,7 @@
         <v>7</v>
       </c>
       <c r="K277" t="n">
-        <v>10.93366607274151</v>
+        <v>10.93181450941635</v>
       </c>
     </row>
     <row r="278">
@@ -11839,7 +11839,7 @@
         <v>7</v>
       </c>
       <c r="K278" t="n">
-        <v>10.99451771464207</v>
+        <v>10.99471119916965</v>
       </c>
     </row>
     <row r="279">
@@ -11880,7 +11880,7 @@
         <v>7</v>
       </c>
       <c r="K279" t="n">
-        <v>11.01398975244947</v>
+        <v>11.01403501917856</v>
       </c>
     </row>
     <row r="280">
@@ -11921,7 +11921,7 @@
         <v>7</v>
       </c>
       <c r="K280" t="n">
-        <v>10.94464035966949</v>
+        <v>10.98360851806071</v>
       </c>
     </row>
     <row r="281">
@@ -11962,7 +11962,7 @@
         <v>7</v>
       </c>
       <c r="K281" t="n">
-        <v>10.87454393270211</v>
+        <v>10.87185681435206</v>
       </c>
     </row>
     <row r="282">
@@ -12003,7 +12003,7 @@
         <v>7</v>
       </c>
       <c r="K282" t="n">
-        <v>10.8697265650179</v>
+        <v>10.86892360754432</v>
       </c>
     </row>
     <row r="283">
@@ -12044,7 +12044,7 @@
         <v>7</v>
       </c>
       <c r="K283" t="n">
-        <v>10.78344121762455</v>
+        <v>10.77889366400938</v>
       </c>
     </row>
     <row r="284">
@@ -12085,7 +12085,7 @@
         <v>7</v>
       </c>
       <c r="K284" t="n">
-        <v>10.47894384845322</v>
+        <v>10.52198977187999</v>
       </c>
     </row>
     <row r="285">
@@ -12126,7 +12126,7 @@
         <v>7</v>
       </c>
       <c r="K285" t="n">
-        <v>10.40804462411561</v>
+        <v>10.41206116985837</v>
       </c>
     </row>
     <row r="286">
@@ -12167,7 +12167,7 @@
         <v>7</v>
       </c>
       <c r="K286" t="n">
-        <v>10.39862734326141</v>
+        <v>10.40553721523984</v>
       </c>
     </row>
     <row r="287">
@@ -12208,7 +12208,7 @@
         <v>7</v>
       </c>
       <c r="K287" t="n">
-        <v>10.31465250658979</v>
+        <v>10.31001914177254</v>
       </c>
     </row>
     <row r="288">
@@ -12249,7 +12249,7 @@
         <v>7</v>
       </c>
       <c r="K288" t="n">
-        <v>10.09146661452745</v>
+        <v>10.08770532344359</v>
       </c>
     </row>
     <row r="289">
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="K289" t="n">
-        <v>10.09146661452745</v>
+        <v>10.08770532344359</v>
       </c>
     </row>
     <row r="290">
@@ -12331,7 +12331,7 @@
         <v>7</v>
       </c>
       <c r="K290" t="n">
-        <v>10.09146661452745</v>
+        <v>10.08770532344359</v>
       </c>
     </row>
     <row r="291">
@@ -12372,7 +12372,7 @@
         <v>7</v>
       </c>
       <c r="K291" t="n">
-        <v>9.998652005373946</v>
+        <v>9.994630783667898</v>
       </c>
     </row>
     <row r="292">
@@ -12413,7 +12413,7 @@
         <v>7</v>
       </c>
       <c r="K292" t="n">
-        <v>9.627176800538392</v>
+        <v>9.624105172891772</v>
       </c>
     </row>
     <row r="293">
@@ -12454,7 +12454,7 @@
         <v>7</v>
       </c>
       <c r="K293" t="n">
-        <v>9.547101279853123</v>
+        <v>9.543782134055416</v>
       </c>
     </row>
     <row r="294">
@@ -12495,7 +12495,7 @@
         <v>7</v>
       </c>
       <c r="K294" t="n">
-        <v>9.537637545562722</v>
+        <v>9.538941431503558</v>
       </c>
     </row>
     <row r="295">
@@ -12536,7 +12536,7 @@
         <v>7</v>
       </c>
       <c r="K295" t="n">
-        <v>9.339565464354987</v>
+        <v>9.334004061759153</v>
       </c>
     </row>
     <row r="296">
@@ -12577,7 +12577,7 @@
         <v>7</v>
       </c>
       <c r="K296" t="n">
-        <v>9.173625430582824</v>
+        <v>9.176338456358412</v>
       </c>
     </row>
     <row r="297">
@@ -12618,7 +12618,7 @@
         <v>7</v>
       </c>
       <c r="K297" t="n">
-        <v>9.025812203187257</v>
+        <v>9.020285454770427</v>
       </c>
     </row>
     <row r="298">
@@ -12659,7 +12659,7 @@
         <v>7</v>
       </c>
       <c r="K298" t="n">
-        <v>9.006879282161655</v>
+        <v>9.01057541601169</v>
       </c>
     </row>
     <row r="299">
@@ -12700,7 +12700,7 @@
         <v>7</v>
       </c>
       <c r="K299" t="n">
-        <v>9.006879282161655</v>
+        <v>9.01057541601169</v>
       </c>
     </row>
     <row r="300">
@@ -12741,7 +12741,7 @@
         <v>7</v>
       </c>
       <c r="K300" t="n">
-        <v>8.861183513553238</v>
+        <v>8.855761363874596</v>
       </c>
     </row>
     <row r="301">
@@ -12782,7 +12782,7 @@
         <v>7</v>
       </c>
       <c r="K301" t="n">
-        <v>8.547412728732105</v>
+        <v>8.546348272872395</v>
       </c>
     </row>
     <row r="302">
@@ -12823,7 +12823,7 @@
         <v>7</v>
       </c>
       <c r="K302" t="n">
-        <v>8.404708773756287</v>
+        <v>8.403928718084162</v>
       </c>
     </row>
     <row r="303">
@@ -12864,7 +12864,7 @@
         <v>7</v>
       </c>
       <c r="K303" t="n">
-        <v>8.291888650451861</v>
+        <v>8.291770443794743</v>
       </c>
     </row>
     <row r="304">
@@ -12905,7 +12905,7 @@
         <v>7</v>
       </c>
       <c r="K304" t="n">
-        <v>8.291888650451861</v>
+        <v>8.291770443794743</v>
       </c>
     </row>
     <row r="305">
@@ -12946,7 +12946,7 @@
         <v>7</v>
       </c>
       <c r="K305" t="n">
-        <v>8.165029969200923</v>
+        <v>8.186103021316733</v>
       </c>
     </row>
     <row r="306">
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="K306" t="n">
-        <v>8.165029969200923</v>
+        <v>8.186103021316733</v>
       </c>
     </row>
     <row r="307">
@@ -13028,7 +13028,7 @@
         <v>7</v>
       </c>
       <c r="K307" t="n">
-        <v>8.084842963827313</v>
+        <v>8.005525396393255</v>
       </c>
     </row>
     <row r="308">
@@ -13069,7 +13069,7 @@
         <v>7</v>
       </c>
       <c r="K308" t="n">
-        <v>8.084842963827313</v>
+        <v>8.005525396393255</v>
       </c>
     </row>
     <row r="309">
@@ -13110,7 +13110,7 @@
         <v>7</v>
       </c>
       <c r="K309" t="n">
-        <v>10.10820283313736</v>
+        <v>7.976544028032436</v>
       </c>
     </row>
     <row r="310">
@@ -13151,7 +13151,7 @@
         <v>7</v>
       </c>
       <c r="K310" t="n">
-        <v>10.10820283313736</v>
+        <v>7.976544028032436</v>
       </c>
     </row>
     <row r="311">
@@ -13192,7 +13192,7 @@
         <v>7</v>
       </c>
       <c r="K311" t="n">
-        <v>8.012503119472658</v>
+        <v>8.01530679485449</v>
       </c>
     </row>
     <row r="312">
@@ -13233,7 +13233,7 @@
         <v>7</v>
       </c>
       <c r="K312" t="n">
-        <v>8.012503119472658</v>
+        <v>8.01530679485449</v>
       </c>
     </row>
     <row r="313">
@@ -13274,7 +13274,7 @@
         <v>8</v>
       </c>
       <c r="K313" t="n">
-        <v>8.962446912990094</v>
+        <v>9.014228768516777</v>
       </c>
     </row>
     <row r="314">
@@ -13315,7 +13315,7 @@
         <v>8</v>
       </c>
       <c r="K314" t="n">
-        <v>10.04429015944742</v>
+        <v>10.07641504399982</v>
       </c>
     </row>
     <row r="315">
@@ -13356,7 +13356,7 @@
         <v>8</v>
       </c>
       <c r="K315" t="n">
-        <v>10.04429015944742</v>
+        <v>10.07641504399982</v>
       </c>
     </row>
     <row r="316">
@@ -13397,7 +13397,7 @@
         <v>8</v>
       </c>
       <c r="K316" t="n">
-        <v>10.37771817328758</v>
+        <v>10.40712814137166</v>
       </c>
     </row>
     <row r="317">
@@ -13438,7 +13438,7 @@
         <v>8</v>
       </c>
       <c r="K317" t="n">
-        <v>11.03656923159764</v>
+        <v>10.77770329182979</v>
       </c>
     </row>
     <row r="318">
@@ -13479,7 +13479,7 @@
         <v>8</v>
       </c>
       <c r="K318" t="n">
-        <v>11.95788110580619</v>
+        <v>11.99643185863644</v>
       </c>
     </row>
     <row r="319">
@@ -13520,7 +13520,7 @@
         <v>8</v>
       </c>
       <c r="K319" t="n">
-        <v>12.48307800769145</v>
+        <v>12.52406013963824</v>
       </c>
     </row>
     <row r="320">
@@ -13561,7 +13561,7 @@
         <v>8</v>
       </c>
       <c r="K320" t="n">
-        <v>15.0180188076118</v>
+        <v>14.88474784948277</v>
       </c>
     </row>
     <row r="321">
@@ -13602,7 +13602,7 @@
         <v>8</v>
       </c>
       <c r="K321" t="n">
-        <v>14.99113673485492</v>
+        <v>14.98016347076968</v>
       </c>
     </row>
     <row r="322">
@@ -13643,7 +13643,7 @@
         <v>8</v>
       </c>
       <c r="K322" t="n">
-        <v>12.27388887120917</v>
+        <v>12.25951281634962</v>
       </c>
     </row>
     <row r="323">
@@ -13684,7 +13684,7 @@
         <v>8</v>
       </c>
       <c r="K323" t="n">
-        <v>12.12900492634642</v>
+        <v>12.11956971700767</v>
       </c>
     </row>
     <row r="324">
@@ -13725,7 +13725,7 @@
         <v>8</v>
       </c>
       <c r="K324" t="n">
-        <v>12.12900492634642</v>
+        <v>12.11956971700767</v>
       </c>
     </row>
     <row r="325">
@@ -13766,7 +13766,7 @@
         <v>8</v>
       </c>
       <c r="K325" t="n">
-        <v>12.00777517994545</v>
+        <v>11.99484696995554</v>
       </c>
     </row>
     <row r="326">
@@ -13807,7 +13807,7 @@
         <v>8</v>
       </c>
       <c r="K326" t="n">
-        <v>12.00777517994545</v>
+        <v>11.99484696995554</v>
       </c>
     </row>
     <row r="327">
@@ -13848,7 +13848,7 @@
         <v>8</v>
       </c>
       <c r="K327" t="n">
-        <v>3.884433380990276</v>
+        <v>3.866220788643953</v>
       </c>
     </row>
     <row r="328">
@@ -13889,7 +13889,7 @@
         <v>8</v>
       </c>
       <c r="K328" t="n">
-        <v>3.622531082202372</v>
+        <v>3.619099671600917</v>
       </c>
     </row>
     <row r="329">
@@ -13930,7 +13930,7 @@
         <v>8</v>
       </c>
       <c r="K329" t="n">
-        <v>3.598712166195315</v>
+        <v>3.599468442878978</v>
       </c>
     </row>
     <row r="330">
@@ -13971,7 +13971,7 @@
         <v>8</v>
       </c>
       <c r="K330" t="n">
-        <v>3.917737752631037</v>
+        <v>3.924054603056808</v>
       </c>
     </row>
     <row r="331">
@@ -14012,7 +14012,7 @@
         <v>8</v>
       </c>
       <c r="K331" t="n">
-        <v>3.917737752631037</v>
+        <v>3.924054603056808</v>
       </c>
     </row>
     <row r="332">
@@ -14053,7 +14053,7 @@
         <v>8</v>
       </c>
       <c r="K332" t="n">
-        <v>4.136809907297358</v>
+        <v>4.13864359488086</v>
       </c>
     </row>
     <row r="333">
@@ -14094,7 +14094,7 @@
         <v>8</v>
       </c>
       <c r="K333" t="n">
-        <v>4.136809907297358</v>
+        <v>4.13864359488086</v>
       </c>
     </row>
     <row r="334">
@@ -14135,7 +14135,7 @@
         <v>8</v>
       </c>
       <c r="K334" t="n">
-        <v>4.158115381825009</v>
+        <v>4.156886845079575</v>
       </c>
     </row>
     <row r="335">
@@ -14176,7 +14176,7 @@
         <v>8</v>
       </c>
       <c r="K335" t="n">
-        <v>4.158115381825009</v>
+        <v>4.156886845079575</v>
       </c>
     </row>
     <row r="336">
@@ -14217,7 +14217,7 @@
         <v>8</v>
       </c>
       <c r="K336" t="n">
-        <v>4.158115381825009</v>
+        <v>4.156886845079575</v>
       </c>
     </row>
     <row r="337">
@@ -14258,7 +14258,7 @@
         <v>8</v>
       </c>
       <c r="K337" t="n">
-        <v>4.133096902042531</v>
+        <v>4.130619985003639</v>
       </c>
     </row>
     <row r="338">
@@ -14299,7 +14299,7 @@
         <v>8</v>
       </c>
       <c r="K338" t="n">
-        <v>4.070340637306797</v>
+        <v>4.06833159155279</v>
       </c>
     </row>
     <row r="339">
@@ -14340,7 +14340,7 @@
         <v>8</v>
       </c>
       <c r="K339" t="n">
-        <v>4.028032961093987</v>
+        <v>4.030181806090239</v>
       </c>
     </row>
     <row r="340">
@@ -14381,7 +14381,7 @@
         <v>8</v>
       </c>
       <c r="K340" t="n">
-        <v>4.400722162326129</v>
+        <v>4.412786269932516</v>
       </c>
     </row>
     <row r="341">
@@ -14422,7 +14422,7 @@
         <v>8</v>
       </c>
       <c r="K341" t="n">
-        <v>4.90360089809189</v>
+        <v>4.913612422288211</v>
       </c>
     </row>
     <row r="342">
@@ -14463,7 +14463,7 @@
         <v>8</v>
       </c>
       <c r="K342" t="n">
-        <v>5.188158174608672</v>
+        <v>5.192065567431922</v>
       </c>
     </row>
     <row r="343">
@@ -14504,7 +14504,7 @@
         <v>8</v>
       </c>
       <c r="K343" t="n">
-        <v>5.348460043825728</v>
+        <v>5.356106192027201</v>
       </c>
     </row>
     <row r="344">
@@ -14545,7 +14545,7 @@
         <v>8</v>
       </c>
       <c r="K344" t="n">
-        <v>5.348460043825728</v>
+        <v>5.356106192027201</v>
       </c>
     </row>
     <row r="345">
@@ -14586,7 +14586,7 @@
         <v>8</v>
       </c>
       <c r="K345" t="n">
-        <v>5.348460043825728</v>
+        <v>5.356106192027201</v>
       </c>
     </row>
     <row r="346">
@@ -14627,7 +14627,7 @@
         <v>8</v>
       </c>
       <c r="K346" t="n">
-        <v>5.478333415292999</v>
+        <v>5.480016652395757</v>
       </c>
     </row>
     <row r="347">
@@ -14668,7 +14668,7 @@
         <v>8</v>
       </c>
       <c r="K347" t="n">
-        <v>5.488795294232706</v>
+        <v>5.491042703562415</v>
       </c>
     </row>
     <row r="348">
@@ -14709,7 +14709,7 @@
         <v>8</v>
       </c>
       <c r="K348" t="n">
-        <v>5.497198494964292</v>
+        <v>5.491042703562415</v>
       </c>
     </row>
     <row r="349">
@@ -14750,7 +14750,7 @@
         <v>8</v>
       </c>
       <c r="K349" t="n">
-        <v>5.497198494964292</v>
+        <v>5.4983438205277</v>
       </c>
     </row>
     <row r="350">
@@ -14791,7 +14791,7 @@
         <v>8</v>
       </c>
       <c r="K350" t="n">
-        <v>5.486406504185313</v>
+        <v>5.487385431223445</v>
       </c>
     </row>
     <row r="351">
@@ -14832,7 +14832,7 @@
         <v>8</v>
       </c>
       <c r="K351" t="n">
-        <v>5.477443803054033</v>
+        <v>5.47947795380307</v>
       </c>
     </row>
     <row r="352">
@@ -14873,7 +14873,7 @@
         <v>8</v>
       </c>
       <c r="K352" t="n">
-        <v>5.477443803054033</v>
+        <v>5.47947795380307</v>
       </c>
     </row>
     <row r="353">
@@ -14914,7 +14914,7 @@
         <v>8</v>
       </c>
       <c r="K353" t="n">
-        <v>5.491522189547601</v>
+        <v>5.493542937439704</v>
       </c>
     </row>
     <row r="354">
@@ -14955,7 +14955,7 @@
         <v>8</v>
       </c>
       <c r="K354" t="n">
-        <v>5.491522189547601</v>
+        <v>5.493542937439704</v>
       </c>
     </row>
     <row r="355">
@@ -14996,7 +14996,7 @@
         <v>8</v>
       </c>
       <c r="K355" t="n">
-        <v>5.491522189547601</v>
+        <v>5.493542937439704</v>
       </c>
     </row>
     <row r="356">
@@ -15037,7 +15037,7 @@
         <v>8</v>
       </c>
       <c r="K356" t="n">
-        <v>5.707097386306653</v>
+        <v>5.716025162854907</v>
       </c>
     </row>
     <row r="357">
@@ -15078,7 +15078,7 @@
         <v>8</v>
       </c>
       <c r="K357" t="n">
-        <v>6.744113134025241</v>
+        <v>6.749732136920431</v>
       </c>
     </row>
     <row r="358">
@@ -15119,7 +15119,7 @@
         <v>8</v>
       </c>
       <c r="K358" t="n">
-        <v>6.870150773213437</v>
+        <v>6.879319707763301</v>
       </c>
     </row>
     <row r="359">
@@ -15160,7 +15160,7 @@
         <v>8</v>
       </c>
       <c r="K359" t="n">
-        <v>6.870150773213437</v>
+        <v>6.879319707763301</v>
       </c>
     </row>
     <row r="360">
@@ -15201,7 +15201,7 @@
         <v>8</v>
       </c>
       <c r="K360" t="n">
-        <v>7.179054632564358</v>
+        <v>7.184340385818421</v>
       </c>
     </row>
     <row r="361">
@@ -15242,7 +15242,7 @@
         <v>8</v>
       </c>
       <c r="K361" t="n">
-        <v>7.179054632564358</v>
+        <v>7.184340385818421</v>
       </c>
     </row>
     <row r="362">
@@ -15283,7 +15283,7 @@
         <v>8</v>
       </c>
       <c r="K362" t="n">
-        <v>7.179054632564358</v>
+        <v>7.184340385818421</v>
       </c>
     </row>
     <row r="363">
@@ -15324,7 +15324,7 @@
         <v>8</v>
       </c>
       <c r="K363" t="n">
-        <v>7.258122634681863</v>
+        <v>7.260889547423665</v>
       </c>
     </row>
     <row r="364">
@@ -15365,7 +15365,7 @@
         <v>8</v>
       </c>
       <c r="K364" t="n">
-        <v>7.306276720897095</v>
+        <v>7.311845395581873</v>
       </c>
     </row>
     <row r="365">
@@ -15406,7 +15406,7 @@
         <v>8</v>
       </c>
       <c r="K365" t="n">
-        <v>7.348743207040283</v>
+        <v>7.349895543139533</v>
       </c>
     </row>
     <row r="366">
@@ -15447,7 +15447,7 @@
         <v>8</v>
       </c>
       <c r="K366" t="n">
-        <v>7.348743207040283</v>
+        <v>7.349895543139533</v>
       </c>
     </row>
     <row r="367">
@@ -15488,7 +15488,7 @@
         <v>8</v>
       </c>
       <c r="K367" t="n">
-        <v>7.365072711322708</v>
+        <v>7.36701414660349</v>
       </c>
     </row>
     <row r="368">
@@ -15529,7 +15529,7 @@
         <v>8</v>
       </c>
       <c r="K368" t="n">
-        <v>7.404052151859517</v>
+        <v>7.407286514821164</v>
       </c>
     </row>
     <row r="369">
@@ -15570,7 +15570,7 @@
         <v>8</v>
       </c>
       <c r="K369" t="n">
-        <v>7.404052151859517</v>
+        <v>7.407286514821164</v>
       </c>
     </row>
     <row r="370">
@@ -15611,7 +15611,7 @@
         <v>8</v>
       </c>
       <c r="K370" t="n">
-        <v>8.087367220920493</v>
+        <v>8.094757608661167</v>
       </c>
     </row>
     <row r="371">
@@ -15652,7 +15652,7 @@
         <v>8</v>
       </c>
       <c r="K371" t="n">
-        <v>8.340750589921145</v>
+        <v>8.350090046356627</v>
       </c>
     </row>
     <row r="372">
@@ -15693,7 +15693,7 @@
         <v>8</v>
       </c>
       <c r="K372" t="n">
-        <v>8.623745928928621</v>
+        <v>8.628502832098432</v>
       </c>
     </row>
     <row r="373">
@@ -15734,7 +15734,7 @@
         <v>8</v>
       </c>
       <c r="K373" t="n">
-        <v>8.697296182943857</v>
+        <v>8.696161459984177</v>
       </c>
     </row>
     <row r="374">
@@ -15775,7 +15775,7 @@
         <v>8</v>
       </c>
       <c r="K374" t="n">
-        <v>8.659404250601028</v>
+        <v>8.656426495880293</v>
       </c>
     </row>
     <row r="375">
@@ -15816,7 +15816,7 @@
         <v>8</v>
       </c>
       <c r="K375" t="n">
-        <v>8.659404250601028</v>
+        <v>8.656426495880293</v>
       </c>
     </row>
     <row r="376">
@@ -15857,7 +15857,7 @@
         <v>8</v>
       </c>
       <c r="K376" t="n">
-        <v>8.538718972935298</v>
+        <v>8.534190410129144</v>
       </c>
     </row>
     <row r="377">
@@ -15898,7 +15898,7 @@
         <v>8</v>
       </c>
       <c r="K377" t="n">
-        <v>8.538718972935298</v>
+        <v>8.534190410129144</v>
       </c>
     </row>
     <row r="378">
@@ -15939,7 +15939,7 @@
         <v>8</v>
       </c>
       <c r="K378" t="n">
-        <v>8.404225858255087</v>
+        <v>8.402348893859223</v>
       </c>
     </row>
     <row r="379">
@@ -15980,7 +15980,7 @@
         <v>8</v>
       </c>
       <c r="K379" t="n">
-        <v>8.404225858255087</v>
+        <v>8.402348893859223</v>
       </c>
     </row>
     <row r="380">
@@ -16021,7 +16021,7 @@
         <v>8</v>
       </c>
       <c r="K380" t="n">
-        <v>8.391287514488182</v>
+        <v>8.392813887619312</v>
       </c>
     </row>
     <row r="381">
@@ -16062,7 +16062,7 @@
         <v>8</v>
       </c>
       <c r="K381" t="n">
-        <v>8.463281404358067</v>
+        <v>8.466198603222791</v>
       </c>
     </row>
     <row r="382">
@@ -16103,7 +16103,7 @@
         <v>8</v>
       </c>
       <c r="K382" t="n">
-        <v>8.700570124913613</v>
+        <v>8.702461326030033</v>
       </c>
     </row>
     <row r="383">
@@ -16144,7 +16144,7 @@
         <v>8</v>
       </c>
       <c r="K383" t="n">
-        <v>8.799567433230429</v>
+        <v>8.803367861797094</v>
       </c>
     </row>
     <row r="384">
@@ -16185,7 +16185,7 @@
         <v>8</v>
       </c>
       <c r="K384" t="n">
-        <v>8.843701850391344</v>
+        <v>8.843963827093846</v>
       </c>
     </row>
     <row r="385">
@@ -16226,7 +16226,7 @@
         <v>8</v>
       </c>
       <c r="K385" t="n">
-        <v>8.843701850391344</v>
+        <v>8.843963827093846</v>
       </c>
     </row>
     <row r="386">
@@ -16267,7 +16267,7 @@
         <v>8</v>
       </c>
       <c r="K386" t="n">
-        <v>8.837430548943365</v>
+        <v>8.836234455714006</v>
       </c>
     </row>
     <row r="387">
@@ -16308,7 +16308,7 @@
         <v>8</v>
       </c>
       <c r="K387" t="n">
-        <v>8.749537786932692</v>
+        <v>8.74573193277479</v>
       </c>
     </row>
     <row r="388">
@@ -16349,7 +16349,7 @@
         <v>8</v>
       </c>
       <c r="K388" t="n">
-        <v>8.749537786932692</v>
+        <v>8.74573193277479</v>
       </c>
     </row>
     <row r="389">
@@ -16390,7 +16390,7 @@
         <v>8</v>
       </c>
       <c r="K389" t="n">
-        <v>8.55068835419284</v>
+        <v>8.544376116676162</v>
       </c>
     </row>
     <row r="390">
@@ -16431,7 +16431,7 @@
         <v>8</v>
       </c>
       <c r="K390" t="n">
-        <v>8.309932461868314</v>
+        <v>8.304507190322116</v>
       </c>
     </row>
     <row r="391">
@@ -16472,7 +16472,7 @@
         <v>8</v>
       </c>
       <c r="K391" t="n">
-        <v>8.004749304126664</v>
+        <v>8.003965124536361</v>
       </c>
     </row>
     <row r="392">
@@ -16513,7 +16513,7 @@
         <v>8</v>
       </c>
       <c r="K392" t="n">
-        <v>8.004749304126664</v>
+        <v>8.003965124536361</v>
       </c>
     </row>
     <row r="393">
@@ -16554,7 +16554,7 @@
         <v>8</v>
       </c>
       <c r="K393" t="n">
-        <v>7.980597705416823</v>
+        <v>7.980036307729057</v>
       </c>
     </row>
     <row r="394">
@@ -16595,7 +16595,7 @@
         <v>8</v>
       </c>
       <c r="K394" t="n">
-        <v>8.026457772919128</v>
+        <v>8.028046339295912</v>
       </c>
     </row>
     <row r="395">
@@ -16636,7 +16636,7 @@
         <v>8</v>
       </c>
       <c r="K395" t="n">
-        <v>8.05747743403867</v>
+        <v>8.057488374008145</v>
       </c>
     </row>
     <row r="396">
@@ -16677,7 +16677,7 @@
         <v>8</v>
       </c>
       <c r="K396" t="n">
-        <v>8.057113182471557</v>
+        <v>8.05726575353625</v>
       </c>
     </row>
     <row r="397">
@@ -16718,7 +16718,7 @@
         <v>8</v>
       </c>
       <c r="K397" t="n">
-        <v>8.02406702144741</v>
+        <v>8.022469780113418</v>
       </c>
     </row>
     <row r="398">
@@ -16759,7 +16759,7 @@
         <v>8</v>
       </c>
       <c r="K398" t="n">
-        <v>7.879034253500655</v>
+        <v>7.875957728059163</v>
       </c>
     </row>
     <row r="399">
@@ -16800,7 +16800,7 @@
         <v>8</v>
       </c>
       <c r="K399" t="n">
-        <v>7.879034253500655</v>
+        <v>7.875957728059163</v>
       </c>
     </row>
     <row r="400">
@@ -16841,7 +16841,7 @@
         <v>8</v>
       </c>
       <c r="K400" t="n">
-        <v>7.817602445190611</v>
+        <v>7.811851400977439</v>
       </c>
     </row>
     <row r="401">
@@ -16882,7 +16882,7 @@
         <v>8</v>
       </c>
       <c r="K401" t="n">
-        <v>7.817602445190611</v>
+        <v>7.811851400977439</v>
       </c>
     </row>
     <row r="402">
@@ -16923,7 +16923,7 @@
         <v>8</v>
       </c>
       <c r="K402" t="n">
-        <v>7.736349103445513</v>
+        <v>7.731833149068643</v>
       </c>
     </row>
     <row r="403">
@@ -16964,7 +16964,7 @@
         <v>8</v>
       </c>
       <c r="K403" t="n">
-        <v>7.736349103445513</v>
+        <v>7.731833149068643</v>
       </c>
     </row>
     <row r="404">
@@ -17005,7 +17005,7 @@
         <v>8</v>
       </c>
       <c r="K404" t="n">
-        <v>7.736349103445513</v>
+        <v>7.731833149068643</v>
       </c>
     </row>
     <row r="405">
@@ -17046,7 +17046,7 @@
         <v>8</v>
       </c>
       <c r="K405" t="n">
-        <v>7.653238757860326</v>
+        <v>7.650451554109252</v>
       </c>
     </row>
     <row r="406">
@@ -17087,7 +17087,7 @@
         <v>8</v>
       </c>
       <c r="K406" t="n">
-        <v>7.587469474219201</v>
+        <v>7.586686298193537</v>
       </c>
     </row>
     <row r="407">
@@ -17128,7 +17128,7 @@
         <v>8</v>
       </c>
       <c r="K407" t="n">
-        <v>7.534771954579769</v>
+        <v>7.533189913057362</v>
       </c>
     </row>
     <row r="408">
@@ -17169,7 +17169,7 @@
         <v>8</v>
       </c>
       <c r="K408" t="n">
-        <v>7.485768987206552</v>
+        <v>7.483993789352441</v>
       </c>
     </row>
     <row r="409">
@@ -17210,7 +17210,7 @@
         <v>8</v>
       </c>
       <c r="K409" t="n">
-        <v>7.485768987206552</v>
+        <v>7.483993789352441</v>
       </c>
     </row>
     <row r="410">
@@ -17251,7 +17251,7 @@
         <v>8</v>
       </c>
       <c r="K410" t="n">
-        <v>7.420703799823401</v>
+        <v>7.420303174905045</v>
       </c>
     </row>
     <row r="411">
@@ -17292,7 +17292,7 @@
         <v>8</v>
       </c>
       <c r="K411" t="n">
-        <v>7.420703799823401</v>
+        <v>7.420303174905045</v>
       </c>
     </row>
     <row r="412">
@@ -17333,7 +17333,7 @@
         <v>8</v>
       </c>
       <c r="K412" t="n">
-        <v>7.431752521869918</v>
+        <v>7.43139060722263</v>
       </c>
     </row>
     <row r="413">
@@ -17374,7 +17374,7 @@
         <v>8</v>
       </c>
       <c r="K413" t="n">
-        <v>7.42865706242139</v>
+        <v>7.427839703761403</v>
       </c>
     </row>
     <row r="414">
@@ -17415,7 +17415,7 @@
         <v>8</v>
       </c>
       <c r="K414" t="n">
-        <v>7.42865706242139</v>
+        <v>7.427839703761403</v>
       </c>
     </row>
     <row r="415">
@@ -17456,7 +17456,7 @@
         <v>8</v>
       </c>
       <c r="K415" t="n">
-        <v>7.407001590927718</v>
+        <v>7.407552322773213</v>
       </c>
     </row>
     <row r="416">
@@ -17497,7 +17497,7 @@
         <v>8</v>
       </c>
       <c r="K416" t="n">
-        <v>7.407001590927718</v>
+        <v>7.407552322773213</v>
       </c>
     </row>
     <row r="417">
@@ -17538,7 +17538,7 @@
         <v>8</v>
       </c>
       <c r="K417" t="n">
-        <v>7.407001590927718</v>
+        <v>7.407552322773213</v>
       </c>
     </row>
     <row r="418">
@@ -17579,7 +17579,7 @@
         <v>8</v>
       </c>
       <c r="K418" t="n">
-        <v>7.394775202099418</v>
+        <v>7.395089580929015</v>
       </c>
     </row>
     <row r="419">
@@ -17620,7 +17620,7 @@
         <v>8</v>
       </c>
       <c r="K419" t="n">
-        <v>7.47514438232257</v>
+        <v>7.477259583458363</v>
       </c>
     </row>
     <row r="420">
@@ -17661,7 +17661,7 @@
         <v>8</v>
       </c>
       <c r="K420" t="n">
-        <v>7.47514438232257</v>
+        <v>7.477259583458363</v>
       </c>
     </row>
     <row r="421">
@@ -17702,7 +17702,7 @@
         <v>8</v>
       </c>
       <c r="K421" t="n">
-        <v>7.548352359179225</v>
+        <v>7.550597544269779</v>
       </c>
     </row>
     <row r="422">
@@ -17743,7 +17743,7 @@
         <v>8</v>
       </c>
       <c r="K422" t="n">
-        <v>7.690723817060812</v>
+        <v>7.692884463073841</v>
       </c>
     </row>
     <row r="423">
@@ -17784,7 +17784,7 @@
         <v>8</v>
       </c>
       <c r="K423" t="n">
-        <v>7.690723817060812</v>
+        <v>7.692884463073841</v>
       </c>
     </row>
     <row r="424">
@@ -17825,7 +17825,7 @@
         <v>8</v>
       </c>
       <c r="K424" t="n">
-        <v>7.742221438687249</v>
+        <v>7.743614554822457</v>
       </c>
     </row>
     <row r="425">
@@ -17866,7 +17866,7 @@
         <v>8</v>
       </c>
       <c r="K425" t="n">
-        <v>7.760793803264704</v>
+        <v>7.759723709843031</v>
       </c>
     </row>
     <row r="426">
@@ -17907,7 +17907,7 @@
         <v>8</v>
       </c>
       <c r="K426" t="n">
-        <v>7.748843574772835</v>
+        <v>7.747731570425375</v>
       </c>
     </row>
     <row r="427">
@@ -17948,7 +17948,7 @@
         <v>8</v>
       </c>
       <c r="K427" t="n">
-        <v>7.697250352476516</v>
+        <v>7.696936080969674</v>
       </c>
     </row>
     <row r="428">
@@ -17989,7 +17989,7 @@
         <v>8</v>
       </c>
       <c r="K428" t="n">
-        <v>7.663500383200234</v>
+        <v>7.659023738779619</v>
       </c>
     </row>
     <row r="429">
@@ -18030,7 +18030,7 @@
         <v>8</v>
       </c>
       <c r="K429" t="n">
-        <v>7.663500383200234</v>
+        <v>7.659023738779619</v>
       </c>
     </row>
     <row r="430">
@@ -18071,7 +18071,7 @@
         <v>8</v>
       </c>
       <c r="K430" t="n">
-        <v>7.663500383200234</v>
+        <v>7.659023738779619</v>
       </c>
     </row>
     <row r="431">
@@ -18112,7 +18112,7 @@
         <v>8</v>
       </c>
       <c r="K431" t="n">
-        <v>7.620721963861576</v>
+        <v>7.613253674943286</v>
       </c>
     </row>
     <row r="432">
@@ -18153,7 +18153,7 @@
         <v>8</v>
       </c>
       <c r="K432" t="n">
-        <v>7.583389237265234</v>
+        <v>7.579520149495464</v>
       </c>
     </row>
     <row r="433">
@@ -18194,7 +18194,7 @@
         <v>8</v>
       </c>
       <c r="K433" t="n">
-        <v>7.583389237265234</v>
+        <v>7.579520149495464</v>
       </c>
     </row>
     <row r="434">
@@ -18235,7 +18235,7 @@
         <v>8</v>
       </c>
       <c r="K434" t="n">
-        <v>7.493900677171784</v>
+        <v>7.494050648606311</v>
       </c>
     </row>
     <row r="435">
@@ -18276,7 +18276,7 @@
         <v>8</v>
       </c>
       <c r="K435" t="n">
-        <v>7.494215154032344</v>
+        <v>7.497931352678832</v>
       </c>
     </row>
     <row r="436">
@@ -18317,7 +18317,7 @@
         <v>8</v>
       </c>
       <c r="K436" t="n">
-        <v>7.453650234517263</v>
+        <v>7.45236225970664</v>
       </c>
     </row>
     <row r="437">
@@ -18358,7 +18358,7 @@
         <v>8</v>
       </c>
       <c r="K437" t="n">
-        <v>7.412763008893109</v>
+        <v>7.411241378394384</v>
       </c>
     </row>
     <row r="438">
@@ -18399,7 +18399,7 @@
         <v>8</v>
       </c>
       <c r="K438" t="n">
-        <v>7.347021858356184</v>
+        <v>7.345246601113276</v>
       </c>
     </row>
     <row r="439">
@@ -18440,7 +18440,7 @@
         <v>8</v>
       </c>
       <c r="K439" t="n">
-        <v>7.347021858356184</v>
+        <v>7.345246601113276</v>
       </c>
     </row>
     <row r="440">
@@ -18481,7 +18481,7 @@
         <v>8</v>
       </c>
       <c r="K440" t="n">
-        <v>7.226002592159174</v>
+        <v>7.272582399569549</v>
       </c>
     </row>
     <row r="441">
@@ -18522,7 +18522,7 @@
         <v>8</v>
       </c>
       <c r="K441" t="n">
-        <v>7.226002592159174</v>
+        <v>7.224604230130017</v>
       </c>
     </row>
     <row r="442">
@@ -18563,7 +18563,7 @@
         <v>8</v>
       </c>
       <c r="K442" t="n">
-        <v>7.165442106631088</v>
+        <v>7.163175653150597</v>
       </c>
     </row>
     <row r="443">
@@ -18604,7 +18604,7 @@
         <v>8</v>
       </c>
       <c r="K443" t="n">
-        <v>6.999368546921748</v>
+        <v>6.996851428132203</v>
       </c>
     </row>
     <row r="444">
@@ -18645,7 +18645,7 @@
         <v>8</v>
       </c>
       <c r="K444" t="n">
-        <v>6.915708436118067</v>
+        <v>6.913460891584817</v>
       </c>
     </row>
     <row r="445">
@@ -18686,7 +18686,7 @@
         <v>8</v>
       </c>
       <c r="K445" t="n">
-        <v>6.792166952248122</v>
+        <v>6.790568058590531</v>
       </c>
     </row>
     <row r="446">
@@ -18727,7 +18727,7 @@
         <v>8</v>
       </c>
       <c r="K446" t="n">
-        <v>6.734986402288253</v>
+        <v>6.733583289096011</v>
       </c>
     </row>
     <row r="447">
@@ -18768,7 +18768,7 @@
         <v>8</v>
       </c>
       <c r="K447" t="n">
-        <v>6.734986402288253</v>
+        <v>6.733583289096011</v>
       </c>
     </row>
     <row r="448">
@@ -18809,7 +18809,7 @@
         <v>8</v>
       </c>
       <c r="K448" t="n">
-        <v>6.734986402288253</v>
+        <v>6.733583289096011</v>
       </c>
     </row>
     <row r="449">
@@ -18850,7 +18850,7 @@
         <v>8</v>
       </c>
       <c r="K449" t="n">
-        <v>6.692801400992137</v>
+        <v>6.691646525426118</v>
       </c>
     </row>
     <row r="450">
@@ -18891,7 +18891,7 @@
         <v>8</v>
       </c>
       <c r="K450" t="n">
-        <v>6.692801400992137</v>
+        <v>6.691646525426118</v>
       </c>
     </row>
     <row r="451">
@@ -18932,7 +18932,7 @@
         <v>8</v>
       </c>
       <c r="K451" t="n">
-        <v>6.643340672420938</v>
+        <v>6.641757339654447</v>
       </c>
     </row>
     <row r="452">
@@ -18973,7 +18973,7 @@
         <v>8</v>
       </c>
       <c r="K452" t="n">
-        <v>6.643340672420938</v>
+        <v>6.641757339654447</v>
       </c>
     </row>
     <row r="453">
@@ -19014,7 +19014,7 @@
         <v>8</v>
       </c>
       <c r="K453" t="n">
-        <v>6.580519510065824</v>
+        <v>6.57900024170686</v>
       </c>
     </row>
     <row r="454">
@@ -19055,7 +19055,7 @@
         <v>8</v>
       </c>
       <c r="K454" t="n">
-        <v>6.537610963367728</v>
+        <v>6.536602370850352</v>
       </c>
     </row>
     <row r="455">
@@ -19096,7 +19096,7 @@
         <v>8</v>
       </c>
       <c r="K455" t="n">
-        <v>6.537610963367728</v>
+        <v>6.536602370850352</v>
       </c>
     </row>
     <row r="456">
@@ -19137,7 +19137,7 @@
         <v>8</v>
       </c>
       <c r="K456" t="n">
-        <v>6.490942147165584</v>
+        <v>6.490480416926951</v>
       </c>
     </row>
     <row r="457">
@@ -19178,7 +19178,7 @@
         <v>8</v>
       </c>
       <c r="K457" t="n">
-        <v>6.460936097684441</v>
+        <v>6.460664105461015</v>
       </c>
     </row>
     <row r="458">
@@ -19219,7 +19219,7 @@
         <v>8</v>
       </c>
       <c r="K458" t="n">
-        <v>6.4470393470795</v>
+        <v>6.446928624515428</v>
       </c>
     </row>
     <row r="459">
@@ -19260,7 +19260,7 @@
         <v>8</v>
       </c>
       <c r="K459" t="n">
-        <v>6.448807491095861</v>
+        <v>6.448707769067252</v>
       </c>
     </row>
     <row r="460">
@@ -19301,7 +19301,7 @@
         <v>8</v>
       </c>
       <c r="K460" t="n">
-        <v>6.424136051140363</v>
+        <v>6.424388654681563</v>
       </c>
     </row>
     <row r="461">
@@ -19342,7 +19342,7 @@
         <v>8</v>
       </c>
       <c r="K461" t="n">
-        <v>6.424136051140363</v>
+        <v>6.424388654681563</v>
       </c>
     </row>
     <row r="462">
@@ -19383,7 +19383,7 @@
         <v>8</v>
       </c>
       <c r="K462" t="n">
-        <v>6.4918602191819</v>
+        <v>6.492603569918453</v>
       </c>
     </row>
     <row r="463">
@@ -19424,7 +19424,7 @@
         <v>8</v>
       </c>
       <c r="K463" t="n">
-        <v>6.525411988807496</v>
+        <v>6.526124822036008</v>
       </c>
     </row>
     <row r="464">
@@ -19465,7 +19465,7 @@
         <v>8</v>
       </c>
       <c r="K464" t="n">
-        <v>6.722232742995771</v>
+        <v>6.66305508597492</v>
       </c>
     </row>
     <row r="465">
@@ -19506,7 +19506,7 @@
         <v>8</v>
       </c>
       <c r="K465" t="n">
-        <v>6.722232742995771</v>
+        <v>6.723428557209363</v>
       </c>
     </row>
     <row r="466">
@@ -19547,7 +19547,7 @@
         <v>8</v>
       </c>
       <c r="K466" t="n">
-        <v>6.782814894425483</v>
+        <v>6.783885763270686</v>
       </c>
     </row>
     <row r="467">
@@ -19588,7 +19588,7 @@
         <v>8</v>
       </c>
       <c r="K467" t="n">
-        <v>6.828055490999511</v>
+        <v>6.828670365890868</v>
       </c>
     </row>
     <row r="468">
@@ -19629,7 +19629,7 @@
         <v>8</v>
       </c>
       <c r="K468" t="n">
-        <v>6.837217126248234</v>
+        <v>6.837161099155451</v>
       </c>
     </row>
     <row r="469">
@@ -19670,7 +19670,7 @@
         <v>8</v>
       </c>
       <c r="K469" t="n">
-        <v>6.82970298783613</v>
+        <v>6.829509397471056</v>
       </c>
     </row>
     <row r="470">
@@ -19711,7 +19711,7 @@
         <v>8</v>
       </c>
       <c r="K470" t="n">
-        <v>6.82970298783613</v>
+        <v>6.829509397471056</v>
       </c>
     </row>
     <row r="471">
@@ -19752,7 +19752,7 @@
         <v>8</v>
       </c>
       <c r="K471" t="n">
-        <v>6.761866688053744</v>
+        <v>6.761108500186765</v>
       </c>
     </row>
     <row r="472">
@@ -19793,7 +19793,7 @@
         <v>8</v>
       </c>
       <c r="K472" t="n">
-        <v>6.714596691439461</v>
+        <v>6.713791044915213</v>
       </c>
     </row>
     <row r="473">
@@ -19834,7 +19834,7 @@
         <v>8</v>
       </c>
       <c r="K473" t="n">
-        <v>6.502353806899219</v>
+        <v>6.501728373076356</v>
       </c>
     </row>
     <row r="474">
@@ -19875,7 +19875,7 @@
         <v>8</v>
       </c>
       <c r="K474" t="n">
-        <v>6.419123464553661</v>
+        <v>6.419145311553008</v>
       </c>
     </row>
     <row r="475">
@@ -19916,7 +19916,7 @@
         <v>8</v>
       </c>
       <c r="K475" t="n">
-        <v>6.421942525599955</v>
+        <v>6.421924633055831</v>
       </c>
     </row>
     <row r="476">
@@ -19957,7 +19957,7 @@
         <v>8</v>
       </c>
       <c r="K476" t="n">
-        <v>6.487141782442913</v>
+        <v>6.487893436702236</v>
       </c>
     </row>
     <row r="477">
@@ -19998,7 +19998,7 @@
         <v>8</v>
       </c>
       <c r="K477" t="n">
-        <v>6.574359814674901</v>
+        <v>6.575409556332859</v>
       </c>
     </row>
     <row r="478">
@@ -20039,7 +20039,7 @@
         <v>8</v>
       </c>
       <c r="K478" t="n">
-        <v>7.462176575568333</v>
+        <v>7.463208746537341</v>
       </c>
     </row>
     <row r="479">
@@ -20080,7 +20080,7 @@
         <v>8</v>
       </c>
       <c r="K479" t="n">
-        <v>7.543984587235664</v>
+        <v>7.565523816357302</v>
       </c>
     </row>
     <row r="480">
@@ -20121,7 +20121,7 @@
         <v>8</v>
       </c>
       <c r="K480" t="n">
-        <v>7.445559242238189</v>
+        <v>7.445728052035823</v>
       </c>
     </row>
     <row r="481">
@@ -20162,7 +20162,7 @@
         <v>8</v>
       </c>
       <c r="K481" t="n">
-        <v>7.445559242238189</v>
+        <v>7.445728052035823</v>
       </c>
     </row>
     <row r="482">
@@ -20203,7 +20203,7 @@
         <v>8</v>
       </c>
       <c r="K482" t="n">
-        <v>7.445559242238189</v>
+        <v>7.445728052035823</v>
       </c>
     </row>
     <row r="483">
@@ -20244,7 +20244,7 @@
         <v>8</v>
       </c>
       <c r="K483" t="n">
-        <v>7.643434689205128</v>
+        <v>7.644722730513733</v>
       </c>
     </row>
     <row r="484">
@@ -20285,7 +20285,7 @@
         <v>8</v>
       </c>
       <c r="K484" t="n">
-        <v>7.799410224410647</v>
+        <v>7.800788172377027</v>
       </c>
     </row>
     <row r="485">
@@ -20326,7 +20326,7 @@
         <v>8</v>
       </c>
       <c r="K485" t="n">
-        <v>8.54444280178312</v>
+        <v>8.54677620466745</v>
       </c>
     </row>
     <row r="486">
@@ -20367,7 +20367,7 @@
         <v>8</v>
       </c>
       <c r="K486" t="n">
-        <v>8.868340429734996</v>
+        <v>8.869138758361908</v>
       </c>
     </row>
     <row r="487">
@@ -20408,7 +20408,7 @@
         <v>8</v>
       </c>
       <c r="K487" t="n">
-        <v>8.868340429734996</v>
+        <v>8.869138758361908</v>
       </c>
     </row>
     <row r="488">
@@ -20449,7 +20449,7 @@
         <v>8</v>
       </c>
       <c r="K488" t="n">
-        <v>9.590831002629944</v>
+        <v>9.544015582431344</v>
       </c>
     </row>
     <row r="489">
@@ -20490,7 +20490,7 @@
         <v>8</v>
       </c>
       <c r="K489" t="n">
-        <v>9.821170185428153</v>
+        <v>9.728853813024601</v>
       </c>
     </row>
     <row r="490">
@@ -20531,7 +20531,7 @@
         <v>8</v>
       </c>
       <c r="K490" t="n">
-        <v>9.821170185428153</v>
+        <v>9.728853813024601</v>
       </c>
     </row>
     <row r="491">
@@ -20572,7 +20572,7 @@
         <v>8</v>
       </c>
       <c r="K491" t="n">
-        <v>9.757112264971322</v>
+        <v>9.748310394183147</v>
       </c>
     </row>
     <row r="492">
@@ -20613,7 +20613,7 @@
         <v>8</v>
       </c>
       <c r="K492" t="n">
-        <v>9.757112264971322</v>
+        <v>9.748310394183147</v>
       </c>
     </row>
     <row r="493">
@@ -20654,7 +20654,7 @@
         <v>8</v>
       </c>
       <c r="K493" t="n">
-        <v>9.594593115290277</v>
+        <v>9.729808472048479</v>
       </c>
     </row>
     <row r="494">
@@ -20695,7 +20695,7 @@
         <v>8</v>
       </c>
       <c r="K494" t="n">
-        <v>9.679328450888336</v>
+        <v>9.929902948018308</v>
       </c>
     </row>
     <row r="495">
@@ -20736,7 +20736,7 @@
         <v>8</v>
       </c>
       <c r="K495" t="n">
-        <v>10.28204465498533</v>
+        <v>10.47074422528908</v>
       </c>
     </row>
     <row r="496">
@@ -20777,7 +20777,7 @@
         <v>8</v>
       </c>
       <c r="K496" t="n">
-        <v>10.28204465498533</v>
+        <v>10.47074422528908</v>
       </c>
     </row>
     <row r="497">
@@ -20818,7 +20818,7 @@
         <v>8</v>
       </c>
       <c r="K497" t="n">
-        <v>11.65451815317547</v>
+        <v>11.48323668864996</v>
       </c>
     </row>
     <row r="498">
@@ -20859,7 +20859,7 @@
         <v>8</v>
       </c>
       <c r="K498" t="n">
-        <v>11.65451815317547</v>
+        <v>11.48323668864996</v>
       </c>
     </row>
     <row r="499">
@@ -20900,7 +20900,7 @@
         <v>8</v>
       </c>
       <c r="K499" t="n">
-        <v>11.65451815317547</v>
+        <v>11.48323668864996</v>
       </c>
     </row>
     <row r="500">
@@ -20941,7 +20941,7 @@
         <v>8</v>
       </c>
       <c r="K500" t="n">
-        <v>11.65451815317547</v>
+        <v>11.48323668864996</v>
       </c>
     </row>
     <row r="501">
@@ -20982,7 +20982,7 @@
         <v>8</v>
       </c>
       <c r="K501" t="n">
-        <v>12.56764572808129</v>
+        <v>12.22105538427832</v>
       </c>
     </row>
     <row r="502">
@@ -21023,7 +21023,7 @@
         <v>8</v>
       </c>
       <c r="K502" t="n">
-        <v>12.56764572808129</v>
+        <v>12.22105538427832</v>
       </c>
     </row>
     <row r="503">
@@ -21064,7 +21064,7 @@
         <v>8</v>
       </c>
       <c r="K503" t="n">
-        <v>12.56764572808129</v>
+        <v>12.22105538427832</v>
       </c>
     </row>
     <row r="504">
@@ -21105,7 +21105,7 @@
         <v>8</v>
       </c>
       <c r="K504" t="n">
-        <v>12.56764572808129</v>
+        <v>12.22105538427832</v>
       </c>
     </row>
     <row r="505">
@@ -21146,7 +21146,7 @@
         <v>8</v>
       </c>
       <c r="K505" t="n">
-        <v>12.28275412133916</v>
+        <v>12.15772444834559</v>
       </c>
     </row>
     <row r="506">
@@ -21187,7 +21187,7 @@
         <v>8</v>
       </c>
       <c r="K506" t="n">
-        <v>11.95297558050846</v>
+        <v>11.95492638980695</v>
       </c>
     </row>
     <row r="507">
@@ -21228,7 +21228,7 @@
         <v>8</v>
       </c>
       <c r="K507" t="n">
-        <v>11.98256901992308</v>
+        <v>11.98602471761617</v>
       </c>
     </row>
     <row r="508">
@@ -21269,7 +21269,7 @@
         <v>8</v>
       </c>
       <c r="K508" t="n">
-        <v>11.9670705359759</v>
+        <v>11.96068376740817</v>
       </c>
     </row>
     <row r="509">
@@ -21310,7 +21310,7 @@
         <v>8</v>
       </c>
       <c r="K509" t="n">
-        <v>11.94388011410195</v>
+        <v>12.10379158337082</v>
       </c>
     </row>
     <row r="510">
@@ -21351,7 +21351,7 @@
         <v>8</v>
       </c>
       <c r="K510" t="n">
-        <v>11.94984037627904</v>
+        <v>11.95580998810384</v>
       </c>
     </row>
     <row r="511">
@@ -21392,7 +21392,7 @@
         <v>8</v>
       </c>
       <c r="K511" t="n">
-        <v>11.94984037627904</v>
+        <v>11.95580998810384</v>
       </c>
     </row>
     <row r="512">
@@ -21433,7 +21433,7 @@
         <v>8</v>
       </c>
       <c r="K512" t="n">
-        <v>11.98482961517762</v>
+        <v>11.98051490329823</v>
       </c>
     </row>
     <row r="513">
@@ -21474,7 +21474,7 @@
         <v>8</v>
       </c>
       <c r="K513" t="n">
-        <v>11.98916214856828</v>
+        <v>11.98070190146556</v>
       </c>
     </row>
     <row r="514">
@@ -21515,7 +21515,7 @@
         <v>19</v>
       </c>
       <c r="K514" t="n">
-        <v>11.90068433427212</v>
+        <v>11.88117161976044</v>
       </c>
     </row>
     <row r="515">
@@ -21556,7 +21556,7 @@
         <v>19</v>
       </c>
       <c r="K515" t="n">
-        <v>1.854511666012223</v>
+        <v>1.85572978718837</v>
       </c>
     </row>
     <row r="516">
@@ -21597,7 +21597,7 @@
         <v>19</v>
       </c>
       <c r="K516" t="n">
-        <v>1.837854804432754</v>
+        <v>1.838096516283072</v>
       </c>
     </row>
     <row r="517">
@@ -21638,7 +21638,7 @@
         <v>19</v>
       </c>
       <c r="K517" t="n">
-        <v>1.837854804432754</v>
+        <v>1.838096516283072</v>
       </c>
     </row>
     <row r="518">
@@ -21679,7 +21679,7 @@
         <v>19</v>
       </c>
       <c r="K518" t="n">
-        <v>1.878518409700617</v>
+        <v>1.878859936890544</v>
       </c>
     </row>
     <row r="519">
@@ -21720,7 +21720,7 @@
         <v>19</v>
       </c>
       <c r="K519" t="n">
-        <v>1.933052751035792</v>
+        <v>1.933112016300526</v>
       </c>
     </row>
     <row r="520">
@@ -21761,7 +21761,7 @@
         <v>19</v>
       </c>
       <c r="K520" t="n">
-        <v>1.936871790508979</v>
+        <v>1.93709300117483</v>
       </c>
     </row>
     <row r="521">
@@ -21802,7 +21802,7 @@
         <v>19</v>
       </c>
       <c r="K521" t="n">
-        <v>2.031667658521711</v>
+        <v>2.032094218298037</v>
       </c>
     </row>
     <row r="522">
@@ -21843,7 +21843,7 @@
         <v>19</v>
       </c>
       <c r="K522" t="n">
-        <v>2.058067351255422</v>
+        <v>2.058402171770663</v>
       </c>
     </row>
     <row r="523">
@@ -21884,7 +21884,7 @@
         <v>19</v>
       </c>
       <c r="K523" t="n">
-        <v>2.075892286368119</v>
+        <v>2.076223902440697</v>
       </c>
     </row>
     <row r="524">
@@ -21925,7 +21925,7 @@
         <v>19</v>
       </c>
       <c r="K524" t="n">
-        <v>2.103265806005446</v>
+        <v>2.103488704265414</v>
       </c>
     </row>
     <row r="525">
@@ -21966,7 +21966,7 @@
         <v>19</v>
       </c>
       <c r="K525" t="n">
-        <v>2.103265806005446</v>
+        <v>2.103488704265414</v>
       </c>
     </row>
     <row r="526">
@@ -22007,7 +22007,7 @@
         <v>19</v>
       </c>
       <c r="K526" t="n">
-        <v>2.117983780045384</v>
+        <v>2.117826818710892</v>
       </c>
     </row>
     <row r="527">
@@ -22048,7 +22048,7 @@
         <v>19</v>
       </c>
       <c r="K527" t="n">
-        <v>2.074231144885531</v>
+        <v>2.074042264543303</v>
       </c>
     </row>
     <row r="528">
@@ -22089,7 +22089,7 @@
         <v>19</v>
       </c>
       <c r="K528" t="n">
-        <v>2.03991513908291</v>
+        <v>2.039424154469031</v>
       </c>
     </row>
     <row r="529">
@@ -22130,7 +22130,7 @@
         <v>19</v>
       </c>
       <c r="K529" t="n">
-        <v>2.03991513908291</v>
+        <v>2.039424154469031</v>
       </c>
     </row>
     <row r="530">
@@ -22171,7 +22171,7 @@
         <v>19</v>
       </c>
       <c r="K530" t="n">
-        <v>2.03991513908291</v>
+        <v>2.039424154469031</v>
       </c>
     </row>
     <row r="531">
@@ -22212,7 +22212,7 @@
         <v>19</v>
       </c>
       <c r="K531" t="n">
-        <v>1.942154179002464</v>
+        <v>1.941656787344563</v>
       </c>
     </row>
     <row r="532">
@@ -22253,7 +22253,7 @@
         <v>19</v>
       </c>
       <c r="K532" t="n">
-        <v>1.942154179002464</v>
+        <v>1.941656787344563</v>
       </c>
     </row>
     <row r="533">
@@ -22294,7 +22294,7 @@
         <v>19</v>
       </c>
       <c r="K533" t="n">
-        <v>1.918784314882659</v>
+        <v>1.918326736163464</v>
       </c>
     </row>
     <row r="534">
@@ -22335,7 +22335,7 @@
         <v>19</v>
       </c>
       <c r="K534" t="n">
-        <v>1.918784314882659</v>
+        <v>1.918326736163464</v>
       </c>
     </row>
     <row r="535">
@@ -22376,7 +22376,7 @@
         <v>19</v>
       </c>
       <c r="K535" t="n">
-        <v>1.894223016198969</v>
+        <v>1.892101062755566</v>
       </c>
     </row>
     <row r="536">
@@ -22417,7 +22417,7 @@
         <v>19</v>
       </c>
       <c r="K536" t="n">
-        <v>1.856385428556687</v>
+        <v>1.855335433541099</v>
       </c>
     </row>
     <row r="537">
@@ -22458,7 +22458,7 @@
         <v>19</v>
       </c>
       <c r="K537" t="n">
-        <v>1.804787300755467</v>
+        <v>1.804178465313572</v>
       </c>
     </row>
     <row r="538">
@@ -22499,7 +22499,7 @@
         <v>19</v>
       </c>
       <c r="K538" t="n">
-        <v>1.804787300755467</v>
+        <v>1.804178465313572</v>
       </c>
     </row>
     <row r="539">
@@ -22540,7 +22540,7 @@
         <v>19</v>
       </c>
       <c r="K539" t="n">
-        <v>1.754472334537045</v>
+        <v>1.754041407348934</v>
       </c>
     </row>
     <row r="540">
@@ -22581,7 +22581,7 @@
         <v>19</v>
       </c>
       <c r="K540" t="n">
-        <v>1.657703849841727</v>
+        <v>1.657904222626092</v>
       </c>
     </row>
     <row r="541">
@@ -22622,7 +22622,7 @@
         <v>19</v>
       </c>
       <c r="K541" t="n">
-        <v>1.616854180602157</v>
+        <v>1.616756697577507</v>
       </c>
     </row>
     <row r="542">
@@ -22663,7 +22663,7 @@
         <v>19</v>
       </c>
       <c r="K542" t="n">
-        <v>1.616854180602157</v>
+        <v>1.616756697577507</v>
       </c>
     </row>
     <row r="543">
@@ -22704,7 +22704,7 @@
         <v>19</v>
       </c>
       <c r="K543" t="n">
-        <v>1.616854180602157</v>
+        <v>1.616756697577507</v>
       </c>
     </row>
     <row r="544">
@@ -22745,7 +22745,7 @@
         <v>19</v>
       </c>
       <c r="K544" t="n">
-        <v>1.611744298764642</v>
+        <v>1.611774252105334</v>
       </c>
     </row>
     <row r="545">
@@ -22786,7 +22786,7 @@
         <v>19</v>
       </c>
       <c r="K545" t="n">
-        <v>1.666858466927333</v>
+        <v>1.666920973485501</v>
       </c>
     </row>
     <row r="546">
@@ -22827,7 +22827,7 @@
         <v>19</v>
       </c>
       <c r="K546" t="n">
-        <v>1.689231826882966</v>
+        <v>1.689287768206126</v>
       </c>
     </row>
     <row r="547">
@@ -22868,7 +22868,7 @@
         <v>19</v>
       </c>
       <c r="K547" t="n">
-        <v>1.734199260558366</v>
+        <v>1.734218236554714</v>
       </c>
     </row>
     <row r="548">
@@ -22909,7 +22909,7 @@
         <v>19</v>
       </c>
       <c r="K548" t="n">
-        <v>1.734199260558366</v>
+        <v>1.734218236554714</v>
       </c>
     </row>
     <row r="549">
@@ -22950,7 +22950,7 @@
         <v>19</v>
       </c>
       <c r="K549" t="n">
-        <v>1.73466354682686</v>
+        <v>1.734657143280579</v>
       </c>
     </row>
     <row r="550">
@@ -22991,7 +22991,7 @@
         <v>19</v>
       </c>
       <c r="K550" t="n">
-        <v>1.745256985177947</v>
+        <v>1.745240966537199</v>
       </c>
     </row>
     <row r="551">
@@ -23032,7 +23032,7 @@
         <v>19</v>
       </c>
       <c r="K551" t="n">
-        <v>1.765590904903235</v>
+        <v>1.765560393876544</v>
       </c>
     </row>
     <row r="552">
@@ -23073,7 +23073,7 @@
         <v>19</v>
       </c>
       <c r="K552" t="n">
-        <v>1.795184173327543</v>
+        <v>1.79513828850682</v>
       </c>
     </row>
     <row r="553">
@@ -23114,7 +23114,7 @@
         <v>19</v>
       </c>
       <c r="K553" t="n">
-        <v>2.089489818513586</v>
+        <v>2.089237419681632</v>
       </c>
     </row>
     <row r="554">
@@ -23155,7 +23155,7 @@
         <v>19</v>
       </c>
       <c r="K554" t="n">
-        <v>2.14523251725942</v>
+        <v>2.145076667875582</v>
       </c>
     </row>
     <row r="555">
@@ -23196,7 +23196,7 @@
         <v>19</v>
       </c>
       <c r="K555" t="n">
-        <v>2.159373018416571</v>
+        <v>2.15944143022026</v>
       </c>
     </row>
     <row r="556">
@@ -23237,7 +23237,7 @@
         <v>19</v>
       </c>
       <c r="K556" t="n">
-        <v>2.159373018416571</v>
+        <v>2.15944143022026</v>
       </c>
     </row>
     <row r="557">
@@ -23278,7 +23278,7 @@
         <v>19</v>
       </c>
       <c r="K557" t="n">
-        <v>2.063991914309505</v>
+        <v>2.063832727367848</v>
       </c>
     </row>
     <row r="558">
@@ -23319,7 +23319,7 @@
         <v>19</v>
       </c>
       <c r="K558" t="n">
-        <v>2.063991914309505</v>
+        <v>2.063832727367848</v>
       </c>
     </row>
     <row r="559">
@@ -23360,7 +23360,7 @@
         <v>19</v>
       </c>
       <c r="K559" t="n">
-        <v>2.022490606573764</v>
+        <v>2.022941337998093</v>
       </c>
     </row>
     <row r="560">
@@ -23401,7 +23401,7 @@
         <v>19</v>
       </c>
       <c r="K560" t="n">
-        <v>1.876291638813557</v>
+        <v>1.875706703613675</v>
       </c>
     </row>
     <row r="561">
@@ -23442,7 +23442,7 @@
         <v>19</v>
       </c>
       <c r="K561" t="n">
-        <v>1.80215443369725</v>
+        <v>1.79946299865724</v>
       </c>
     </row>
     <row r="562">
@@ -23483,7 +23483,7 @@
         <v>19</v>
       </c>
       <c r="K562" t="n">
-        <v>1.80215443369725</v>
+        <v>1.79946299865724</v>
       </c>
     </row>
     <row r="563">
@@ -23524,7 +23524,7 @@
         <v>19</v>
       </c>
       <c r="K563" t="n">
-        <v>1.722970997575011</v>
+        <v>1.721598063951953</v>
       </c>
     </row>
     <row r="564">
@@ -23565,7 +23565,7 @@
         <v>19</v>
       </c>
       <c r="K564" t="n">
-        <v>1.646222765020578</v>
+        <v>1.645956132626046</v>
       </c>
     </row>
     <row r="565">
@@ -23606,7 +23606,7 @@
         <v>19</v>
       </c>
       <c r="K565" t="n">
-        <v>1.579538031108389</v>
+        <v>1.579441514804663</v>
       </c>
     </row>
     <row r="566">
@@ -23647,7 +23647,7 @@
         <v>19</v>
       </c>
       <c r="K566" t="n">
-        <v>1.337429187511639</v>
+        <v>1.337550832059575</v>
       </c>
     </row>
     <row r="567">
@@ -23688,7 +23688,7 @@
         <v>19</v>
       </c>
       <c r="K567" t="n">
-        <v>1.337429187511639</v>
+        <v>1.337550832059575</v>
       </c>
     </row>
     <row r="568">
@@ -23729,7 +23729,7 @@
         <v>19</v>
       </c>
       <c r="K568" t="n">
-        <v>1.286885940281709</v>
+        <v>1.287095936034658</v>
       </c>
     </row>
     <row r="569">
@@ -23770,7 +23770,7 @@
         <v>19</v>
       </c>
       <c r="K569" t="n">
-        <v>1.214426202748521</v>
+        <v>1.214661446577096</v>
       </c>
     </row>
     <row r="570">
@@ -23811,7 +23811,7 @@
         <v>19</v>
       </c>
       <c r="K570" t="n">
-        <v>1.006379263468961</v>
+        <v>1.006690003685319</v>
       </c>
     </row>
     <row r="571">
@@ -23852,7 +23852,7 @@
         <v>19</v>
       </c>
       <c r="K571" t="n">
-        <v>0.8976153529990392</v>
+        <v>0.8983280707827717</v>
       </c>
     </row>
     <row r="572">
@@ -23893,7 +23893,7 @@
         <v>19</v>
       </c>
       <c r="K572" t="n">
-        <v>0.8089631242646705</v>
+        <v>0.8091551373637743</v>
       </c>
     </row>
     <row r="573">
@@ -23934,7 +23934,7 @@
         <v>19</v>
       </c>
       <c r="K573" t="n">
-        <v>0.8089631242646705</v>
+        <v>0.8091551373637743</v>
       </c>
     </row>
     <row r="574">
@@ -23975,7 +23975,7 @@
         <v>19</v>
       </c>
       <c r="K574" t="n">
-        <v>0.8089631242646705</v>
+        <v>0.8091551373637743</v>
       </c>
     </row>
     <row r="575">
@@ -24016,7 +24016,7 @@
         <v>19</v>
       </c>
       <c r="K575" t="n">
-        <v>0.8753441795877797</v>
+        <v>0.8752282389007977</v>
       </c>
     </row>
     <row r="576">
@@ -24057,7 +24057,7 @@
         <v>19</v>
       </c>
       <c r="K576" t="n">
-        <v>0.9155859948818886</v>
+        <v>0.9152446291018608</v>
       </c>
     </row>
     <row r="577">
@@ -24098,7 +24098,7 @@
         <v>19</v>
       </c>
       <c r="K577" t="n">
-        <v>0.9155859948818886</v>
+        <v>0.9152446291018608</v>
       </c>
     </row>
     <row r="578">
@@ -24139,7 +24139,7 @@
         <v>19</v>
       </c>
       <c r="K578" t="n">
-        <v>0.9977260068355764</v>
+        <v>0.9980172015630825</v>
       </c>
     </row>
     <row r="579">
@@ -24180,7 +24180,7 @@
         <v>19</v>
       </c>
       <c r="K579" t="n">
-        <v>1.032098116289559</v>
+        <v>1.032136080695234</v>
       </c>
     </row>
     <row r="580">
@@ -24221,7 +24221,7 @@
         <v>19</v>
       </c>
       <c r="K580" t="n">
-        <v>1.041232127642572</v>
+        <v>1.04119248242215</v>
       </c>
     </row>
     <row r="581">
@@ -24262,7 +24262,7 @@
         <v>19</v>
       </c>
       <c r="K581" t="n">
-        <v>1.050726503268967</v>
+        <v>1.050763030139293</v>
       </c>
     </row>
     <row r="582">
@@ -24303,7 +24303,7 @@
         <v>19</v>
       </c>
       <c r="K582" t="n">
-        <v>1.075127849159322</v>
+        <v>1.075190997174825</v>
       </c>
     </row>
     <row r="583">
@@ -24344,7 +24344,7 @@
         <v>19</v>
       </c>
       <c r="K583" t="n">
-        <v>1.219802879810765</v>
+        <v>1.219847995745593</v>
       </c>
     </row>
     <row r="584">
@@ -24385,7 +24385,7 @@
         <v>19</v>
       </c>
       <c r="K584" t="n">
-        <v>1.251228837352856</v>
+        <v>1.251237726182353</v>
       </c>
     </row>
   </sheetData>
